--- a/modeles/Canevas_import_ENTREES.xlsx
+++ b/modeles/Canevas_import_ENTREES.xlsx
@@ -272,10 +272,15 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
+        <t>Nom du fournisseur (facultatif).</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
         <t>Code engin (liste). Vide = stock commun.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Remarque libre.</t>
       </text>
@@ -573,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:M1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -586,8 +591,9 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -643,10 +649,15 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>Engin destinataire</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Observations</t>
         </is>
@@ -665,6 +676,7 @@
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -679,6 +691,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -693,6 +706,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -707,6 +721,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -721,6 +736,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -735,6 +751,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -749,6 +766,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -763,6 +781,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -777,6 +796,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -791,6 +811,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -805,6 +826,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -819,6 +841,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -833,6 +856,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -847,6 +871,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -861,6 +886,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -875,6 +901,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -889,6 +916,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -903,6 +931,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -917,6 +946,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -931,6 +961,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -945,6 +976,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -959,6 +991,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -973,6 +1006,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -987,6 +1021,7 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1001,6 +1036,7 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1015,6 +1051,7 @@
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1029,6 +1066,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1043,6 +1081,7 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1057,6 +1096,7 @@
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1071,6 +1111,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1085,6 +1126,7 @@
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1099,6 +1141,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1113,6 +1156,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1127,6 +1171,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1141,6 +1186,7 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1155,6 +1201,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1169,6 +1216,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1183,6 +1231,7 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1197,6 +1246,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1211,6 +1261,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1225,6 +1276,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1239,6 +1291,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="n"/>
       <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1253,6 +1306,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -1267,6 +1321,7 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -1281,6 +1336,7 @@
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -1295,6 +1351,7 @@
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -1309,6 +1366,7 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -1323,6 +1381,7 @@
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="n"/>
       <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -1337,6 +1396,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -1351,6 +1411,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -1365,6 +1426,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="n"/>
       <c r="L52" s="3" t="n"/>
+      <c r="M52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -1379,6 +1441,7 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="n"/>
       <c r="L53" s="3" t="n"/>
+      <c r="M53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -1393,6 +1456,7 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="n"/>
       <c r="L54" s="3" t="n"/>
+      <c r="M54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -1407,6 +1471,7 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="n"/>
+      <c r="M55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -1421,6 +1486,7 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="n"/>
       <c r="L56" s="3" t="n"/>
+      <c r="M56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -1435,6 +1501,7 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="n"/>
       <c r="L57" s="3" t="n"/>
+      <c r="M57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -1449,6 +1516,7 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="n"/>
+      <c r="M58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -1463,6 +1531,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="n"/>
       <c r="L59" s="3" t="n"/>
+      <c r="M59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -1477,6 +1546,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="n"/>
+      <c r="M60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -1491,6 +1561,7 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="n"/>
       <c r="L61" s="3" t="n"/>
+      <c r="M61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -1505,6 +1576,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="n"/>
       <c r="L62" s="3" t="n"/>
+      <c r="M62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -1519,6 +1591,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="n"/>
       <c r="L63" s="3" t="n"/>
+      <c r="M63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -1533,6 +1606,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="n"/>
       <c r="L64" s="3" t="n"/>
+      <c r="M64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -1547,6 +1621,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="n"/>
       <c r="L65" s="3" t="n"/>
+      <c r="M65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -1561,6 +1636,7 @@
       <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="n"/>
       <c r="L66" s="3" t="n"/>
+      <c r="M66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -1575,6 +1651,7 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="n"/>
       <c r="L67" s="3" t="n"/>
+      <c r="M67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -1589,6 +1666,7 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="n"/>
       <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -1603,6 +1681,7 @@
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="n"/>
       <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -1617,6 +1696,7 @@
       <c r="J70" s="3" t="n"/>
       <c r="K70" s="3" t="n"/>
       <c r="L70" s="3" t="n"/>
+      <c r="M70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -1631,6 +1711,7 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="n"/>
       <c r="L71" s="3" t="n"/>
+      <c r="M71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -1645,6 +1726,7 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="n"/>
       <c r="L72" s="3" t="n"/>
+      <c r="M72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -1659,6 +1741,7 @@
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="n"/>
       <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -1673,6 +1756,7 @@
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="n"/>
       <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -1687,6 +1771,7 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="n"/>
       <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -1701,6 +1786,7 @@
       <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="n"/>
       <c r="L76" s="3" t="n"/>
+      <c r="M76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -1715,6 +1801,7 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="n"/>
       <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -1729,6 +1816,7 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="n"/>
       <c r="L78" s="3" t="n"/>
+      <c r="M78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -1743,6 +1831,7 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="n"/>
       <c r="L79" s="3" t="n"/>
+      <c r="M79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -1757,6 +1846,7 @@
       <c r="J80" s="3" t="n"/>
       <c r="K80" s="3" t="n"/>
       <c r="L80" s="3" t="n"/>
+      <c r="M80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -1771,6 +1861,7 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="n"/>
       <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -1785,6 +1876,7 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="n"/>
       <c r="L82" s="3" t="n"/>
+      <c r="M82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -1799,6 +1891,7 @@
       <c r="J83" s="3" t="n"/>
       <c r="K83" s="3" t="n"/>
       <c r="L83" s="3" t="n"/>
+      <c r="M83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -1813,6 +1906,7 @@
       <c r="J84" s="3" t="n"/>
       <c r="K84" s="3" t="n"/>
       <c r="L84" s="3" t="n"/>
+      <c r="M84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -1827,6 +1921,7 @@
       <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="n"/>
       <c r="L85" s="3" t="n"/>
+      <c r="M85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -1841,6 +1936,7 @@
       <c r="J86" s="3" t="n"/>
       <c r="K86" s="3" t="n"/>
       <c r="L86" s="3" t="n"/>
+      <c r="M86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -1855,6 +1951,7 @@
       <c r="J87" s="3" t="n"/>
       <c r="K87" s="3" t="n"/>
       <c r="L87" s="3" t="n"/>
+      <c r="M87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -1869,6 +1966,7 @@
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="n"/>
       <c r="L88" s="3" t="n"/>
+      <c r="M88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -1883,6 +1981,7 @@
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="n"/>
       <c r="L89" s="3" t="n"/>
+      <c r="M89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -1897,6 +1996,7 @@
       <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="n"/>
       <c r="L90" s="3" t="n"/>
+      <c r="M90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -1911,6 +2011,7 @@
       <c r="J91" s="3" t="n"/>
       <c r="K91" s="3" t="n"/>
       <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -1925,6 +2026,7 @@
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="n"/>
       <c r="L92" s="3" t="n"/>
+      <c r="M92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -1939,6 +2041,7 @@
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="n"/>
       <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -1953,6 +2056,7 @@
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="n"/>
       <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -1967,6 +2071,7 @@
       <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="n"/>
       <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -1981,6 +2086,7 @@
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="n"/>
       <c r="L96" s="3" t="n"/>
+      <c r="M96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -1995,6 +2101,7 @@
       <c r="J97" s="3" t="n"/>
       <c r="K97" s="3" t="n"/>
       <c r="L97" s="3" t="n"/>
+      <c r="M97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -2009,6 +2116,7 @@
       <c r="J98" s="3" t="n"/>
       <c r="K98" s="3" t="n"/>
       <c r="L98" s="3" t="n"/>
+      <c r="M98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -2023,6 +2131,7 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="n"/>
       <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -2037,6 +2146,7 @@
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="3" t="n"/>
       <c r="L100" s="3" t="n"/>
+      <c r="M100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -2051,6 +2161,7 @@
       <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="n"/>
       <c r="L101" s="3" t="n"/>
+      <c r="M101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -2065,6 +2176,7 @@
       <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="n"/>
       <c r="L102" s="3" t="n"/>
+      <c r="M102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -2079,6 +2191,7 @@
       <c r="J103" s="3" t="n"/>
       <c r="K103" s="3" t="n"/>
       <c r="L103" s="3" t="n"/>
+      <c r="M103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -2093,6 +2206,7 @@
       <c r="J104" s="3" t="n"/>
       <c r="K104" s="3" t="n"/>
       <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -2107,6 +2221,7 @@
       <c r="J105" s="3" t="n"/>
       <c r="K105" s="3" t="n"/>
       <c r="L105" s="3" t="n"/>
+      <c r="M105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -2121,6 +2236,7 @@
       <c r="J106" s="3" t="n"/>
       <c r="K106" s="3" t="n"/>
       <c r="L106" s="3" t="n"/>
+      <c r="M106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -2135,6 +2251,7 @@
       <c r="J107" s="3" t="n"/>
       <c r="K107" s="3" t="n"/>
       <c r="L107" s="3" t="n"/>
+      <c r="M107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -2149,6 +2266,7 @@
       <c r="J108" s="3" t="n"/>
       <c r="K108" s="3" t="n"/>
       <c r="L108" s="3" t="n"/>
+      <c r="M108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -2163,6 +2281,7 @@
       <c r="J109" s="3" t="n"/>
       <c r="K109" s="3" t="n"/>
       <c r="L109" s="3" t="n"/>
+      <c r="M109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -2177,6 +2296,7 @@
       <c r="J110" s="3" t="n"/>
       <c r="K110" s="3" t="n"/>
       <c r="L110" s="3" t="n"/>
+      <c r="M110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -2191,6 +2311,7 @@
       <c r="J111" s="3" t="n"/>
       <c r="K111" s="3" t="n"/>
       <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -2205,6 +2326,7 @@
       <c r="J112" s="3" t="n"/>
       <c r="K112" s="3" t="n"/>
       <c r="L112" s="3" t="n"/>
+      <c r="M112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -2219,6 +2341,7 @@
       <c r="J113" s="3" t="n"/>
       <c r="K113" s="3" t="n"/>
       <c r="L113" s="3" t="n"/>
+      <c r="M113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -2233,6 +2356,7 @@
       <c r="J114" s="3" t="n"/>
       <c r="K114" s="3" t="n"/>
       <c r="L114" s="3" t="n"/>
+      <c r="M114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -2247,6 +2371,7 @@
       <c r="J115" s="3" t="n"/>
       <c r="K115" s="3" t="n"/>
       <c r="L115" s="3" t="n"/>
+      <c r="M115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -2261,6 +2386,7 @@
       <c r="J116" s="3" t="n"/>
       <c r="K116" s="3" t="n"/>
       <c r="L116" s="3" t="n"/>
+      <c r="M116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -2275,6 +2401,7 @@
       <c r="J117" s="3" t="n"/>
       <c r="K117" s="3" t="n"/>
       <c r="L117" s="3" t="n"/>
+      <c r="M117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -2289,6 +2416,7 @@
       <c r="J118" s="3" t="n"/>
       <c r="K118" s="3" t="n"/>
       <c r="L118" s="3" t="n"/>
+      <c r="M118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -2303,6 +2431,7 @@
       <c r="J119" s="3" t="n"/>
       <c r="K119" s="3" t="n"/>
       <c r="L119" s="3" t="n"/>
+      <c r="M119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -2317,6 +2446,7 @@
       <c r="J120" s="3" t="n"/>
       <c r="K120" s="3" t="n"/>
       <c r="L120" s="3" t="n"/>
+      <c r="M120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -2331,6 +2461,7 @@
       <c r="J121" s="3" t="n"/>
       <c r="K121" s="3" t="n"/>
       <c r="L121" s="3" t="n"/>
+      <c r="M121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -2345,6 +2476,7 @@
       <c r="J122" s="3" t="n"/>
       <c r="K122" s="3" t="n"/>
       <c r="L122" s="3" t="n"/>
+      <c r="M122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -2359,6 +2491,7 @@
       <c r="J123" s="3" t="n"/>
       <c r="K123" s="3" t="n"/>
       <c r="L123" s="3" t="n"/>
+      <c r="M123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -2373,6 +2506,7 @@
       <c r="J124" s="3" t="n"/>
       <c r="K124" s="3" t="n"/>
       <c r="L124" s="3" t="n"/>
+      <c r="M124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -2387,6 +2521,7 @@
       <c r="J125" s="3" t="n"/>
       <c r="K125" s="3" t="n"/>
       <c r="L125" s="3" t="n"/>
+      <c r="M125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -2401,6 +2536,7 @@
       <c r="J126" s="3" t="n"/>
       <c r="K126" s="3" t="n"/>
       <c r="L126" s="3" t="n"/>
+      <c r="M126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -2415,6 +2551,7 @@
       <c r="J127" s="3" t="n"/>
       <c r="K127" s="3" t="n"/>
       <c r="L127" s="3" t="n"/>
+      <c r="M127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -2429,6 +2566,7 @@
       <c r="J128" s="3" t="n"/>
       <c r="K128" s="3" t="n"/>
       <c r="L128" s="3" t="n"/>
+      <c r="M128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -2443,6 +2581,7 @@
       <c r="J129" s="3" t="n"/>
       <c r="K129" s="3" t="n"/>
       <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -2457,6 +2596,7 @@
       <c r="J130" s="3" t="n"/>
       <c r="K130" s="3" t="n"/>
       <c r="L130" s="3" t="n"/>
+      <c r="M130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -2471,6 +2611,7 @@
       <c r="J131" s="3" t="n"/>
       <c r="K131" s="3" t="n"/>
       <c r="L131" s="3" t="n"/>
+      <c r="M131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -2485,6 +2626,7 @@
       <c r="J132" s="3" t="n"/>
       <c r="K132" s="3" t="n"/>
       <c r="L132" s="3" t="n"/>
+      <c r="M132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -2499,6 +2641,7 @@
       <c r="J133" s="3" t="n"/>
       <c r="K133" s="3" t="n"/>
       <c r="L133" s="3" t="n"/>
+      <c r="M133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -2513,6 +2656,7 @@
       <c r="J134" s="3" t="n"/>
       <c r="K134" s="3" t="n"/>
       <c r="L134" s="3" t="n"/>
+      <c r="M134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -2527,6 +2671,7 @@
       <c r="J135" s="3" t="n"/>
       <c r="K135" s="3" t="n"/>
       <c r="L135" s="3" t="n"/>
+      <c r="M135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -2541,6 +2686,7 @@
       <c r="J136" s="3" t="n"/>
       <c r="K136" s="3" t="n"/>
       <c r="L136" s="3" t="n"/>
+      <c r="M136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -2555,6 +2701,7 @@
       <c r="J137" s="3" t="n"/>
       <c r="K137" s="3" t="n"/>
       <c r="L137" s="3" t="n"/>
+      <c r="M137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -2569,6 +2716,7 @@
       <c r="J138" s="3" t="n"/>
       <c r="K138" s="3" t="n"/>
       <c r="L138" s="3" t="n"/>
+      <c r="M138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -2583,6 +2731,7 @@
       <c r="J139" s="3" t="n"/>
       <c r="K139" s="3" t="n"/>
       <c r="L139" s="3" t="n"/>
+      <c r="M139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -2597,6 +2746,7 @@
       <c r="J140" s="3" t="n"/>
       <c r="K140" s="3" t="n"/>
       <c r="L140" s="3" t="n"/>
+      <c r="M140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -2611,6 +2761,7 @@
       <c r="J141" s="3" t="n"/>
       <c r="K141" s="3" t="n"/>
       <c r="L141" s="3" t="n"/>
+      <c r="M141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -2625,6 +2776,7 @@
       <c r="J142" s="3" t="n"/>
       <c r="K142" s="3" t="n"/>
       <c r="L142" s="3" t="n"/>
+      <c r="M142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -2639,6 +2791,7 @@
       <c r="J143" s="3" t="n"/>
       <c r="K143" s="3" t="n"/>
       <c r="L143" s="3" t="n"/>
+      <c r="M143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -2653,6 +2806,7 @@
       <c r="J144" s="3" t="n"/>
       <c r="K144" s="3" t="n"/>
       <c r="L144" s="3" t="n"/>
+      <c r="M144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -2667,6 +2821,7 @@
       <c r="J145" s="3" t="n"/>
       <c r="K145" s="3" t="n"/>
       <c r="L145" s="3" t="n"/>
+      <c r="M145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -2681,6 +2836,7 @@
       <c r="J146" s="3" t="n"/>
       <c r="K146" s="3" t="n"/>
       <c r="L146" s="3" t="n"/>
+      <c r="M146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -2695,6 +2851,7 @@
       <c r="J147" s="3" t="n"/>
       <c r="K147" s="3" t="n"/>
       <c r="L147" s="3" t="n"/>
+      <c r="M147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -2709,6 +2866,7 @@
       <c r="J148" s="3" t="n"/>
       <c r="K148" s="3" t="n"/>
       <c r="L148" s="3" t="n"/>
+      <c r="M148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -2723,6 +2881,7 @@
       <c r="J149" s="3" t="n"/>
       <c r="K149" s="3" t="n"/>
       <c r="L149" s="3" t="n"/>
+      <c r="M149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -2737,6 +2896,7 @@
       <c r="J150" s="3" t="n"/>
       <c r="K150" s="3" t="n"/>
       <c r="L150" s="3" t="n"/>
+      <c r="M150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -2751,6 +2911,7 @@
       <c r="J151" s="3" t="n"/>
       <c r="K151" s="3" t="n"/>
       <c r="L151" s="3" t="n"/>
+      <c r="M151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -2765,6 +2926,7 @@
       <c r="J152" s="3" t="n"/>
       <c r="K152" s="3" t="n"/>
       <c r="L152" s="3" t="n"/>
+      <c r="M152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -2779,6 +2941,7 @@
       <c r="J153" s="3" t="n"/>
       <c r="K153" s="3" t="n"/>
       <c r="L153" s="3" t="n"/>
+      <c r="M153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -2793,6 +2956,7 @@
       <c r="J154" s="3" t="n"/>
       <c r="K154" s="3" t="n"/>
       <c r="L154" s="3" t="n"/>
+      <c r="M154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -2807,6 +2971,7 @@
       <c r="J155" s="3" t="n"/>
       <c r="K155" s="3" t="n"/>
       <c r="L155" s="3" t="n"/>
+      <c r="M155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -2821,6 +2986,7 @@
       <c r="J156" s="3" t="n"/>
       <c r="K156" s="3" t="n"/>
       <c r="L156" s="3" t="n"/>
+      <c r="M156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -2835,6 +3001,7 @@
       <c r="J157" s="3" t="n"/>
       <c r="K157" s="3" t="n"/>
       <c r="L157" s="3" t="n"/>
+      <c r="M157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -2849,6 +3016,7 @@
       <c r="J158" s="3" t="n"/>
       <c r="K158" s="3" t="n"/>
       <c r="L158" s="3" t="n"/>
+      <c r="M158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -2863,6 +3031,7 @@
       <c r="J159" s="3" t="n"/>
       <c r="K159" s="3" t="n"/>
       <c r="L159" s="3" t="n"/>
+      <c r="M159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -2877,6 +3046,7 @@
       <c r="J160" s="3" t="n"/>
       <c r="K160" s="3" t="n"/>
       <c r="L160" s="3" t="n"/>
+      <c r="M160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -2891,6 +3061,7 @@
       <c r="J161" s="3" t="n"/>
       <c r="K161" s="3" t="n"/>
       <c r="L161" s="3" t="n"/>
+      <c r="M161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -2905,6 +3076,7 @@
       <c r="J162" s="3" t="n"/>
       <c r="K162" s="3" t="n"/>
       <c r="L162" s="3" t="n"/>
+      <c r="M162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -2919,6 +3091,7 @@
       <c r="J163" s="3" t="n"/>
       <c r="K163" s="3" t="n"/>
       <c r="L163" s="3" t="n"/>
+      <c r="M163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -2933,6 +3106,7 @@
       <c r="J164" s="3" t="n"/>
       <c r="K164" s="3" t="n"/>
       <c r="L164" s="3" t="n"/>
+      <c r="M164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -2947,6 +3121,7 @@
       <c r="J165" s="3" t="n"/>
       <c r="K165" s="3" t="n"/>
       <c r="L165" s="3" t="n"/>
+      <c r="M165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -2961,6 +3136,7 @@
       <c r="J166" s="3" t="n"/>
       <c r="K166" s="3" t="n"/>
       <c r="L166" s="3" t="n"/>
+      <c r="M166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -2975,6 +3151,7 @@
       <c r="J167" s="3" t="n"/>
       <c r="K167" s="3" t="n"/>
       <c r="L167" s="3" t="n"/>
+      <c r="M167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -2989,6 +3166,7 @@
       <c r="J168" s="3" t="n"/>
       <c r="K168" s="3" t="n"/>
       <c r="L168" s="3" t="n"/>
+      <c r="M168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -3003,6 +3181,7 @@
       <c r="J169" s="3" t="n"/>
       <c r="K169" s="3" t="n"/>
       <c r="L169" s="3" t="n"/>
+      <c r="M169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -3017,6 +3196,7 @@
       <c r="J170" s="3" t="n"/>
       <c r="K170" s="3" t="n"/>
       <c r="L170" s="3" t="n"/>
+      <c r="M170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -3031,6 +3211,7 @@
       <c r="J171" s="3" t="n"/>
       <c r="K171" s="3" t="n"/>
       <c r="L171" s="3" t="n"/>
+      <c r="M171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -3045,6 +3226,7 @@
       <c r="J172" s="3" t="n"/>
       <c r="K172" s="3" t="n"/>
       <c r="L172" s="3" t="n"/>
+      <c r="M172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -3059,6 +3241,7 @@
       <c r="J173" s="3" t="n"/>
       <c r="K173" s="3" t="n"/>
       <c r="L173" s="3" t="n"/>
+      <c r="M173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -3073,6 +3256,7 @@
       <c r="J174" s="3" t="n"/>
       <c r="K174" s="3" t="n"/>
       <c r="L174" s="3" t="n"/>
+      <c r="M174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -3087,6 +3271,7 @@
       <c r="J175" s="3" t="n"/>
       <c r="K175" s="3" t="n"/>
       <c r="L175" s="3" t="n"/>
+      <c r="M175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -3101,6 +3286,7 @@
       <c r="J176" s="3" t="n"/>
       <c r="K176" s="3" t="n"/>
       <c r="L176" s="3" t="n"/>
+      <c r="M176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -3115,6 +3301,7 @@
       <c r="J177" s="3" t="n"/>
       <c r="K177" s="3" t="n"/>
       <c r="L177" s="3" t="n"/>
+      <c r="M177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -3129,6 +3316,7 @@
       <c r="J178" s="3" t="n"/>
       <c r="K178" s="3" t="n"/>
       <c r="L178" s="3" t="n"/>
+      <c r="M178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -3143,6 +3331,7 @@
       <c r="J179" s="3" t="n"/>
       <c r="K179" s="3" t="n"/>
       <c r="L179" s="3" t="n"/>
+      <c r="M179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -3157,6 +3346,7 @@
       <c r="J180" s="3" t="n"/>
       <c r="K180" s="3" t="n"/>
       <c r="L180" s="3" t="n"/>
+      <c r="M180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -3171,6 +3361,7 @@
       <c r="J181" s="3" t="n"/>
       <c r="K181" s="3" t="n"/>
       <c r="L181" s="3" t="n"/>
+      <c r="M181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -3185,6 +3376,7 @@
       <c r="J182" s="3" t="n"/>
       <c r="K182" s="3" t="n"/>
       <c r="L182" s="3" t="n"/>
+      <c r="M182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -3199,6 +3391,7 @@
       <c r="J183" s="3" t="n"/>
       <c r="K183" s="3" t="n"/>
       <c r="L183" s="3" t="n"/>
+      <c r="M183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -3213,6 +3406,7 @@
       <c r="J184" s="3" t="n"/>
       <c r="K184" s="3" t="n"/>
       <c r="L184" s="3" t="n"/>
+      <c r="M184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -3227,6 +3421,7 @@
       <c r="J185" s="3" t="n"/>
       <c r="K185" s="3" t="n"/>
       <c r="L185" s="3" t="n"/>
+      <c r="M185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -3241,6 +3436,7 @@
       <c r="J186" s="3" t="n"/>
       <c r="K186" s="3" t="n"/>
       <c r="L186" s="3" t="n"/>
+      <c r="M186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -3255,6 +3451,7 @@
       <c r="J187" s="3" t="n"/>
       <c r="K187" s="3" t="n"/>
       <c r="L187" s="3" t="n"/>
+      <c r="M187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -3269,6 +3466,7 @@
       <c r="J188" s="3" t="n"/>
       <c r="K188" s="3" t="n"/>
       <c r="L188" s="3" t="n"/>
+      <c r="M188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -3283,6 +3481,7 @@
       <c r="J189" s="3" t="n"/>
       <c r="K189" s="3" t="n"/>
       <c r="L189" s="3" t="n"/>
+      <c r="M189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -3297,6 +3496,7 @@
       <c r="J190" s="3" t="n"/>
       <c r="K190" s="3" t="n"/>
       <c r="L190" s="3" t="n"/>
+      <c r="M190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -3311,6 +3511,7 @@
       <c r="J191" s="3" t="n"/>
       <c r="K191" s="3" t="n"/>
       <c r="L191" s="3" t="n"/>
+      <c r="M191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -3325,6 +3526,7 @@
       <c r="J192" s="3" t="n"/>
       <c r="K192" s="3" t="n"/>
       <c r="L192" s="3" t="n"/>
+      <c r="M192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -3339,6 +3541,7 @@
       <c r="J193" s="3" t="n"/>
       <c r="K193" s="3" t="n"/>
       <c r="L193" s="3" t="n"/>
+      <c r="M193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -3353,6 +3556,7 @@
       <c r="J194" s="3" t="n"/>
       <c r="K194" s="3" t="n"/>
       <c r="L194" s="3" t="n"/>
+      <c r="M194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -3367,6 +3571,7 @@
       <c r="J195" s="3" t="n"/>
       <c r="K195" s="3" t="n"/>
       <c r="L195" s="3" t="n"/>
+      <c r="M195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -3381,6 +3586,7 @@
       <c r="J196" s="3" t="n"/>
       <c r="K196" s="3" t="n"/>
       <c r="L196" s="3" t="n"/>
+      <c r="M196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -3395,6 +3601,7 @@
       <c r="J197" s="3" t="n"/>
       <c r="K197" s="3" t="n"/>
       <c r="L197" s="3" t="n"/>
+      <c r="M197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -3409,6 +3616,7 @@
       <c r="J198" s="3" t="n"/>
       <c r="K198" s="3" t="n"/>
       <c r="L198" s="3" t="n"/>
+      <c r="M198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -3423,6 +3631,7 @@
       <c r="J199" s="3" t="n"/>
       <c r="K199" s="3" t="n"/>
       <c r="L199" s="3" t="n"/>
+      <c r="M199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -3437,6 +3646,7 @@
       <c r="J200" s="3" t="n"/>
       <c r="K200" s="3" t="n"/>
       <c r="L200" s="3" t="n"/>
+      <c r="M200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -3451,6 +3661,7 @@
       <c r="J201" s="3" t="n"/>
       <c r="K201" s="3" t="n"/>
       <c r="L201" s="3" t="n"/>
+      <c r="M201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -3465,6 +3676,7 @@
       <c r="J202" s="3" t="n"/>
       <c r="K202" s="3" t="n"/>
       <c r="L202" s="3" t="n"/>
+      <c r="M202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -3479,6 +3691,7 @@
       <c r="J203" s="3" t="n"/>
       <c r="K203" s="3" t="n"/>
       <c r="L203" s="3" t="n"/>
+      <c r="M203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -3493,6 +3706,7 @@
       <c r="J204" s="3" t="n"/>
       <c r="K204" s="3" t="n"/>
       <c r="L204" s="3" t="n"/>
+      <c r="M204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -3507,6 +3721,7 @@
       <c r="J205" s="3" t="n"/>
       <c r="K205" s="3" t="n"/>
       <c r="L205" s="3" t="n"/>
+      <c r="M205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -3521,6 +3736,7 @@
       <c r="J206" s="3" t="n"/>
       <c r="K206" s="3" t="n"/>
       <c r="L206" s="3" t="n"/>
+      <c r="M206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -3535,6 +3751,7 @@
       <c r="J207" s="3" t="n"/>
       <c r="K207" s="3" t="n"/>
       <c r="L207" s="3" t="n"/>
+      <c r="M207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -3549,6 +3766,7 @@
       <c r="J208" s="3" t="n"/>
       <c r="K208" s="3" t="n"/>
       <c r="L208" s="3" t="n"/>
+      <c r="M208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -3563,6 +3781,7 @@
       <c r="J209" s="3" t="n"/>
       <c r="K209" s="3" t="n"/>
       <c r="L209" s="3" t="n"/>
+      <c r="M209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -3577,6 +3796,7 @@
       <c r="J210" s="3" t="n"/>
       <c r="K210" s="3" t="n"/>
       <c r="L210" s="3" t="n"/>
+      <c r="M210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -3591,6 +3811,7 @@
       <c r="J211" s="3" t="n"/>
       <c r="K211" s="3" t="n"/>
       <c r="L211" s="3" t="n"/>
+      <c r="M211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -3605,6 +3826,7 @@
       <c r="J212" s="3" t="n"/>
       <c r="K212" s="3" t="n"/>
       <c r="L212" s="3" t="n"/>
+      <c r="M212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -3619,6 +3841,7 @@
       <c r="J213" s="3" t="n"/>
       <c r="K213" s="3" t="n"/>
       <c r="L213" s="3" t="n"/>
+      <c r="M213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -3633,6 +3856,7 @@
       <c r="J214" s="3" t="n"/>
       <c r="K214" s="3" t="n"/>
       <c r="L214" s="3" t="n"/>
+      <c r="M214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -3647,6 +3871,7 @@
       <c r="J215" s="3" t="n"/>
       <c r="K215" s="3" t="n"/>
       <c r="L215" s="3" t="n"/>
+      <c r="M215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -3661,6 +3886,7 @@
       <c r="J216" s="3" t="n"/>
       <c r="K216" s="3" t="n"/>
       <c r="L216" s="3" t="n"/>
+      <c r="M216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -3675,6 +3901,7 @@
       <c r="J217" s="3" t="n"/>
       <c r="K217" s="3" t="n"/>
       <c r="L217" s="3" t="n"/>
+      <c r="M217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -3689,6 +3916,7 @@
       <c r="J218" s="3" t="n"/>
       <c r="K218" s="3" t="n"/>
       <c r="L218" s="3" t="n"/>
+      <c r="M218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -3703,6 +3931,7 @@
       <c r="J219" s="3" t="n"/>
       <c r="K219" s="3" t="n"/>
       <c r="L219" s="3" t="n"/>
+      <c r="M219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -3717,6 +3946,7 @@
       <c r="J220" s="3" t="n"/>
       <c r="K220" s="3" t="n"/>
       <c r="L220" s="3" t="n"/>
+      <c r="M220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -3731,6 +3961,7 @@
       <c r="J221" s="3" t="n"/>
       <c r="K221" s="3" t="n"/>
       <c r="L221" s="3" t="n"/>
+      <c r="M221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -3745,6 +3976,7 @@
       <c r="J222" s="3" t="n"/>
       <c r="K222" s="3" t="n"/>
       <c r="L222" s="3" t="n"/>
+      <c r="M222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -3759,6 +3991,7 @@
       <c r="J223" s="3" t="n"/>
       <c r="K223" s="3" t="n"/>
       <c r="L223" s="3" t="n"/>
+      <c r="M223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -3773,6 +4006,7 @@
       <c r="J224" s="3" t="n"/>
       <c r="K224" s="3" t="n"/>
       <c r="L224" s="3" t="n"/>
+      <c r="M224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -3787,6 +4021,7 @@
       <c r="J225" s="3" t="n"/>
       <c r="K225" s="3" t="n"/>
       <c r="L225" s="3" t="n"/>
+      <c r="M225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -3801,6 +4036,7 @@
       <c r="J226" s="3" t="n"/>
       <c r="K226" s="3" t="n"/>
       <c r="L226" s="3" t="n"/>
+      <c r="M226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -3815,6 +4051,7 @@
       <c r="J227" s="3" t="n"/>
       <c r="K227" s="3" t="n"/>
       <c r="L227" s="3" t="n"/>
+      <c r="M227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -3829,6 +4066,7 @@
       <c r="J228" s="3" t="n"/>
       <c r="K228" s="3" t="n"/>
       <c r="L228" s="3" t="n"/>
+      <c r="M228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -3843,6 +4081,7 @@
       <c r="J229" s="3" t="n"/>
       <c r="K229" s="3" t="n"/>
       <c r="L229" s="3" t="n"/>
+      <c r="M229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -3857,6 +4096,7 @@
       <c r="J230" s="3" t="n"/>
       <c r="K230" s="3" t="n"/>
       <c r="L230" s="3" t="n"/>
+      <c r="M230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -3871,6 +4111,7 @@
       <c r="J231" s="3" t="n"/>
       <c r="K231" s="3" t="n"/>
       <c r="L231" s="3" t="n"/>
+      <c r="M231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -3885,6 +4126,7 @@
       <c r="J232" s="3" t="n"/>
       <c r="K232" s="3" t="n"/>
       <c r="L232" s="3" t="n"/>
+      <c r="M232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -3899,6 +4141,7 @@
       <c r="J233" s="3" t="n"/>
       <c r="K233" s="3" t="n"/>
       <c r="L233" s="3" t="n"/>
+      <c r="M233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -3913,6 +4156,7 @@
       <c r="J234" s="3" t="n"/>
       <c r="K234" s="3" t="n"/>
       <c r="L234" s="3" t="n"/>
+      <c r="M234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -3927,6 +4171,7 @@
       <c r="J235" s="3" t="n"/>
       <c r="K235" s="3" t="n"/>
       <c r="L235" s="3" t="n"/>
+      <c r="M235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -3941,6 +4186,7 @@
       <c r="J236" s="3" t="n"/>
       <c r="K236" s="3" t="n"/>
       <c r="L236" s="3" t="n"/>
+      <c r="M236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -3955,6 +4201,7 @@
       <c r="J237" s="3" t="n"/>
       <c r="K237" s="3" t="n"/>
       <c r="L237" s="3" t="n"/>
+      <c r="M237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -3969,6 +4216,7 @@
       <c r="J238" s="3" t="n"/>
       <c r="K238" s="3" t="n"/>
       <c r="L238" s="3" t="n"/>
+      <c r="M238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -3983,6 +4231,7 @@
       <c r="J239" s="3" t="n"/>
       <c r="K239" s="3" t="n"/>
       <c r="L239" s="3" t="n"/>
+      <c r="M239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -3997,6 +4246,7 @@
       <c r="J240" s="3" t="n"/>
       <c r="K240" s="3" t="n"/>
       <c r="L240" s="3" t="n"/>
+      <c r="M240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -4011,6 +4261,7 @@
       <c r="J241" s="3" t="n"/>
       <c r="K241" s="3" t="n"/>
       <c r="L241" s="3" t="n"/>
+      <c r="M241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -4025,6 +4276,7 @@
       <c r="J242" s="3" t="n"/>
       <c r="K242" s="3" t="n"/>
       <c r="L242" s="3" t="n"/>
+      <c r="M242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -4039,6 +4291,7 @@
       <c r="J243" s="3" t="n"/>
       <c r="K243" s="3" t="n"/>
       <c r="L243" s="3" t="n"/>
+      <c r="M243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -4053,6 +4306,7 @@
       <c r="J244" s="3" t="n"/>
       <c r="K244" s="3" t="n"/>
       <c r="L244" s="3" t="n"/>
+      <c r="M244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -4067,6 +4321,7 @@
       <c r="J245" s="3" t="n"/>
       <c r="K245" s="3" t="n"/>
       <c r="L245" s="3" t="n"/>
+      <c r="M245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -4081,6 +4336,7 @@
       <c r="J246" s="3" t="n"/>
       <c r="K246" s="3" t="n"/>
       <c r="L246" s="3" t="n"/>
+      <c r="M246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -4095,6 +4351,7 @@
       <c r="J247" s="3" t="n"/>
       <c r="K247" s="3" t="n"/>
       <c r="L247" s="3" t="n"/>
+      <c r="M247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -4109,6 +4366,7 @@
       <c r="J248" s="3" t="n"/>
       <c r="K248" s="3" t="n"/>
       <c r="L248" s="3" t="n"/>
+      <c r="M248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -4123,6 +4381,7 @@
       <c r="J249" s="3" t="n"/>
       <c r="K249" s="3" t="n"/>
       <c r="L249" s="3" t="n"/>
+      <c r="M249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -4137,6 +4396,7 @@
       <c r="J250" s="3" t="n"/>
       <c r="K250" s="3" t="n"/>
       <c r="L250" s="3" t="n"/>
+      <c r="M250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -4151,6 +4411,7 @@
       <c r="J251" s="3" t="n"/>
       <c r="K251" s="3" t="n"/>
       <c r="L251" s="3" t="n"/>
+      <c r="M251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -4165,6 +4426,7 @@
       <c r="J252" s="3" t="n"/>
       <c r="K252" s="3" t="n"/>
       <c r="L252" s="3" t="n"/>
+      <c r="M252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -4179,6 +4441,7 @@
       <c r="J253" s="3" t="n"/>
       <c r="K253" s="3" t="n"/>
       <c r="L253" s="3" t="n"/>
+      <c r="M253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -4193,6 +4456,7 @@
       <c r="J254" s="3" t="n"/>
       <c r="K254" s="3" t="n"/>
       <c r="L254" s="3" t="n"/>
+      <c r="M254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -4207,6 +4471,7 @@
       <c r="J255" s="3" t="n"/>
       <c r="K255" s="3" t="n"/>
       <c r="L255" s="3" t="n"/>
+      <c r="M255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -4221,6 +4486,7 @@
       <c r="J256" s="3" t="n"/>
       <c r="K256" s="3" t="n"/>
       <c r="L256" s="3" t="n"/>
+      <c r="M256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -4235,6 +4501,7 @@
       <c r="J257" s="3" t="n"/>
       <c r="K257" s="3" t="n"/>
       <c r="L257" s="3" t="n"/>
+      <c r="M257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -4249,6 +4516,7 @@
       <c r="J258" s="3" t="n"/>
       <c r="K258" s="3" t="n"/>
       <c r="L258" s="3" t="n"/>
+      <c r="M258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -4263,6 +4531,7 @@
       <c r="J259" s="3" t="n"/>
       <c r="K259" s="3" t="n"/>
       <c r="L259" s="3" t="n"/>
+      <c r="M259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -4277,6 +4546,7 @@
       <c r="J260" s="3" t="n"/>
       <c r="K260" s="3" t="n"/>
       <c r="L260" s="3" t="n"/>
+      <c r="M260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -4291,6 +4561,7 @@
       <c r="J261" s="3" t="n"/>
       <c r="K261" s="3" t="n"/>
       <c r="L261" s="3" t="n"/>
+      <c r="M261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -4305,6 +4576,7 @@
       <c r="J262" s="3" t="n"/>
       <c r="K262" s="3" t="n"/>
       <c r="L262" s="3" t="n"/>
+      <c r="M262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -4319,6 +4591,7 @@
       <c r="J263" s="3" t="n"/>
       <c r="K263" s="3" t="n"/>
       <c r="L263" s="3" t="n"/>
+      <c r="M263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -4333,6 +4606,7 @@
       <c r="J264" s="3" t="n"/>
       <c r="K264" s="3" t="n"/>
       <c r="L264" s="3" t="n"/>
+      <c r="M264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -4347,6 +4621,7 @@
       <c r="J265" s="3" t="n"/>
       <c r="K265" s="3" t="n"/>
       <c r="L265" s="3" t="n"/>
+      <c r="M265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -4361,6 +4636,7 @@
       <c r="J266" s="3" t="n"/>
       <c r="K266" s="3" t="n"/>
       <c r="L266" s="3" t="n"/>
+      <c r="M266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -4375,6 +4651,7 @@
       <c r="J267" s="3" t="n"/>
       <c r="K267" s="3" t="n"/>
       <c r="L267" s="3" t="n"/>
+      <c r="M267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -4389,6 +4666,7 @@
       <c r="J268" s="3" t="n"/>
       <c r="K268" s="3" t="n"/>
       <c r="L268" s="3" t="n"/>
+      <c r="M268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -4403,6 +4681,7 @@
       <c r="J269" s="3" t="n"/>
       <c r="K269" s="3" t="n"/>
       <c r="L269" s="3" t="n"/>
+      <c r="M269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -4417,6 +4696,7 @@
       <c r="J270" s="3" t="n"/>
       <c r="K270" s="3" t="n"/>
       <c r="L270" s="3" t="n"/>
+      <c r="M270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -4431,6 +4711,7 @@
       <c r="J271" s="3" t="n"/>
       <c r="K271" s="3" t="n"/>
       <c r="L271" s="3" t="n"/>
+      <c r="M271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -4445,6 +4726,7 @@
       <c r="J272" s="3" t="n"/>
       <c r="K272" s="3" t="n"/>
       <c r="L272" s="3" t="n"/>
+      <c r="M272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -4459,6 +4741,7 @@
       <c r="J273" s="3" t="n"/>
       <c r="K273" s="3" t="n"/>
       <c r="L273" s="3" t="n"/>
+      <c r="M273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -4473,6 +4756,7 @@
       <c r="J274" s="3" t="n"/>
       <c r="K274" s="3" t="n"/>
       <c r="L274" s="3" t="n"/>
+      <c r="M274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -4487,6 +4771,7 @@
       <c r="J275" s="3" t="n"/>
       <c r="K275" s="3" t="n"/>
       <c r="L275" s="3" t="n"/>
+      <c r="M275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -4501,6 +4786,7 @@
       <c r="J276" s="3" t="n"/>
       <c r="K276" s="3" t="n"/>
       <c r="L276" s="3" t="n"/>
+      <c r="M276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -4515,6 +4801,7 @@
       <c r="J277" s="3" t="n"/>
       <c r="K277" s="3" t="n"/>
       <c r="L277" s="3" t="n"/>
+      <c r="M277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -4529,6 +4816,7 @@
       <c r="J278" s="3" t="n"/>
       <c r="K278" s="3" t="n"/>
       <c r="L278" s="3" t="n"/>
+      <c r="M278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -4543,6 +4831,7 @@
       <c r="J279" s="3" t="n"/>
       <c r="K279" s="3" t="n"/>
       <c r="L279" s="3" t="n"/>
+      <c r="M279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -4557,6 +4846,7 @@
       <c r="J280" s="3" t="n"/>
       <c r="K280" s="3" t="n"/>
       <c r="L280" s="3" t="n"/>
+      <c r="M280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -4571,6 +4861,7 @@
       <c r="J281" s="3" t="n"/>
       <c r="K281" s="3" t="n"/>
       <c r="L281" s="3" t="n"/>
+      <c r="M281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -4585,6 +4876,7 @@
       <c r="J282" s="3" t="n"/>
       <c r="K282" s="3" t="n"/>
       <c r="L282" s="3" t="n"/>
+      <c r="M282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -4599,6 +4891,7 @@
       <c r="J283" s="3" t="n"/>
       <c r="K283" s="3" t="n"/>
       <c r="L283" s="3" t="n"/>
+      <c r="M283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -4613,6 +4906,7 @@
       <c r="J284" s="3" t="n"/>
       <c r="K284" s="3" t="n"/>
       <c r="L284" s="3" t="n"/>
+      <c r="M284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -4627,6 +4921,7 @@
       <c r="J285" s="3" t="n"/>
       <c r="K285" s="3" t="n"/>
       <c r="L285" s="3" t="n"/>
+      <c r="M285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -4641,6 +4936,7 @@
       <c r="J286" s="3" t="n"/>
       <c r="K286" s="3" t="n"/>
       <c r="L286" s="3" t="n"/>
+      <c r="M286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -4655,6 +4951,7 @@
       <c r="J287" s="3" t="n"/>
       <c r="K287" s="3" t="n"/>
       <c r="L287" s="3" t="n"/>
+      <c r="M287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -4669,6 +4966,7 @@
       <c r="J288" s="3" t="n"/>
       <c r="K288" s="3" t="n"/>
       <c r="L288" s="3" t="n"/>
+      <c r="M288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -4683,6 +4981,7 @@
       <c r="J289" s="3" t="n"/>
       <c r="K289" s="3" t="n"/>
       <c r="L289" s="3" t="n"/>
+      <c r="M289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -4697,6 +4996,7 @@
       <c r="J290" s="3" t="n"/>
       <c r="K290" s="3" t="n"/>
       <c r="L290" s="3" t="n"/>
+      <c r="M290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -4711,6 +5011,7 @@
       <c r="J291" s="3" t="n"/>
       <c r="K291" s="3" t="n"/>
       <c r="L291" s="3" t="n"/>
+      <c r="M291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -4725,6 +5026,7 @@
       <c r="J292" s="3" t="n"/>
       <c r="K292" s="3" t="n"/>
       <c r="L292" s="3" t="n"/>
+      <c r="M292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -4739,6 +5041,7 @@
       <c r="J293" s="3" t="n"/>
       <c r="K293" s="3" t="n"/>
       <c r="L293" s="3" t="n"/>
+      <c r="M293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -4753,6 +5056,7 @@
       <c r="J294" s="3" t="n"/>
       <c r="K294" s="3" t="n"/>
       <c r="L294" s="3" t="n"/>
+      <c r="M294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -4767,6 +5071,7 @@
       <c r="J295" s="3" t="n"/>
       <c r="K295" s="3" t="n"/>
       <c r="L295" s="3" t="n"/>
+      <c r="M295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -4781,6 +5086,7 @@
       <c r="J296" s="3" t="n"/>
       <c r="K296" s="3" t="n"/>
       <c r="L296" s="3" t="n"/>
+      <c r="M296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -4795,6 +5101,7 @@
       <c r="J297" s="3" t="n"/>
       <c r="K297" s="3" t="n"/>
       <c r="L297" s="3" t="n"/>
+      <c r="M297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -4809,6 +5116,7 @@
       <c r="J298" s="3" t="n"/>
       <c r="K298" s="3" t="n"/>
       <c r="L298" s="3" t="n"/>
+      <c r="M298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -4823,6 +5131,7 @@
       <c r="J299" s="3" t="n"/>
       <c r="K299" s="3" t="n"/>
       <c r="L299" s="3" t="n"/>
+      <c r="M299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -4837,6 +5146,7 @@
       <c r="J300" s="3" t="n"/>
       <c r="K300" s="3" t="n"/>
       <c r="L300" s="3" t="n"/>
+      <c r="M300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -4851,6 +5161,7 @@
       <c r="J301" s="3" t="n"/>
       <c r="K301" s="3" t="n"/>
       <c r="L301" s="3" t="n"/>
+      <c r="M301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -4865,6 +5176,7 @@
       <c r="J302" s="3" t="n"/>
       <c r="K302" s="3" t="n"/>
       <c r="L302" s="3" t="n"/>
+      <c r="M302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -4879,6 +5191,7 @@
       <c r="J303" s="3" t="n"/>
       <c r="K303" s="3" t="n"/>
       <c r="L303" s="3" t="n"/>
+      <c r="M303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -4893,6 +5206,7 @@
       <c r="J304" s="3" t="n"/>
       <c r="K304" s="3" t="n"/>
       <c r="L304" s="3" t="n"/>
+      <c r="M304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -4907,6 +5221,7 @@
       <c r="J305" s="3" t="n"/>
       <c r="K305" s="3" t="n"/>
       <c r="L305" s="3" t="n"/>
+      <c r="M305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -4921,6 +5236,7 @@
       <c r="J306" s="3" t="n"/>
       <c r="K306" s="3" t="n"/>
       <c r="L306" s="3" t="n"/>
+      <c r="M306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -4935,6 +5251,7 @@
       <c r="J307" s="3" t="n"/>
       <c r="K307" s="3" t="n"/>
       <c r="L307" s="3" t="n"/>
+      <c r="M307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -4949,6 +5266,7 @@
       <c r="J308" s="3" t="n"/>
       <c r="K308" s="3" t="n"/>
       <c r="L308" s="3" t="n"/>
+      <c r="M308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -4963,6 +5281,7 @@
       <c r="J309" s="3" t="n"/>
       <c r="K309" s="3" t="n"/>
       <c r="L309" s="3" t="n"/>
+      <c r="M309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -4977,6 +5296,7 @@
       <c r="J310" s="3" t="n"/>
       <c r="K310" s="3" t="n"/>
       <c r="L310" s="3" t="n"/>
+      <c r="M310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -4991,6 +5311,7 @@
       <c r="J311" s="3" t="n"/>
       <c r="K311" s="3" t="n"/>
       <c r="L311" s="3" t="n"/>
+      <c r="M311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -5005,6 +5326,7 @@
       <c r="J312" s="3" t="n"/>
       <c r="K312" s="3" t="n"/>
       <c r="L312" s="3" t="n"/>
+      <c r="M312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -5019,6 +5341,7 @@
       <c r="J313" s="3" t="n"/>
       <c r="K313" s="3" t="n"/>
       <c r="L313" s="3" t="n"/>
+      <c r="M313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -5033,6 +5356,7 @@
       <c r="J314" s="3" t="n"/>
       <c r="K314" s="3" t="n"/>
       <c r="L314" s="3" t="n"/>
+      <c r="M314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -5047,6 +5371,7 @@
       <c r="J315" s="3" t="n"/>
       <c r="K315" s="3" t="n"/>
       <c r="L315" s="3" t="n"/>
+      <c r="M315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -5061,6 +5386,7 @@
       <c r="J316" s="3" t="n"/>
       <c r="K316" s="3" t="n"/>
       <c r="L316" s="3" t="n"/>
+      <c r="M316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -5075,6 +5401,7 @@
       <c r="J317" s="3" t="n"/>
       <c r="K317" s="3" t="n"/>
       <c r="L317" s="3" t="n"/>
+      <c r="M317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -5089,6 +5416,7 @@
       <c r="J318" s="3" t="n"/>
       <c r="K318" s="3" t="n"/>
       <c r="L318" s="3" t="n"/>
+      <c r="M318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -5103,6 +5431,7 @@
       <c r="J319" s="3" t="n"/>
       <c r="K319" s="3" t="n"/>
       <c r="L319" s="3" t="n"/>
+      <c r="M319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -5117,6 +5446,7 @@
       <c r="J320" s="3" t="n"/>
       <c r="K320" s="3" t="n"/>
       <c r="L320" s="3" t="n"/>
+      <c r="M320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -5131,6 +5461,7 @@
       <c r="J321" s="3" t="n"/>
       <c r="K321" s="3" t="n"/>
       <c r="L321" s="3" t="n"/>
+      <c r="M321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -5145,6 +5476,7 @@
       <c r="J322" s="3" t="n"/>
       <c r="K322" s="3" t="n"/>
       <c r="L322" s="3" t="n"/>
+      <c r="M322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -5159,6 +5491,7 @@
       <c r="J323" s="3" t="n"/>
       <c r="K323" s="3" t="n"/>
       <c r="L323" s="3" t="n"/>
+      <c r="M323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -5173,6 +5506,7 @@
       <c r="J324" s="3" t="n"/>
       <c r="K324" s="3" t="n"/>
       <c r="L324" s="3" t="n"/>
+      <c r="M324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -5187,6 +5521,7 @@
       <c r="J325" s="3" t="n"/>
       <c r="K325" s="3" t="n"/>
       <c r="L325" s="3" t="n"/>
+      <c r="M325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -5201,6 +5536,7 @@
       <c r="J326" s="3" t="n"/>
       <c r="K326" s="3" t="n"/>
       <c r="L326" s="3" t="n"/>
+      <c r="M326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -5215,6 +5551,7 @@
       <c r="J327" s="3" t="n"/>
       <c r="K327" s="3" t="n"/>
       <c r="L327" s="3" t="n"/>
+      <c r="M327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -5229,6 +5566,7 @@
       <c r="J328" s="3" t="n"/>
       <c r="K328" s="3" t="n"/>
       <c r="L328" s="3" t="n"/>
+      <c r="M328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -5243,6 +5581,7 @@
       <c r="J329" s="3" t="n"/>
       <c r="K329" s="3" t="n"/>
       <c r="L329" s="3" t="n"/>
+      <c r="M329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -5257,6 +5596,7 @@
       <c r="J330" s="3" t="n"/>
       <c r="K330" s="3" t="n"/>
       <c r="L330" s="3" t="n"/>
+      <c r="M330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -5271,6 +5611,7 @@
       <c r="J331" s="3" t="n"/>
       <c r="K331" s="3" t="n"/>
       <c r="L331" s="3" t="n"/>
+      <c r="M331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -5285,6 +5626,7 @@
       <c r="J332" s="3" t="n"/>
       <c r="K332" s="3" t="n"/>
       <c r="L332" s="3" t="n"/>
+      <c r="M332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -5299,6 +5641,7 @@
       <c r="J333" s="3" t="n"/>
       <c r="K333" s="3" t="n"/>
       <c r="L333" s="3" t="n"/>
+      <c r="M333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -5313,6 +5656,7 @@
       <c r="J334" s="3" t="n"/>
       <c r="K334" s="3" t="n"/>
       <c r="L334" s="3" t="n"/>
+      <c r="M334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -5327,6 +5671,7 @@
       <c r="J335" s="3" t="n"/>
       <c r="K335" s="3" t="n"/>
       <c r="L335" s="3" t="n"/>
+      <c r="M335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -5341,6 +5686,7 @@
       <c r="J336" s="3" t="n"/>
       <c r="K336" s="3" t="n"/>
       <c r="L336" s="3" t="n"/>
+      <c r="M336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -5355,6 +5701,7 @@
       <c r="J337" s="3" t="n"/>
       <c r="K337" s="3" t="n"/>
       <c r="L337" s="3" t="n"/>
+      <c r="M337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -5369,6 +5716,7 @@
       <c r="J338" s="3" t="n"/>
       <c r="K338" s="3" t="n"/>
       <c r="L338" s="3" t="n"/>
+      <c r="M338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -5383,6 +5731,7 @@
       <c r="J339" s="3" t="n"/>
       <c r="K339" s="3" t="n"/>
       <c r="L339" s="3" t="n"/>
+      <c r="M339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -5397,6 +5746,7 @@
       <c r="J340" s="3" t="n"/>
       <c r="K340" s="3" t="n"/>
       <c r="L340" s="3" t="n"/>
+      <c r="M340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -5411,6 +5761,7 @@
       <c r="J341" s="3" t="n"/>
       <c r="K341" s="3" t="n"/>
       <c r="L341" s="3" t="n"/>
+      <c r="M341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -5425,6 +5776,7 @@
       <c r="J342" s="3" t="n"/>
       <c r="K342" s="3" t="n"/>
       <c r="L342" s="3" t="n"/>
+      <c r="M342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -5439,6 +5791,7 @@
       <c r="J343" s="3" t="n"/>
       <c r="K343" s="3" t="n"/>
       <c r="L343" s="3" t="n"/>
+      <c r="M343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -5453,6 +5806,7 @@
       <c r="J344" s="3" t="n"/>
       <c r="K344" s="3" t="n"/>
       <c r="L344" s="3" t="n"/>
+      <c r="M344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -5467,6 +5821,7 @@
       <c r="J345" s="3" t="n"/>
       <c r="K345" s="3" t="n"/>
       <c r="L345" s="3" t="n"/>
+      <c r="M345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -5481,6 +5836,7 @@
       <c r="J346" s="3" t="n"/>
       <c r="K346" s="3" t="n"/>
       <c r="L346" s="3" t="n"/>
+      <c r="M346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -5495,6 +5851,7 @@
       <c r="J347" s="3" t="n"/>
       <c r="K347" s="3" t="n"/>
       <c r="L347" s="3" t="n"/>
+      <c r="M347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -5509,6 +5866,7 @@
       <c r="J348" s="3" t="n"/>
       <c r="K348" s="3" t="n"/>
       <c r="L348" s="3" t="n"/>
+      <c r="M348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -5523,6 +5881,7 @@
       <c r="J349" s="3" t="n"/>
       <c r="K349" s="3" t="n"/>
       <c r="L349" s="3" t="n"/>
+      <c r="M349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -5537,6 +5896,7 @@
       <c r="J350" s="3" t="n"/>
       <c r="K350" s="3" t="n"/>
       <c r="L350" s="3" t="n"/>
+      <c r="M350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -5551,6 +5911,7 @@
       <c r="J351" s="3" t="n"/>
       <c r="K351" s="3" t="n"/>
       <c r="L351" s="3" t="n"/>
+      <c r="M351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -5565,6 +5926,7 @@
       <c r="J352" s="3" t="n"/>
       <c r="K352" s="3" t="n"/>
       <c r="L352" s="3" t="n"/>
+      <c r="M352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -5579,6 +5941,7 @@
       <c r="J353" s="3" t="n"/>
       <c r="K353" s="3" t="n"/>
       <c r="L353" s="3" t="n"/>
+      <c r="M353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -5593,6 +5956,7 @@
       <c r="J354" s="3" t="n"/>
       <c r="K354" s="3" t="n"/>
       <c r="L354" s="3" t="n"/>
+      <c r="M354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -5607,6 +5971,7 @@
       <c r="J355" s="3" t="n"/>
       <c r="K355" s="3" t="n"/>
       <c r="L355" s="3" t="n"/>
+      <c r="M355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -5621,6 +5986,7 @@
       <c r="J356" s="3" t="n"/>
       <c r="K356" s="3" t="n"/>
       <c r="L356" s="3" t="n"/>
+      <c r="M356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -5635,6 +6001,7 @@
       <c r="J357" s="3" t="n"/>
       <c r="K357" s="3" t="n"/>
       <c r="L357" s="3" t="n"/>
+      <c r="M357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -5649,6 +6016,7 @@
       <c r="J358" s="3" t="n"/>
       <c r="K358" s="3" t="n"/>
       <c r="L358" s="3" t="n"/>
+      <c r="M358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -5663,6 +6031,7 @@
       <c r="J359" s="3" t="n"/>
       <c r="K359" s="3" t="n"/>
       <c r="L359" s="3" t="n"/>
+      <c r="M359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -5677,6 +6046,7 @@
       <c r="J360" s="3" t="n"/>
       <c r="K360" s="3" t="n"/>
       <c r="L360" s="3" t="n"/>
+      <c r="M360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -5691,6 +6061,7 @@
       <c r="J361" s="3" t="n"/>
       <c r="K361" s="3" t="n"/>
       <c r="L361" s="3" t="n"/>
+      <c r="M361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -5705,6 +6076,7 @@
       <c r="J362" s="3" t="n"/>
       <c r="K362" s="3" t="n"/>
       <c r="L362" s="3" t="n"/>
+      <c r="M362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -5719,6 +6091,7 @@
       <c r="J363" s="3" t="n"/>
       <c r="K363" s="3" t="n"/>
       <c r="L363" s="3" t="n"/>
+      <c r="M363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -5733,6 +6106,7 @@
       <c r="J364" s="3" t="n"/>
       <c r="K364" s="3" t="n"/>
       <c r="L364" s="3" t="n"/>
+      <c r="M364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -5747,6 +6121,7 @@
       <c r="J365" s="3" t="n"/>
       <c r="K365" s="3" t="n"/>
       <c r="L365" s="3" t="n"/>
+      <c r="M365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -5761,6 +6136,7 @@
       <c r="J366" s="3" t="n"/>
       <c r="K366" s="3" t="n"/>
       <c r="L366" s="3" t="n"/>
+      <c r="M366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -5775,6 +6151,7 @@
       <c r="J367" s="3" t="n"/>
       <c r="K367" s="3" t="n"/>
       <c r="L367" s="3" t="n"/>
+      <c r="M367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -5789,6 +6166,7 @@
       <c r="J368" s="3" t="n"/>
       <c r="K368" s="3" t="n"/>
       <c r="L368" s="3" t="n"/>
+      <c r="M368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -5803,6 +6181,7 @@
       <c r="J369" s="3" t="n"/>
       <c r="K369" s="3" t="n"/>
       <c r="L369" s="3" t="n"/>
+      <c r="M369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -5817,6 +6196,7 @@
       <c r="J370" s="3" t="n"/>
       <c r="K370" s="3" t="n"/>
       <c r="L370" s="3" t="n"/>
+      <c r="M370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n"/>
@@ -5831,6 +6211,7 @@
       <c r="J371" s="3" t="n"/>
       <c r="K371" s="3" t="n"/>
       <c r="L371" s="3" t="n"/>
+      <c r="M371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -5845,6 +6226,7 @@
       <c r="J372" s="3" t="n"/>
       <c r="K372" s="3" t="n"/>
       <c r="L372" s="3" t="n"/>
+      <c r="M372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="n"/>
@@ -5859,6 +6241,7 @@
       <c r="J373" s="3" t="n"/>
       <c r="K373" s="3" t="n"/>
       <c r="L373" s="3" t="n"/>
+      <c r="M373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -5873,6 +6256,7 @@
       <c r="J374" s="3" t="n"/>
       <c r="K374" s="3" t="n"/>
       <c r="L374" s="3" t="n"/>
+      <c r="M374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n"/>
@@ -5887,6 +6271,7 @@
       <c r="J375" s="3" t="n"/>
       <c r="K375" s="3" t="n"/>
       <c r="L375" s="3" t="n"/>
+      <c r="M375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -5901,6 +6286,7 @@
       <c r="J376" s="3" t="n"/>
       <c r="K376" s="3" t="n"/>
       <c r="L376" s="3" t="n"/>
+      <c r="M376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n"/>
@@ -5915,6 +6301,7 @@
       <c r="J377" s="3" t="n"/>
       <c r="K377" s="3" t="n"/>
       <c r="L377" s="3" t="n"/>
+      <c r="M377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -5929,6 +6316,7 @@
       <c r="J378" s="3" t="n"/>
       <c r="K378" s="3" t="n"/>
       <c r="L378" s="3" t="n"/>
+      <c r="M378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n"/>
@@ -5943,6 +6331,7 @@
       <c r="J379" s="3" t="n"/>
       <c r="K379" s="3" t="n"/>
       <c r="L379" s="3" t="n"/>
+      <c r="M379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -5957,6 +6346,7 @@
       <c r="J380" s="3" t="n"/>
       <c r="K380" s="3" t="n"/>
       <c r="L380" s="3" t="n"/>
+      <c r="M380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n"/>
@@ -5971,6 +6361,7 @@
       <c r="J381" s="3" t="n"/>
       <c r="K381" s="3" t="n"/>
       <c r="L381" s="3" t="n"/>
+      <c r="M381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -5985,6 +6376,7 @@
       <c r="J382" s="3" t="n"/>
       <c r="K382" s="3" t="n"/>
       <c r="L382" s="3" t="n"/>
+      <c r="M382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n"/>
@@ -5999,6 +6391,7 @@
       <c r="J383" s="3" t="n"/>
       <c r="K383" s="3" t="n"/>
       <c r="L383" s="3" t="n"/>
+      <c r="M383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -6013,6 +6406,7 @@
       <c r="J384" s="3" t="n"/>
       <c r="K384" s="3" t="n"/>
       <c r="L384" s="3" t="n"/>
+      <c r="M384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n"/>
@@ -6027,6 +6421,7 @@
       <c r="J385" s="3" t="n"/>
       <c r="K385" s="3" t="n"/>
       <c r="L385" s="3" t="n"/>
+      <c r="M385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -6041,6 +6436,7 @@
       <c r="J386" s="3" t="n"/>
       <c r="K386" s="3" t="n"/>
       <c r="L386" s="3" t="n"/>
+      <c r="M386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="n"/>
@@ -6055,6 +6451,7 @@
       <c r="J387" s="3" t="n"/>
       <c r="K387" s="3" t="n"/>
       <c r="L387" s="3" t="n"/>
+      <c r="M387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -6069,6 +6466,7 @@
       <c r="J388" s="3" t="n"/>
       <c r="K388" s="3" t="n"/>
       <c r="L388" s="3" t="n"/>
+      <c r="M388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n"/>
@@ -6083,6 +6481,7 @@
       <c r="J389" s="3" t="n"/>
       <c r="K389" s="3" t="n"/>
       <c r="L389" s="3" t="n"/>
+      <c r="M389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -6097,6 +6496,7 @@
       <c r="J390" s="3" t="n"/>
       <c r="K390" s="3" t="n"/>
       <c r="L390" s="3" t="n"/>
+      <c r="M390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n"/>
@@ -6111,6 +6511,7 @@
       <c r="J391" s="3" t="n"/>
       <c r="K391" s="3" t="n"/>
       <c r="L391" s="3" t="n"/>
+      <c r="M391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -6125,6 +6526,7 @@
       <c r="J392" s="3" t="n"/>
       <c r="K392" s="3" t="n"/>
       <c r="L392" s="3" t="n"/>
+      <c r="M392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n"/>
@@ -6139,6 +6541,7 @@
       <c r="J393" s="3" t="n"/>
       <c r="K393" s="3" t="n"/>
       <c r="L393" s="3" t="n"/>
+      <c r="M393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -6153,6 +6556,7 @@
       <c r="J394" s="3" t="n"/>
       <c r="K394" s="3" t="n"/>
       <c r="L394" s="3" t="n"/>
+      <c r="M394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n"/>
@@ -6167,6 +6571,7 @@
       <c r="J395" s="3" t="n"/>
       <c r="K395" s="3" t="n"/>
       <c r="L395" s="3" t="n"/>
+      <c r="M395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -6181,6 +6586,7 @@
       <c r="J396" s="3" t="n"/>
       <c r="K396" s="3" t="n"/>
       <c r="L396" s="3" t="n"/>
+      <c r="M396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="n"/>
@@ -6195,6 +6601,7 @@
       <c r="J397" s="3" t="n"/>
       <c r="K397" s="3" t="n"/>
       <c r="L397" s="3" t="n"/>
+      <c r="M397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -6209,6 +6616,7 @@
       <c r="J398" s="3" t="n"/>
       <c r="K398" s="3" t="n"/>
       <c r="L398" s="3" t="n"/>
+      <c r="M398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n"/>
@@ -6223,6 +6631,7 @@
       <c r="J399" s="3" t="n"/>
       <c r="K399" s="3" t="n"/>
       <c r="L399" s="3" t="n"/>
+      <c r="M399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="n"/>
@@ -6237,6 +6646,7 @@
       <c r="J400" s="3" t="n"/>
       <c r="K400" s="3" t="n"/>
       <c r="L400" s="3" t="n"/>
+      <c r="M400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="n"/>
@@ -6251,6 +6661,7 @@
       <c r="J401" s="3" t="n"/>
       <c r="K401" s="3" t="n"/>
       <c r="L401" s="3" t="n"/>
+      <c r="M401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="n"/>
@@ -6265,6 +6676,7 @@
       <c r="J402" s="3" t="n"/>
       <c r="K402" s="3" t="n"/>
       <c r="L402" s="3" t="n"/>
+      <c r="M402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="n"/>
@@ -6279,6 +6691,7 @@
       <c r="J403" s="3" t="n"/>
       <c r="K403" s="3" t="n"/>
       <c r="L403" s="3" t="n"/>
+      <c r="M403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n"/>
@@ -6293,6 +6706,7 @@
       <c r="J404" s="3" t="n"/>
       <c r="K404" s="3" t="n"/>
       <c r="L404" s="3" t="n"/>
+      <c r="M404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="n"/>
@@ -6307,6 +6721,7 @@
       <c r="J405" s="3" t="n"/>
       <c r="K405" s="3" t="n"/>
       <c r="L405" s="3" t="n"/>
+      <c r="M405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n"/>
@@ -6321,6 +6736,7 @@
       <c r="J406" s="3" t="n"/>
       <c r="K406" s="3" t="n"/>
       <c r="L406" s="3" t="n"/>
+      <c r="M406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="n"/>
@@ -6335,6 +6751,7 @@
       <c r="J407" s="3" t="n"/>
       <c r="K407" s="3" t="n"/>
       <c r="L407" s="3" t="n"/>
+      <c r="M407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="n"/>
@@ -6349,6 +6766,7 @@
       <c r="J408" s="3" t="n"/>
       <c r="K408" s="3" t="n"/>
       <c r="L408" s="3" t="n"/>
+      <c r="M408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="n"/>
@@ -6363,6 +6781,7 @@
       <c r="J409" s="3" t="n"/>
       <c r="K409" s="3" t="n"/>
       <c r="L409" s="3" t="n"/>
+      <c r="M409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="n"/>
@@ -6377,6 +6796,7 @@
       <c r="J410" s="3" t="n"/>
       <c r="K410" s="3" t="n"/>
       <c r="L410" s="3" t="n"/>
+      <c r="M410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="n"/>
@@ -6391,6 +6811,7 @@
       <c r="J411" s="3" t="n"/>
       <c r="K411" s="3" t="n"/>
       <c r="L411" s="3" t="n"/>
+      <c r="M411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="n"/>
@@ -6405,6 +6826,7 @@
       <c r="J412" s="3" t="n"/>
       <c r="K412" s="3" t="n"/>
       <c r="L412" s="3" t="n"/>
+      <c r="M412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="n"/>
@@ -6419,6 +6841,7 @@
       <c r="J413" s="3" t="n"/>
       <c r="K413" s="3" t="n"/>
       <c r="L413" s="3" t="n"/>
+      <c r="M413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="n"/>
@@ -6433,6 +6856,7 @@
       <c r="J414" s="3" t="n"/>
       <c r="K414" s="3" t="n"/>
       <c r="L414" s="3" t="n"/>
+      <c r="M414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="n"/>
@@ -6447,6 +6871,7 @@
       <c r="J415" s="3" t="n"/>
       <c r="K415" s="3" t="n"/>
       <c r="L415" s="3" t="n"/>
+      <c r="M415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="n"/>
@@ -6461,6 +6886,7 @@
       <c r="J416" s="3" t="n"/>
       <c r="K416" s="3" t="n"/>
       <c r="L416" s="3" t="n"/>
+      <c r="M416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="n"/>
@@ -6475,6 +6901,7 @@
       <c r="J417" s="3" t="n"/>
       <c r="K417" s="3" t="n"/>
       <c r="L417" s="3" t="n"/>
+      <c r="M417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="n"/>
@@ -6489,6 +6916,7 @@
       <c r="J418" s="3" t="n"/>
       <c r="K418" s="3" t="n"/>
       <c r="L418" s="3" t="n"/>
+      <c r="M418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="n"/>
@@ -6503,6 +6931,7 @@
       <c r="J419" s="3" t="n"/>
       <c r="K419" s="3" t="n"/>
       <c r="L419" s="3" t="n"/>
+      <c r="M419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="n"/>
@@ -6517,6 +6946,7 @@
       <c r="J420" s="3" t="n"/>
       <c r="K420" s="3" t="n"/>
       <c r="L420" s="3" t="n"/>
+      <c r="M420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="n"/>
@@ -6531,6 +6961,7 @@
       <c r="J421" s="3" t="n"/>
       <c r="K421" s="3" t="n"/>
       <c r="L421" s="3" t="n"/>
+      <c r="M421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="n"/>
@@ -6545,6 +6976,7 @@
       <c r="J422" s="3" t="n"/>
       <c r="K422" s="3" t="n"/>
       <c r="L422" s="3" t="n"/>
+      <c r="M422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="n"/>
@@ -6559,6 +6991,7 @@
       <c r="J423" s="3" t="n"/>
       <c r="K423" s="3" t="n"/>
       <c r="L423" s="3" t="n"/>
+      <c r="M423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="n"/>
@@ -6573,6 +7006,7 @@
       <c r="J424" s="3" t="n"/>
       <c r="K424" s="3" t="n"/>
       <c r="L424" s="3" t="n"/>
+      <c r="M424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="n"/>
@@ -6587,6 +7021,7 @@
       <c r="J425" s="3" t="n"/>
       <c r="K425" s="3" t="n"/>
       <c r="L425" s="3" t="n"/>
+      <c r="M425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="n"/>
@@ -6601,6 +7036,7 @@
       <c r="J426" s="3" t="n"/>
       <c r="K426" s="3" t="n"/>
       <c r="L426" s="3" t="n"/>
+      <c r="M426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="n"/>
@@ -6615,6 +7051,7 @@
       <c r="J427" s="3" t="n"/>
       <c r="K427" s="3" t="n"/>
       <c r="L427" s="3" t="n"/>
+      <c r="M427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="n"/>
@@ -6629,6 +7066,7 @@
       <c r="J428" s="3" t="n"/>
       <c r="K428" s="3" t="n"/>
       <c r="L428" s="3" t="n"/>
+      <c r="M428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="n"/>
@@ -6643,6 +7081,7 @@
       <c r="J429" s="3" t="n"/>
       <c r="K429" s="3" t="n"/>
       <c r="L429" s="3" t="n"/>
+      <c r="M429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="n"/>
@@ -6657,6 +7096,7 @@
       <c r="J430" s="3" t="n"/>
       <c r="K430" s="3" t="n"/>
       <c r="L430" s="3" t="n"/>
+      <c r="M430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="n"/>
@@ -6671,6 +7111,7 @@
       <c r="J431" s="3" t="n"/>
       <c r="K431" s="3" t="n"/>
       <c r="L431" s="3" t="n"/>
+      <c r="M431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="n"/>
@@ -6685,6 +7126,7 @@
       <c r="J432" s="3" t="n"/>
       <c r="K432" s="3" t="n"/>
       <c r="L432" s="3" t="n"/>
+      <c r="M432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="n"/>
@@ -6699,6 +7141,7 @@
       <c r="J433" s="3" t="n"/>
       <c r="K433" s="3" t="n"/>
       <c r="L433" s="3" t="n"/>
+      <c r="M433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="n"/>
@@ -6713,6 +7156,7 @@
       <c r="J434" s="3" t="n"/>
       <c r="K434" s="3" t="n"/>
       <c r="L434" s="3" t="n"/>
+      <c r="M434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="n"/>
@@ -6727,6 +7171,7 @@
       <c r="J435" s="3" t="n"/>
       <c r="K435" s="3" t="n"/>
       <c r="L435" s="3" t="n"/>
+      <c r="M435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="n"/>
@@ -6741,6 +7186,7 @@
       <c r="J436" s="3" t="n"/>
       <c r="K436" s="3" t="n"/>
       <c r="L436" s="3" t="n"/>
+      <c r="M436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="n"/>
@@ -6755,6 +7201,7 @@
       <c r="J437" s="3" t="n"/>
       <c r="K437" s="3" t="n"/>
       <c r="L437" s="3" t="n"/>
+      <c r="M437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="n"/>
@@ -6769,6 +7216,7 @@
       <c r="J438" s="3" t="n"/>
       <c r="K438" s="3" t="n"/>
       <c r="L438" s="3" t="n"/>
+      <c r="M438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="n"/>
@@ -6783,6 +7231,7 @@
       <c r="J439" s="3" t="n"/>
       <c r="K439" s="3" t="n"/>
       <c r="L439" s="3" t="n"/>
+      <c r="M439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="n"/>
@@ -6797,6 +7246,7 @@
       <c r="J440" s="3" t="n"/>
       <c r="K440" s="3" t="n"/>
       <c r="L440" s="3" t="n"/>
+      <c r="M440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="n"/>
@@ -6811,6 +7261,7 @@
       <c r="J441" s="3" t="n"/>
       <c r="K441" s="3" t="n"/>
       <c r="L441" s="3" t="n"/>
+      <c r="M441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="n"/>
@@ -6825,6 +7276,7 @@
       <c r="J442" s="3" t="n"/>
       <c r="K442" s="3" t="n"/>
       <c r="L442" s="3" t="n"/>
+      <c r="M442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="n"/>
@@ -6839,6 +7291,7 @@
       <c r="J443" s="3" t="n"/>
       <c r="K443" s="3" t="n"/>
       <c r="L443" s="3" t="n"/>
+      <c r="M443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n"/>
@@ -6853,6 +7306,7 @@
       <c r="J444" s="3" t="n"/>
       <c r="K444" s="3" t="n"/>
       <c r="L444" s="3" t="n"/>
+      <c r="M444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="n"/>
@@ -6867,6 +7321,7 @@
       <c r="J445" s="3" t="n"/>
       <c r="K445" s="3" t="n"/>
       <c r="L445" s="3" t="n"/>
+      <c r="M445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="n"/>
@@ -6881,6 +7336,7 @@
       <c r="J446" s="3" t="n"/>
       <c r="K446" s="3" t="n"/>
       <c r="L446" s="3" t="n"/>
+      <c r="M446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="n"/>
@@ -6895,6 +7351,7 @@
       <c r="J447" s="3" t="n"/>
       <c r="K447" s="3" t="n"/>
       <c r="L447" s="3" t="n"/>
+      <c r="M447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="n"/>
@@ -6909,6 +7366,7 @@
       <c r="J448" s="3" t="n"/>
       <c r="K448" s="3" t="n"/>
       <c r="L448" s="3" t="n"/>
+      <c r="M448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="n"/>
@@ -6923,6 +7381,7 @@
       <c r="J449" s="3" t="n"/>
       <c r="K449" s="3" t="n"/>
       <c r="L449" s="3" t="n"/>
+      <c r="M449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="n"/>
@@ -6937,6 +7396,7 @@
       <c r="J450" s="3" t="n"/>
       <c r="K450" s="3" t="n"/>
       <c r="L450" s="3" t="n"/>
+      <c r="M450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="n"/>
@@ -6951,6 +7411,7 @@
       <c r="J451" s="3" t="n"/>
       <c r="K451" s="3" t="n"/>
       <c r="L451" s="3" t="n"/>
+      <c r="M451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="n"/>
@@ -6965,6 +7426,7 @@
       <c r="J452" s="3" t="n"/>
       <c r="K452" s="3" t="n"/>
       <c r="L452" s="3" t="n"/>
+      <c r="M452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="n"/>
@@ -6979,6 +7441,7 @@
       <c r="J453" s="3" t="n"/>
       <c r="K453" s="3" t="n"/>
       <c r="L453" s="3" t="n"/>
+      <c r="M453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="n"/>
@@ -6993,6 +7456,7 @@
       <c r="J454" s="3" t="n"/>
       <c r="K454" s="3" t="n"/>
       <c r="L454" s="3" t="n"/>
+      <c r="M454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="n"/>
@@ -7007,6 +7471,7 @@
       <c r="J455" s="3" t="n"/>
       <c r="K455" s="3" t="n"/>
       <c r="L455" s="3" t="n"/>
+      <c r="M455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="n"/>
@@ -7021,6 +7486,7 @@
       <c r="J456" s="3" t="n"/>
       <c r="K456" s="3" t="n"/>
       <c r="L456" s="3" t="n"/>
+      <c r="M456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="n"/>
@@ -7035,6 +7501,7 @@
       <c r="J457" s="3" t="n"/>
       <c r="K457" s="3" t="n"/>
       <c r="L457" s="3" t="n"/>
+      <c r="M457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="n"/>
@@ -7049,6 +7516,7 @@
       <c r="J458" s="3" t="n"/>
       <c r="K458" s="3" t="n"/>
       <c r="L458" s="3" t="n"/>
+      <c r="M458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="n"/>
@@ -7063,6 +7531,7 @@
       <c r="J459" s="3" t="n"/>
       <c r="K459" s="3" t="n"/>
       <c r="L459" s="3" t="n"/>
+      <c r="M459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="n"/>
@@ -7077,6 +7546,7 @@
       <c r="J460" s="3" t="n"/>
       <c r="K460" s="3" t="n"/>
       <c r="L460" s="3" t="n"/>
+      <c r="M460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="n"/>
@@ -7091,6 +7561,7 @@
       <c r="J461" s="3" t="n"/>
       <c r="K461" s="3" t="n"/>
       <c r="L461" s="3" t="n"/>
+      <c r="M461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="n"/>
@@ -7105,6 +7576,7 @@
       <c r="J462" s="3" t="n"/>
       <c r="K462" s="3" t="n"/>
       <c r="L462" s="3" t="n"/>
+      <c r="M462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="n"/>
@@ -7119,6 +7591,7 @@
       <c r="J463" s="3" t="n"/>
       <c r="K463" s="3" t="n"/>
       <c r="L463" s="3" t="n"/>
+      <c r="M463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="n"/>
@@ -7133,6 +7606,7 @@
       <c r="J464" s="3" t="n"/>
       <c r="K464" s="3" t="n"/>
       <c r="L464" s="3" t="n"/>
+      <c r="M464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="n"/>
@@ -7147,6 +7621,7 @@
       <c r="J465" s="3" t="n"/>
       <c r="K465" s="3" t="n"/>
       <c r="L465" s="3" t="n"/>
+      <c r="M465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="n"/>
@@ -7161,6 +7636,7 @@
       <c r="J466" s="3" t="n"/>
       <c r="K466" s="3" t="n"/>
       <c r="L466" s="3" t="n"/>
+      <c r="M466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="n"/>
@@ -7175,6 +7651,7 @@
       <c r="J467" s="3" t="n"/>
       <c r="K467" s="3" t="n"/>
       <c r="L467" s="3" t="n"/>
+      <c r="M467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="n"/>
@@ -7189,6 +7666,7 @@
       <c r="J468" s="3" t="n"/>
       <c r="K468" s="3" t="n"/>
       <c r="L468" s="3" t="n"/>
+      <c r="M468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="n"/>
@@ -7203,6 +7681,7 @@
       <c r="J469" s="3" t="n"/>
       <c r="K469" s="3" t="n"/>
       <c r="L469" s="3" t="n"/>
+      <c r="M469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="n"/>
@@ -7217,6 +7696,7 @@
       <c r="J470" s="3" t="n"/>
       <c r="K470" s="3" t="n"/>
       <c r="L470" s="3" t="n"/>
+      <c r="M470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="n"/>
@@ -7231,6 +7711,7 @@
       <c r="J471" s="3" t="n"/>
       <c r="K471" s="3" t="n"/>
       <c r="L471" s="3" t="n"/>
+      <c r="M471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="n"/>
@@ -7245,6 +7726,7 @@
       <c r="J472" s="3" t="n"/>
       <c r="K472" s="3" t="n"/>
       <c r="L472" s="3" t="n"/>
+      <c r="M472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="n"/>
@@ -7259,6 +7741,7 @@
       <c r="J473" s="3" t="n"/>
       <c r="K473" s="3" t="n"/>
       <c r="L473" s="3" t="n"/>
+      <c r="M473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n"/>
@@ -7273,6 +7756,7 @@
       <c r="J474" s="3" t="n"/>
       <c r="K474" s="3" t="n"/>
       <c r="L474" s="3" t="n"/>
+      <c r="M474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="n"/>
@@ -7287,6 +7771,7 @@
       <c r="J475" s="3" t="n"/>
       <c r="K475" s="3" t="n"/>
       <c r="L475" s="3" t="n"/>
+      <c r="M475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="n"/>
@@ -7301,6 +7786,7 @@
       <c r="J476" s="3" t="n"/>
       <c r="K476" s="3" t="n"/>
       <c r="L476" s="3" t="n"/>
+      <c r="M476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="n"/>
@@ -7315,6 +7801,7 @@
       <c r="J477" s="3" t="n"/>
       <c r="K477" s="3" t="n"/>
       <c r="L477" s="3" t="n"/>
+      <c r="M477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="n"/>
@@ -7329,6 +7816,7 @@
       <c r="J478" s="3" t="n"/>
       <c r="K478" s="3" t="n"/>
       <c r="L478" s="3" t="n"/>
+      <c r="M478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="n"/>
@@ -7343,6 +7831,7 @@
       <c r="J479" s="3" t="n"/>
       <c r="K479" s="3" t="n"/>
       <c r="L479" s="3" t="n"/>
+      <c r="M479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n"/>
@@ -7357,6 +7846,7 @@
       <c r="J480" s="3" t="n"/>
       <c r="K480" s="3" t="n"/>
       <c r="L480" s="3" t="n"/>
+      <c r="M480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="n"/>
@@ -7371,6 +7861,7 @@
       <c r="J481" s="3" t="n"/>
       <c r="K481" s="3" t="n"/>
       <c r="L481" s="3" t="n"/>
+      <c r="M481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="n"/>
@@ -7385,6 +7876,7 @@
       <c r="J482" s="3" t="n"/>
       <c r="K482" s="3" t="n"/>
       <c r="L482" s="3" t="n"/>
+      <c r="M482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="n"/>
@@ -7399,6 +7891,7 @@
       <c r="J483" s="3" t="n"/>
       <c r="K483" s="3" t="n"/>
       <c r="L483" s="3" t="n"/>
+      <c r="M483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="n"/>
@@ -7413,6 +7906,7 @@
       <c r="J484" s="3" t="n"/>
       <c r="K484" s="3" t="n"/>
       <c r="L484" s="3" t="n"/>
+      <c r="M484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="n"/>
@@ -7427,6 +7921,7 @@
       <c r="J485" s="3" t="n"/>
       <c r="K485" s="3" t="n"/>
       <c r="L485" s="3" t="n"/>
+      <c r="M485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="n"/>
@@ -7441,6 +7936,7 @@
       <c r="J486" s="3" t="n"/>
       <c r="K486" s="3" t="n"/>
       <c r="L486" s="3" t="n"/>
+      <c r="M486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="n"/>
@@ -7455,6 +7951,7 @@
       <c r="J487" s="3" t="n"/>
       <c r="K487" s="3" t="n"/>
       <c r="L487" s="3" t="n"/>
+      <c r="M487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="n"/>
@@ -7469,6 +7966,7 @@
       <c r="J488" s="3" t="n"/>
       <c r="K488" s="3" t="n"/>
       <c r="L488" s="3" t="n"/>
+      <c r="M488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="n"/>
@@ -7483,6 +7981,7 @@
       <c r="J489" s="3" t="n"/>
       <c r="K489" s="3" t="n"/>
       <c r="L489" s="3" t="n"/>
+      <c r="M489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="n"/>
@@ -7497,6 +7996,7 @@
       <c r="J490" s="3" t="n"/>
       <c r="K490" s="3" t="n"/>
       <c r="L490" s="3" t="n"/>
+      <c r="M490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="n"/>
@@ -7511,6 +8011,7 @@
       <c r="J491" s="3" t="n"/>
       <c r="K491" s="3" t="n"/>
       <c r="L491" s="3" t="n"/>
+      <c r="M491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="n"/>
@@ -7525,6 +8026,7 @@
       <c r="J492" s="3" t="n"/>
       <c r="K492" s="3" t="n"/>
       <c r="L492" s="3" t="n"/>
+      <c r="M492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="n"/>
@@ -7539,6 +8041,7 @@
       <c r="J493" s="3" t="n"/>
       <c r="K493" s="3" t="n"/>
       <c r="L493" s="3" t="n"/>
+      <c r="M493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="n"/>
@@ -7553,6 +8056,7 @@
       <c r="J494" s="3" t="n"/>
       <c r="K494" s="3" t="n"/>
       <c r="L494" s="3" t="n"/>
+      <c r="M494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="n"/>
@@ -7567,6 +8071,7 @@
       <c r="J495" s="3" t="n"/>
       <c r="K495" s="3" t="n"/>
       <c r="L495" s="3" t="n"/>
+      <c r="M495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="n"/>
@@ -7581,6 +8086,7 @@
       <c r="J496" s="3" t="n"/>
       <c r="K496" s="3" t="n"/>
       <c r="L496" s="3" t="n"/>
+      <c r="M496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="n"/>
@@ -7595,6 +8101,7 @@
       <c r="J497" s="3" t="n"/>
       <c r="K497" s="3" t="n"/>
       <c r="L497" s="3" t="n"/>
+      <c r="M497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="n"/>
@@ -7609,6 +8116,7 @@
       <c r="J498" s="3" t="n"/>
       <c r="K498" s="3" t="n"/>
       <c r="L498" s="3" t="n"/>
+      <c r="M498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="n"/>
@@ -7623,6 +8131,7 @@
       <c r="J499" s="3" t="n"/>
       <c r="K499" s="3" t="n"/>
       <c r="L499" s="3" t="n"/>
+      <c r="M499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="n"/>
@@ -7637,6 +8146,7 @@
       <c r="J500" s="3" t="n"/>
       <c r="K500" s="3" t="n"/>
       <c r="L500" s="3" t="n"/>
+      <c r="M500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="n"/>
@@ -7651,6 +8161,7 @@
       <c r="J501" s="3" t="n"/>
       <c r="K501" s="3" t="n"/>
       <c r="L501" s="3" t="n"/>
+      <c r="M501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="n"/>
@@ -7665,6 +8176,7 @@
       <c r="J502" s="3" t="n"/>
       <c r="K502" s="3" t="n"/>
       <c r="L502" s="3" t="n"/>
+      <c r="M502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="n"/>
@@ -7679,6 +8191,7 @@
       <c r="J503" s="3" t="n"/>
       <c r="K503" s="3" t="n"/>
       <c r="L503" s="3" t="n"/>
+      <c r="M503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="n"/>
@@ -7693,6 +8206,7 @@
       <c r="J504" s="3" t="n"/>
       <c r="K504" s="3" t="n"/>
       <c r="L504" s="3" t="n"/>
+      <c r="M504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="n"/>
@@ -7707,6 +8221,7 @@
       <c r="J505" s="3" t="n"/>
       <c r="K505" s="3" t="n"/>
       <c r="L505" s="3" t="n"/>
+      <c r="M505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="n"/>
@@ -7721,6 +8236,7 @@
       <c r="J506" s="3" t="n"/>
       <c r="K506" s="3" t="n"/>
       <c r="L506" s="3" t="n"/>
+      <c r="M506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="n"/>
@@ -7735,6 +8251,7 @@
       <c r="J507" s="3" t="n"/>
       <c r="K507" s="3" t="n"/>
       <c r="L507" s="3" t="n"/>
+      <c r="M507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="n"/>
@@ -7749,6 +8266,7 @@
       <c r="J508" s="3" t="n"/>
       <c r="K508" s="3" t="n"/>
       <c r="L508" s="3" t="n"/>
+      <c r="M508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="n"/>
@@ -7763,6 +8281,7 @@
       <c r="J509" s="3" t="n"/>
       <c r="K509" s="3" t="n"/>
       <c r="L509" s="3" t="n"/>
+      <c r="M509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="n"/>
@@ -7777,6 +8296,7 @@
       <c r="J510" s="3" t="n"/>
       <c r="K510" s="3" t="n"/>
       <c r="L510" s="3" t="n"/>
+      <c r="M510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="n"/>
@@ -7791,6 +8311,7 @@
       <c r="J511" s="3" t="n"/>
       <c r="K511" s="3" t="n"/>
       <c r="L511" s="3" t="n"/>
+      <c r="M511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="n"/>
@@ -7805,6 +8326,7 @@
       <c r="J512" s="3" t="n"/>
       <c r="K512" s="3" t="n"/>
       <c r="L512" s="3" t="n"/>
+      <c r="M512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="n"/>
@@ -7819,6 +8341,7 @@
       <c r="J513" s="3" t="n"/>
       <c r="K513" s="3" t="n"/>
       <c r="L513" s="3" t="n"/>
+      <c r="M513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="n"/>
@@ -7833,6 +8356,7 @@
       <c r="J514" s="3" t="n"/>
       <c r="K514" s="3" t="n"/>
       <c r="L514" s="3" t="n"/>
+      <c r="M514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="n"/>
@@ -7847,6 +8371,7 @@
       <c r="J515" s="3" t="n"/>
       <c r="K515" s="3" t="n"/>
       <c r="L515" s="3" t="n"/>
+      <c r="M515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="n"/>
@@ -7861,6 +8386,7 @@
       <c r="J516" s="3" t="n"/>
       <c r="K516" s="3" t="n"/>
       <c r="L516" s="3" t="n"/>
+      <c r="M516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="n"/>
@@ -7875,6 +8401,7 @@
       <c r="J517" s="3" t="n"/>
       <c r="K517" s="3" t="n"/>
       <c r="L517" s="3" t="n"/>
+      <c r="M517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="n"/>
@@ -7889,6 +8416,7 @@
       <c r="J518" s="3" t="n"/>
       <c r="K518" s="3" t="n"/>
       <c r="L518" s="3" t="n"/>
+      <c r="M518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="n"/>
@@ -7903,6 +8431,7 @@
       <c r="J519" s="3" t="n"/>
       <c r="K519" s="3" t="n"/>
       <c r="L519" s="3" t="n"/>
+      <c r="M519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="n"/>
@@ -7917,6 +8446,7 @@
       <c r="J520" s="3" t="n"/>
       <c r="K520" s="3" t="n"/>
       <c r="L520" s="3" t="n"/>
+      <c r="M520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="n"/>
@@ -7931,6 +8461,7 @@
       <c r="J521" s="3" t="n"/>
       <c r="K521" s="3" t="n"/>
       <c r="L521" s="3" t="n"/>
+      <c r="M521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="n"/>
@@ -7945,6 +8476,7 @@
       <c r="J522" s="3" t="n"/>
       <c r="K522" s="3" t="n"/>
       <c r="L522" s="3" t="n"/>
+      <c r="M522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="n"/>
@@ -7959,6 +8491,7 @@
       <c r="J523" s="3" t="n"/>
       <c r="K523" s="3" t="n"/>
       <c r="L523" s="3" t="n"/>
+      <c r="M523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="n"/>
@@ -7973,6 +8506,7 @@
       <c r="J524" s="3" t="n"/>
       <c r="K524" s="3" t="n"/>
       <c r="L524" s="3" t="n"/>
+      <c r="M524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="n"/>
@@ -7987,6 +8521,7 @@
       <c r="J525" s="3" t="n"/>
       <c r="K525" s="3" t="n"/>
       <c r="L525" s="3" t="n"/>
+      <c r="M525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="n"/>
@@ -8001,6 +8536,7 @@
       <c r="J526" s="3" t="n"/>
       <c r="K526" s="3" t="n"/>
       <c r="L526" s="3" t="n"/>
+      <c r="M526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="n"/>
@@ -8015,6 +8551,7 @@
       <c r="J527" s="3" t="n"/>
       <c r="K527" s="3" t="n"/>
       <c r="L527" s="3" t="n"/>
+      <c r="M527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="n"/>
@@ -8029,6 +8566,7 @@
       <c r="J528" s="3" t="n"/>
       <c r="K528" s="3" t="n"/>
       <c r="L528" s="3" t="n"/>
+      <c r="M528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="n"/>
@@ -8043,6 +8581,7 @@
       <c r="J529" s="3" t="n"/>
       <c r="K529" s="3" t="n"/>
       <c r="L529" s="3" t="n"/>
+      <c r="M529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="n"/>
@@ -8057,6 +8596,7 @@
       <c r="J530" s="3" t="n"/>
       <c r="K530" s="3" t="n"/>
       <c r="L530" s="3" t="n"/>
+      <c r="M530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="n"/>
@@ -8071,6 +8611,7 @@
       <c r="J531" s="3" t="n"/>
       <c r="K531" s="3" t="n"/>
       <c r="L531" s="3" t="n"/>
+      <c r="M531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="n"/>
@@ -8085,6 +8626,7 @@
       <c r="J532" s="3" t="n"/>
       <c r="K532" s="3" t="n"/>
       <c r="L532" s="3" t="n"/>
+      <c r="M532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="n"/>
@@ -8099,6 +8641,7 @@
       <c r="J533" s="3" t="n"/>
       <c r="K533" s="3" t="n"/>
       <c r="L533" s="3" t="n"/>
+      <c r="M533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="n"/>
@@ -8113,6 +8656,7 @@
       <c r="J534" s="3" t="n"/>
       <c r="K534" s="3" t="n"/>
       <c r="L534" s="3" t="n"/>
+      <c r="M534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="n"/>
@@ -8127,6 +8671,7 @@
       <c r="J535" s="3" t="n"/>
       <c r="K535" s="3" t="n"/>
       <c r="L535" s="3" t="n"/>
+      <c r="M535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="n"/>
@@ -8141,6 +8686,7 @@
       <c r="J536" s="3" t="n"/>
       <c r="K536" s="3" t="n"/>
       <c r="L536" s="3" t="n"/>
+      <c r="M536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="3" t="n"/>
@@ -8155,6 +8701,7 @@
       <c r="J537" s="3" t="n"/>
       <c r="K537" s="3" t="n"/>
       <c r="L537" s="3" t="n"/>
+      <c r="M537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="n"/>
@@ -8169,6 +8716,7 @@
       <c r="J538" s="3" t="n"/>
       <c r="K538" s="3" t="n"/>
       <c r="L538" s="3" t="n"/>
+      <c r="M538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="3" t="n"/>
@@ -8183,6 +8731,7 @@
       <c r="J539" s="3" t="n"/>
       <c r="K539" s="3" t="n"/>
       <c r="L539" s="3" t="n"/>
+      <c r="M539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="n"/>
@@ -8197,6 +8746,7 @@
       <c r="J540" s="3" t="n"/>
       <c r="K540" s="3" t="n"/>
       <c r="L540" s="3" t="n"/>
+      <c r="M540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="3" t="n"/>
@@ -8211,6 +8761,7 @@
       <c r="J541" s="3" t="n"/>
       <c r="K541" s="3" t="n"/>
       <c r="L541" s="3" t="n"/>
+      <c r="M541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="n"/>
@@ -8225,6 +8776,7 @@
       <c r="J542" s="3" t="n"/>
       <c r="K542" s="3" t="n"/>
       <c r="L542" s="3" t="n"/>
+      <c r="M542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="3" t="n"/>
@@ -8239,6 +8791,7 @@
       <c r="J543" s="3" t="n"/>
       <c r="K543" s="3" t="n"/>
       <c r="L543" s="3" t="n"/>
+      <c r="M543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="n"/>
@@ -8253,6 +8806,7 @@
       <c r="J544" s="3" t="n"/>
       <c r="K544" s="3" t="n"/>
       <c r="L544" s="3" t="n"/>
+      <c r="M544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="3" t="n"/>
@@ -8267,6 +8821,7 @@
       <c r="J545" s="3" t="n"/>
       <c r="K545" s="3" t="n"/>
       <c r="L545" s="3" t="n"/>
+      <c r="M545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="n"/>
@@ -8281,6 +8836,7 @@
       <c r="J546" s="3" t="n"/>
       <c r="K546" s="3" t="n"/>
       <c r="L546" s="3" t="n"/>
+      <c r="M546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="3" t="n"/>
@@ -8295,6 +8851,7 @@
       <c r="J547" s="3" t="n"/>
       <c r="K547" s="3" t="n"/>
       <c r="L547" s="3" t="n"/>
+      <c r="M547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="n"/>
@@ -8309,6 +8866,7 @@
       <c r="J548" s="3" t="n"/>
       <c r="K548" s="3" t="n"/>
       <c r="L548" s="3" t="n"/>
+      <c r="M548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="n"/>
@@ -8323,6 +8881,7 @@
       <c r="J549" s="3" t="n"/>
       <c r="K549" s="3" t="n"/>
       <c r="L549" s="3" t="n"/>
+      <c r="M549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="n"/>
@@ -8337,6 +8896,7 @@
       <c r="J550" s="3" t="n"/>
       <c r="K550" s="3" t="n"/>
       <c r="L550" s="3" t="n"/>
+      <c r="M550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="3" t="n"/>
@@ -8351,6 +8911,7 @@
       <c r="J551" s="3" t="n"/>
       <c r="K551" s="3" t="n"/>
       <c r="L551" s="3" t="n"/>
+      <c r="M551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="n"/>
@@ -8365,6 +8926,7 @@
       <c r="J552" s="3" t="n"/>
       <c r="K552" s="3" t="n"/>
       <c r="L552" s="3" t="n"/>
+      <c r="M552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="3" t="n"/>
@@ -8379,6 +8941,7 @@
       <c r="J553" s="3" t="n"/>
       <c r="K553" s="3" t="n"/>
       <c r="L553" s="3" t="n"/>
+      <c r="M553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="n"/>
@@ -8393,6 +8956,7 @@
       <c r="J554" s="3" t="n"/>
       <c r="K554" s="3" t="n"/>
       <c r="L554" s="3" t="n"/>
+      <c r="M554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="3" t="n"/>
@@ -8407,6 +8971,7 @@
       <c r="J555" s="3" t="n"/>
       <c r="K555" s="3" t="n"/>
       <c r="L555" s="3" t="n"/>
+      <c r="M555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="n"/>
@@ -8421,6 +8986,7 @@
       <c r="J556" s="3" t="n"/>
       <c r="K556" s="3" t="n"/>
       <c r="L556" s="3" t="n"/>
+      <c r="M556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="3" t="n"/>
@@ -8435,6 +9001,7 @@
       <c r="J557" s="3" t="n"/>
       <c r="K557" s="3" t="n"/>
       <c r="L557" s="3" t="n"/>
+      <c r="M557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="n"/>
@@ -8449,6 +9016,7 @@
       <c r="J558" s="3" t="n"/>
       <c r="K558" s="3" t="n"/>
       <c r="L558" s="3" t="n"/>
+      <c r="M558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="3" t="n"/>
@@ -8463,6 +9031,7 @@
       <c r="J559" s="3" t="n"/>
       <c r="K559" s="3" t="n"/>
       <c r="L559" s="3" t="n"/>
+      <c r="M559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="n"/>
@@ -8477,6 +9046,7 @@
       <c r="J560" s="3" t="n"/>
       <c r="K560" s="3" t="n"/>
       <c r="L560" s="3" t="n"/>
+      <c r="M560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="3" t="n"/>
@@ -8491,6 +9061,7 @@
       <c r="J561" s="3" t="n"/>
       <c r="K561" s="3" t="n"/>
       <c r="L561" s="3" t="n"/>
+      <c r="M561" s="3" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="n"/>
@@ -8505,6 +9076,7 @@
       <c r="J562" s="3" t="n"/>
       <c r="K562" s="3" t="n"/>
       <c r="L562" s="3" t="n"/>
+      <c r="M562" s="3" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="3" t="n"/>
@@ -8519,6 +9091,7 @@
       <c r="J563" s="3" t="n"/>
       <c r="K563" s="3" t="n"/>
       <c r="L563" s="3" t="n"/>
+      <c r="M563" s="3" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="n"/>
@@ -8533,6 +9106,7 @@
       <c r="J564" s="3" t="n"/>
       <c r="K564" s="3" t="n"/>
       <c r="L564" s="3" t="n"/>
+      <c r="M564" s="3" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="3" t="n"/>
@@ -8547,6 +9121,7 @@
       <c r="J565" s="3" t="n"/>
       <c r="K565" s="3" t="n"/>
       <c r="L565" s="3" t="n"/>
+      <c r="M565" s="3" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="n"/>
@@ -8561,6 +9136,7 @@
       <c r="J566" s="3" t="n"/>
       <c r="K566" s="3" t="n"/>
       <c r="L566" s="3" t="n"/>
+      <c r="M566" s="3" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="3" t="n"/>
@@ -8575,6 +9151,7 @@
       <c r="J567" s="3" t="n"/>
       <c r="K567" s="3" t="n"/>
       <c r="L567" s="3" t="n"/>
+      <c r="M567" s="3" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="n"/>
@@ -8589,6 +9166,7 @@
       <c r="J568" s="3" t="n"/>
       <c r="K568" s="3" t="n"/>
       <c r="L568" s="3" t="n"/>
+      <c r="M568" s="3" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="3" t="n"/>
@@ -8603,6 +9181,7 @@
       <c r="J569" s="3" t="n"/>
       <c r="K569" s="3" t="n"/>
       <c r="L569" s="3" t="n"/>
+      <c r="M569" s="3" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="n"/>
@@ -8617,6 +9196,7 @@
       <c r="J570" s="3" t="n"/>
       <c r="K570" s="3" t="n"/>
       <c r="L570" s="3" t="n"/>
+      <c r="M570" s="3" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="3" t="n"/>
@@ -8631,6 +9211,7 @@
       <c r="J571" s="3" t="n"/>
       <c r="K571" s="3" t="n"/>
       <c r="L571" s="3" t="n"/>
+      <c r="M571" s="3" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="n"/>
@@ -8645,6 +9226,7 @@
       <c r="J572" s="3" t="n"/>
       <c r="K572" s="3" t="n"/>
       <c r="L572" s="3" t="n"/>
+      <c r="M572" s="3" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="3" t="n"/>
@@ -8659,6 +9241,7 @@
       <c r="J573" s="3" t="n"/>
       <c r="K573" s="3" t="n"/>
       <c r="L573" s="3" t="n"/>
+      <c r="M573" s="3" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="n"/>
@@ -8673,6 +9256,7 @@
       <c r="J574" s="3" t="n"/>
       <c r="K574" s="3" t="n"/>
       <c r="L574" s="3" t="n"/>
+      <c r="M574" s="3" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="3" t="n"/>
@@ -8687,6 +9271,7 @@
       <c r="J575" s="3" t="n"/>
       <c r="K575" s="3" t="n"/>
       <c r="L575" s="3" t="n"/>
+      <c r="M575" s="3" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="n"/>
@@ -8701,6 +9286,7 @@
       <c r="J576" s="3" t="n"/>
       <c r="K576" s="3" t="n"/>
       <c r="L576" s="3" t="n"/>
+      <c r="M576" s="3" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="3" t="n"/>
@@ -8715,6 +9301,7 @@
       <c r="J577" s="3" t="n"/>
       <c r="K577" s="3" t="n"/>
       <c r="L577" s="3" t="n"/>
+      <c r="M577" s="3" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="n"/>
@@ -8729,6 +9316,7 @@
       <c r="J578" s="3" t="n"/>
       <c r="K578" s="3" t="n"/>
       <c r="L578" s="3" t="n"/>
+      <c r="M578" s="3" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="3" t="n"/>
@@ -8743,6 +9331,7 @@
       <c r="J579" s="3" t="n"/>
       <c r="K579" s="3" t="n"/>
       <c r="L579" s="3" t="n"/>
+      <c r="M579" s="3" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="3" t="n"/>
@@ -8757,6 +9346,7 @@
       <c r="J580" s="3" t="n"/>
       <c r="K580" s="3" t="n"/>
       <c r="L580" s="3" t="n"/>
+      <c r="M580" s="3" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="3" t="n"/>
@@ -8771,6 +9361,7 @@
       <c r="J581" s="3" t="n"/>
       <c r="K581" s="3" t="n"/>
       <c r="L581" s="3" t="n"/>
+      <c r="M581" s="3" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="n"/>
@@ -8785,6 +9376,7 @@
       <c r="J582" s="3" t="n"/>
       <c r="K582" s="3" t="n"/>
       <c r="L582" s="3" t="n"/>
+      <c r="M582" s="3" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="3" t="n"/>
@@ -8799,6 +9391,7 @@
       <c r="J583" s="3" t="n"/>
       <c r="K583" s="3" t="n"/>
       <c r="L583" s="3" t="n"/>
+      <c r="M583" s="3" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="3" t="n"/>
@@ -8813,6 +9406,7 @@
       <c r="J584" s="3" t="n"/>
       <c r="K584" s="3" t="n"/>
       <c r="L584" s="3" t="n"/>
+      <c r="M584" s="3" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="3" t="n"/>
@@ -8827,6 +9421,7 @@
       <c r="J585" s="3" t="n"/>
       <c r="K585" s="3" t="n"/>
       <c r="L585" s="3" t="n"/>
+      <c r="M585" s="3" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="3" t="n"/>
@@ -8841,6 +9436,7 @@
       <c r="J586" s="3" t="n"/>
       <c r="K586" s="3" t="n"/>
       <c r="L586" s="3" t="n"/>
+      <c r="M586" s="3" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="3" t="n"/>
@@ -8855,6 +9451,7 @@
       <c r="J587" s="3" t="n"/>
       <c r="K587" s="3" t="n"/>
       <c r="L587" s="3" t="n"/>
+      <c r="M587" s="3" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="3" t="n"/>
@@ -8869,6 +9466,7 @@
       <c r="J588" s="3" t="n"/>
       <c r="K588" s="3" t="n"/>
       <c r="L588" s="3" t="n"/>
+      <c r="M588" s="3" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="3" t="n"/>
@@ -8883,6 +9481,7 @@
       <c r="J589" s="3" t="n"/>
       <c r="K589" s="3" t="n"/>
       <c r="L589" s="3" t="n"/>
+      <c r="M589" s="3" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="3" t="n"/>
@@ -8897,6 +9496,7 @@
       <c r="J590" s="3" t="n"/>
       <c r="K590" s="3" t="n"/>
       <c r="L590" s="3" t="n"/>
+      <c r="M590" s="3" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="3" t="n"/>
@@ -8911,6 +9511,7 @@
       <c r="J591" s="3" t="n"/>
       <c r="K591" s="3" t="n"/>
       <c r="L591" s="3" t="n"/>
+      <c r="M591" s="3" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="3" t="n"/>
@@ -8925,6 +9526,7 @@
       <c r="J592" s="3" t="n"/>
       <c r="K592" s="3" t="n"/>
       <c r="L592" s="3" t="n"/>
+      <c r="M592" s="3" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="3" t="n"/>
@@ -8939,6 +9541,7 @@
       <c r="J593" s="3" t="n"/>
       <c r="K593" s="3" t="n"/>
       <c r="L593" s="3" t="n"/>
+      <c r="M593" s="3" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="3" t="n"/>
@@ -8953,6 +9556,7 @@
       <c r="J594" s="3" t="n"/>
       <c r="K594" s="3" t="n"/>
       <c r="L594" s="3" t="n"/>
+      <c r="M594" s="3" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="3" t="n"/>
@@ -8967,6 +9571,7 @@
       <c r="J595" s="3" t="n"/>
       <c r="K595" s="3" t="n"/>
       <c r="L595" s="3" t="n"/>
+      <c r="M595" s="3" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="3" t="n"/>
@@ -8981,6 +9586,7 @@
       <c r="J596" s="3" t="n"/>
       <c r="K596" s="3" t="n"/>
       <c r="L596" s="3" t="n"/>
+      <c r="M596" s="3" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="3" t="n"/>
@@ -8995,6 +9601,7 @@
       <c r="J597" s="3" t="n"/>
       <c r="K597" s="3" t="n"/>
       <c r="L597" s="3" t="n"/>
+      <c r="M597" s="3" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="3" t="n"/>
@@ -9009,6 +9616,7 @@
       <c r="J598" s="3" t="n"/>
       <c r="K598" s="3" t="n"/>
       <c r="L598" s="3" t="n"/>
+      <c r="M598" s="3" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="3" t="n"/>
@@ -9023,6 +9631,7 @@
       <c r="J599" s="3" t="n"/>
       <c r="K599" s="3" t="n"/>
       <c r="L599" s="3" t="n"/>
+      <c r="M599" s="3" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="3" t="n"/>
@@ -9037,6 +9646,7 @@
       <c r="J600" s="3" t="n"/>
       <c r="K600" s="3" t="n"/>
       <c r="L600" s="3" t="n"/>
+      <c r="M600" s="3" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="3" t="n"/>
@@ -9051,6 +9661,7 @@
       <c r="J601" s="3" t="n"/>
       <c r="K601" s="3" t="n"/>
       <c r="L601" s="3" t="n"/>
+      <c r="M601" s="3" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="3" t="n"/>
@@ -9065,6 +9676,7 @@
       <c r="J602" s="3" t="n"/>
       <c r="K602" s="3" t="n"/>
       <c r="L602" s="3" t="n"/>
+      <c r="M602" s="3" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="3" t="n"/>
@@ -9079,6 +9691,7 @@
       <c r="J603" s="3" t="n"/>
       <c r="K603" s="3" t="n"/>
       <c r="L603" s="3" t="n"/>
+      <c r="M603" s="3" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="n"/>
@@ -9093,6 +9706,7 @@
       <c r="J604" s="3" t="n"/>
       <c r="K604" s="3" t="n"/>
       <c r="L604" s="3" t="n"/>
+      <c r="M604" s="3" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="3" t="n"/>
@@ -9107,6 +9721,7 @@
       <c r="J605" s="3" t="n"/>
       <c r="K605" s="3" t="n"/>
       <c r="L605" s="3" t="n"/>
+      <c r="M605" s="3" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="3" t="n"/>
@@ -9121,6 +9736,7 @@
       <c r="J606" s="3" t="n"/>
       <c r="K606" s="3" t="n"/>
       <c r="L606" s="3" t="n"/>
+      <c r="M606" s="3" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="3" t="n"/>
@@ -9135,6 +9751,7 @@
       <c r="J607" s="3" t="n"/>
       <c r="K607" s="3" t="n"/>
       <c r="L607" s="3" t="n"/>
+      <c r="M607" s="3" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="3" t="n"/>
@@ -9149,6 +9766,7 @@
       <c r="J608" s="3" t="n"/>
       <c r="K608" s="3" t="n"/>
       <c r="L608" s="3" t="n"/>
+      <c r="M608" s="3" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="3" t="n"/>
@@ -9163,6 +9781,7 @@
       <c r="J609" s="3" t="n"/>
       <c r="K609" s="3" t="n"/>
       <c r="L609" s="3" t="n"/>
+      <c r="M609" s="3" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="3" t="n"/>
@@ -9177,6 +9796,7 @@
       <c r="J610" s="3" t="n"/>
       <c r="K610" s="3" t="n"/>
       <c r="L610" s="3" t="n"/>
+      <c r="M610" s="3" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="3" t="n"/>
@@ -9191,6 +9811,7 @@
       <c r="J611" s="3" t="n"/>
       <c r="K611" s="3" t="n"/>
       <c r="L611" s="3" t="n"/>
+      <c r="M611" s="3" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="3" t="n"/>
@@ -9205,6 +9826,7 @@
       <c r="J612" s="3" t="n"/>
       <c r="K612" s="3" t="n"/>
       <c r="L612" s="3" t="n"/>
+      <c r="M612" s="3" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="3" t="n"/>
@@ -9219,6 +9841,7 @@
       <c r="J613" s="3" t="n"/>
       <c r="K613" s="3" t="n"/>
       <c r="L613" s="3" t="n"/>
+      <c r="M613" s="3" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="3" t="n"/>
@@ -9233,6 +9856,7 @@
       <c r="J614" s="3" t="n"/>
       <c r="K614" s="3" t="n"/>
       <c r="L614" s="3" t="n"/>
+      <c r="M614" s="3" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="3" t="n"/>
@@ -9247,6 +9871,7 @@
       <c r="J615" s="3" t="n"/>
       <c r="K615" s="3" t="n"/>
       <c r="L615" s="3" t="n"/>
+      <c r="M615" s="3" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="3" t="n"/>
@@ -9261,6 +9886,7 @@
       <c r="J616" s="3" t="n"/>
       <c r="K616" s="3" t="n"/>
       <c r="L616" s="3" t="n"/>
+      <c r="M616" s="3" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="3" t="n"/>
@@ -9275,6 +9901,7 @@
       <c r="J617" s="3" t="n"/>
       <c r="K617" s="3" t="n"/>
       <c r="L617" s="3" t="n"/>
+      <c r="M617" s="3" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="3" t="n"/>
@@ -9289,6 +9916,7 @@
       <c r="J618" s="3" t="n"/>
       <c r="K618" s="3" t="n"/>
       <c r="L618" s="3" t="n"/>
+      <c r="M618" s="3" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="3" t="n"/>
@@ -9303,6 +9931,7 @@
       <c r="J619" s="3" t="n"/>
       <c r="K619" s="3" t="n"/>
       <c r="L619" s="3" t="n"/>
+      <c r="M619" s="3" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="3" t="n"/>
@@ -9317,6 +9946,7 @@
       <c r="J620" s="3" t="n"/>
       <c r="K620" s="3" t="n"/>
       <c r="L620" s="3" t="n"/>
+      <c r="M620" s="3" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="3" t="n"/>
@@ -9331,6 +9961,7 @@
       <c r="J621" s="3" t="n"/>
       <c r="K621" s="3" t="n"/>
       <c r="L621" s="3" t="n"/>
+      <c r="M621" s="3" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="3" t="n"/>
@@ -9345,6 +9976,7 @@
       <c r="J622" s="3" t="n"/>
       <c r="K622" s="3" t="n"/>
       <c r="L622" s="3" t="n"/>
+      <c r="M622" s="3" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="3" t="n"/>
@@ -9359,6 +9991,7 @@
       <c r="J623" s="3" t="n"/>
       <c r="K623" s="3" t="n"/>
       <c r="L623" s="3" t="n"/>
+      <c r="M623" s="3" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="3" t="n"/>
@@ -9373,6 +10006,7 @@
       <c r="J624" s="3" t="n"/>
       <c r="K624" s="3" t="n"/>
       <c r="L624" s="3" t="n"/>
+      <c r="M624" s="3" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="3" t="n"/>
@@ -9387,6 +10021,7 @@
       <c r="J625" s="3" t="n"/>
       <c r="K625" s="3" t="n"/>
       <c r="L625" s="3" t="n"/>
+      <c r="M625" s="3" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="3" t="n"/>
@@ -9401,6 +10036,7 @@
       <c r="J626" s="3" t="n"/>
       <c r="K626" s="3" t="n"/>
       <c r="L626" s="3" t="n"/>
+      <c r="M626" s="3" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="3" t="n"/>
@@ -9415,6 +10051,7 @@
       <c r="J627" s="3" t="n"/>
       <c r="K627" s="3" t="n"/>
       <c r="L627" s="3" t="n"/>
+      <c r="M627" s="3" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="3" t="n"/>
@@ -9429,6 +10066,7 @@
       <c r="J628" s="3" t="n"/>
       <c r="K628" s="3" t="n"/>
       <c r="L628" s="3" t="n"/>
+      <c r="M628" s="3" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="3" t="n"/>
@@ -9443,6 +10081,7 @@
       <c r="J629" s="3" t="n"/>
       <c r="K629" s="3" t="n"/>
       <c r="L629" s="3" t="n"/>
+      <c r="M629" s="3" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="3" t="n"/>
@@ -9457,6 +10096,7 @@
       <c r="J630" s="3" t="n"/>
       <c r="K630" s="3" t="n"/>
       <c r="L630" s="3" t="n"/>
+      <c r="M630" s="3" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="3" t="n"/>
@@ -9471,6 +10111,7 @@
       <c r="J631" s="3" t="n"/>
       <c r="K631" s="3" t="n"/>
       <c r="L631" s="3" t="n"/>
+      <c r="M631" s="3" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="3" t="n"/>
@@ -9485,6 +10126,7 @@
       <c r="J632" s="3" t="n"/>
       <c r="K632" s="3" t="n"/>
       <c r="L632" s="3" t="n"/>
+      <c r="M632" s="3" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="3" t="n"/>
@@ -9499,6 +10141,7 @@
       <c r="J633" s="3" t="n"/>
       <c r="K633" s="3" t="n"/>
       <c r="L633" s="3" t="n"/>
+      <c r="M633" s="3" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="3" t="n"/>
@@ -9513,6 +10156,7 @@
       <c r="J634" s="3" t="n"/>
       <c r="K634" s="3" t="n"/>
       <c r="L634" s="3" t="n"/>
+      <c r="M634" s="3" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="3" t="n"/>
@@ -9527,6 +10171,7 @@
       <c r="J635" s="3" t="n"/>
       <c r="K635" s="3" t="n"/>
       <c r="L635" s="3" t="n"/>
+      <c r="M635" s="3" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="3" t="n"/>
@@ -9541,6 +10186,7 @@
       <c r="J636" s="3" t="n"/>
       <c r="K636" s="3" t="n"/>
       <c r="L636" s="3" t="n"/>
+      <c r="M636" s="3" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="3" t="n"/>
@@ -9555,6 +10201,7 @@
       <c r="J637" s="3" t="n"/>
       <c r="K637" s="3" t="n"/>
       <c r="L637" s="3" t="n"/>
+      <c r="M637" s="3" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="3" t="n"/>
@@ -9569,6 +10216,7 @@
       <c r="J638" s="3" t="n"/>
       <c r="K638" s="3" t="n"/>
       <c r="L638" s="3" t="n"/>
+      <c r="M638" s="3" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="3" t="n"/>
@@ -9583,6 +10231,7 @@
       <c r="J639" s="3" t="n"/>
       <c r="K639" s="3" t="n"/>
       <c r="L639" s="3" t="n"/>
+      <c r="M639" s="3" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="3" t="n"/>
@@ -9597,6 +10246,7 @@
       <c r="J640" s="3" t="n"/>
       <c r="K640" s="3" t="n"/>
       <c r="L640" s="3" t="n"/>
+      <c r="M640" s="3" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="3" t="n"/>
@@ -9611,6 +10261,7 @@
       <c r="J641" s="3" t="n"/>
       <c r="K641" s="3" t="n"/>
       <c r="L641" s="3" t="n"/>
+      <c r="M641" s="3" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="3" t="n"/>
@@ -9625,6 +10276,7 @@
       <c r="J642" s="3" t="n"/>
       <c r="K642" s="3" t="n"/>
       <c r="L642" s="3" t="n"/>
+      <c r="M642" s="3" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="3" t="n"/>
@@ -9639,6 +10291,7 @@
       <c r="J643" s="3" t="n"/>
       <c r="K643" s="3" t="n"/>
       <c r="L643" s="3" t="n"/>
+      <c r="M643" s="3" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="3" t="n"/>
@@ -9653,6 +10306,7 @@
       <c r="J644" s="3" t="n"/>
       <c r="K644" s="3" t="n"/>
       <c r="L644" s="3" t="n"/>
+      <c r="M644" s="3" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="3" t="n"/>
@@ -9667,6 +10321,7 @@
       <c r="J645" s="3" t="n"/>
       <c r="K645" s="3" t="n"/>
       <c r="L645" s="3" t="n"/>
+      <c r="M645" s="3" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="3" t="n"/>
@@ -9681,6 +10336,7 @@
       <c r="J646" s="3" t="n"/>
       <c r="K646" s="3" t="n"/>
       <c r="L646" s="3" t="n"/>
+      <c r="M646" s="3" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="3" t="n"/>
@@ -9695,6 +10351,7 @@
       <c r="J647" s="3" t="n"/>
       <c r="K647" s="3" t="n"/>
       <c r="L647" s="3" t="n"/>
+      <c r="M647" s="3" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="3" t="n"/>
@@ -9709,6 +10366,7 @@
       <c r="J648" s="3" t="n"/>
       <c r="K648" s="3" t="n"/>
       <c r="L648" s="3" t="n"/>
+      <c r="M648" s="3" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="3" t="n"/>
@@ -9723,6 +10381,7 @@
       <c r="J649" s="3" t="n"/>
       <c r="K649" s="3" t="n"/>
       <c r="L649" s="3" t="n"/>
+      <c r="M649" s="3" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="3" t="n"/>
@@ -9737,6 +10396,7 @@
       <c r="J650" s="3" t="n"/>
       <c r="K650" s="3" t="n"/>
       <c r="L650" s="3" t="n"/>
+      <c r="M650" s="3" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="3" t="n"/>
@@ -9751,6 +10411,7 @@
       <c r="J651" s="3" t="n"/>
       <c r="K651" s="3" t="n"/>
       <c r="L651" s="3" t="n"/>
+      <c r="M651" s="3" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="3" t="n"/>
@@ -9765,6 +10426,7 @@
       <c r="J652" s="3" t="n"/>
       <c r="K652" s="3" t="n"/>
       <c r="L652" s="3" t="n"/>
+      <c r="M652" s="3" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="3" t="n"/>
@@ -9779,6 +10441,7 @@
       <c r="J653" s="3" t="n"/>
       <c r="K653" s="3" t="n"/>
       <c r="L653" s="3" t="n"/>
+      <c r="M653" s="3" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="3" t="n"/>
@@ -9793,6 +10456,7 @@
       <c r="J654" s="3" t="n"/>
       <c r="K654" s="3" t="n"/>
       <c r="L654" s="3" t="n"/>
+      <c r="M654" s="3" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="3" t="n"/>
@@ -9807,6 +10471,7 @@
       <c r="J655" s="3" t="n"/>
       <c r="K655" s="3" t="n"/>
       <c r="L655" s="3" t="n"/>
+      <c r="M655" s="3" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="3" t="n"/>
@@ -9821,6 +10486,7 @@
       <c r="J656" s="3" t="n"/>
       <c r="K656" s="3" t="n"/>
       <c r="L656" s="3" t="n"/>
+      <c r="M656" s="3" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="3" t="n"/>
@@ -9835,6 +10501,7 @@
       <c r="J657" s="3" t="n"/>
       <c r="K657" s="3" t="n"/>
       <c r="L657" s="3" t="n"/>
+      <c r="M657" s="3" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="3" t="n"/>
@@ -9849,6 +10516,7 @@
       <c r="J658" s="3" t="n"/>
       <c r="K658" s="3" t="n"/>
       <c r="L658" s="3" t="n"/>
+      <c r="M658" s="3" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="3" t="n"/>
@@ -9863,6 +10531,7 @@
       <c r="J659" s="3" t="n"/>
       <c r="K659" s="3" t="n"/>
       <c r="L659" s="3" t="n"/>
+      <c r="M659" s="3" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="3" t="n"/>
@@ -9877,6 +10546,7 @@
       <c r="J660" s="3" t="n"/>
       <c r="K660" s="3" t="n"/>
       <c r="L660" s="3" t="n"/>
+      <c r="M660" s="3" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="3" t="n"/>
@@ -9891,6 +10561,7 @@
       <c r="J661" s="3" t="n"/>
       <c r="K661" s="3" t="n"/>
       <c r="L661" s="3" t="n"/>
+      <c r="M661" s="3" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="3" t="n"/>
@@ -9905,6 +10576,7 @@
       <c r="J662" s="3" t="n"/>
       <c r="K662" s="3" t="n"/>
       <c r="L662" s="3" t="n"/>
+      <c r="M662" s="3" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="3" t="n"/>
@@ -9919,6 +10591,7 @@
       <c r="J663" s="3" t="n"/>
       <c r="K663" s="3" t="n"/>
       <c r="L663" s="3" t="n"/>
+      <c r="M663" s="3" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="3" t="n"/>
@@ -9933,6 +10606,7 @@
       <c r="J664" s="3" t="n"/>
       <c r="K664" s="3" t="n"/>
       <c r="L664" s="3" t="n"/>
+      <c r="M664" s="3" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="3" t="n"/>
@@ -9947,6 +10621,7 @@
       <c r="J665" s="3" t="n"/>
       <c r="K665" s="3" t="n"/>
       <c r="L665" s="3" t="n"/>
+      <c r="M665" s="3" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="3" t="n"/>
@@ -9961,6 +10636,7 @@
       <c r="J666" s="3" t="n"/>
       <c r="K666" s="3" t="n"/>
       <c r="L666" s="3" t="n"/>
+      <c r="M666" s="3" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="3" t="n"/>
@@ -9975,6 +10651,7 @@
       <c r="J667" s="3" t="n"/>
       <c r="K667" s="3" t="n"/>
       <c r="L667" s="3" t="n"/>
+      <c r="M667" s="3" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="3" t="n"/>
@@ -9989,6 +10666,7 @@
       <c r="J668" s="3" t="n"/>
       <c r="K668" s="3" t="n"/>
       <c r="L668" s="3" t="n"/>
+      <c r="M668" s="3" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="3" t="n"/>
@@ -10003,6 +10681,7 @@
       <c r="J669" s="3" t="n"/>
       <c r="K669" s="3" t="n"/>
       <c r="L669" s="3" t="n"/>
+      <c r="M669" s="3" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="3" t="n"/>
@@ -10017,6 +10696,7 @@
       <c r="J670" s="3" t="n"/>
       <c r="K670" s="3" t="n"/>
       <c r="L670" s="3" t="n"/>
+      <c r="M670" s="3" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="3" t="n"/>
@@ -10031,6 +10711,7 @@
       <c r="J671" s="3" t="n"/>
       <c r="K671" s="3" t="n"/>
       <c r="L671" s="3" t="n"/>
+      <c r="M671" s="3" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="3" t="n"/>
@@ -10045,6 +10726,7 @@
       <c r="J672" s="3" t="n"/>
       <c r="K672" s="3" t="n"/>
       <c r="L672" s="3" t="n"/>
+      <c r="M672" s="3" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="3" t="n"/>
@@ -10059,6 +10741,7 @@
       <c r="J673" s="3" t="n"/>
       <c r="K673" s="3" t="n"/>
       <c r="L673" s="3" t="n"/>
+      <c r="M673" s="3" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="3" t="n"/>
@@ -10073,6 +10756,7 @@
       <c r="J674" s="3" t="n"/>
       <c r="K674" s="3" t="n"/>
       <c r="L674" s="3" t="n"/>
+      <c r="M674" s="3" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="3" t="n"/>
@@ -10087,6 +10771,7 @@
       <c r="J675" s="3" t="n"/>
       <c r="K675" s="3" t="n"/>
       <c r="L675" s="3" t="n"/>
+      <c r="M675" s="3" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="3" t="n"/>
@@ -10101,6 +10786,7 @@
       <c r="J676" s="3" t="n"/>
       <c r="K676" s="3" t="n"/>
       <c r="L676" s="3" t="n"/>
+      <c r="M676" s="3" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="3" t="n"/>
@@ -10115,6 +10801,7 @@
       <c r="J677" s="3" t="n"/>
       <c r="K677" s="3" t="n"/>
       <c r="L677" s="3" t="n"/>
+      <c r="M677" s="3" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="3" t="n"/>
@@ -10129,6 +10816,7 @@
       <c r="J678" s="3" t="n"/>
       <c r="K678" s="3" t="n"/>
       <c r="L678" s="3" t="n"/>
+      <c r="M678" s="3" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="3" t="n"/>
@@ -10143,6 +10831,7 @@
       <c r="J679" s="3" t="n"/>
       <c r="K679" s="3" t="n"/>
       <c r="L679" s="3" t="n"/>
+      <c r="M679" s="3" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="3" t="n"/>
@@ -10157,6 +10846,7 @@
       <c r="J680" s="3" t="n"/>
       <c r="K680" s="3" t="n"/>
       <c r="L680" s="3" t="n"/>
+      <c r="M680" s="3" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="3" t="n"/>
@@ -10171,6 +10861,7 @@
       <c r="J681" s="3" t="n"/>
       <c r="K681" s="3" t="n"/>
       <c r="L681" s="3" t="n"/>
+      <c r="M681" s="3" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="3" t="n"/>
@@ -10185,6 +10876,7 @@
       <c r="J682" s="3" t="n"/>
       <c r="K682" s="3" t="n"/>
       <c r="L682" s="3" t="n"/>
+      <c r="M682" s="3" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="3" t="n"/>
@@ -10199,6 +10891,7 @@
       <c r="J683" s="3" t="n"/>
       <c r="K683" s="3" t="n"/>
       <c r="L683" s="3" t="n"/>
+      <c r="M683" s="3" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="3" t="n"/>
@@ -10213,6 +10906,7 @@
       <c r="J684" s="3" t="n"/>
       <c r="K684" s="3" t="n"/>
       <c r="L684" s="3" t="n"/>
+      <c r="M684" s="3" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="3" t="n"/>
@@ -10227,6 +10921,7 @@
       <c r="J685" s="3" t="n"/>
       <c r="K685" s="3" t="n"/>
       <c r="L685" s="3" t="n"/>
+      <c r="M685" s="3" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="3" t="n"/>
@@ -10241,6 +10936,7 @@
       <c r="J686" s="3" t="n"/>
       <c r="K686" s="3" t="n"/>
       <c r="L686" s="3" t="n"/>
+      <c r="M686" s="3" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="3" t="n"/>
@@ -10255,6 +10951,7 @@
       <c r="J687" s="3" t="n"/>
       <c r="K687" s="3" t="n"/>
       <c r="L687" s="3" t="n"/>
+      <c r="M687" s="3" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="3" t="n"/>
@@ -10269,6 +10966,7 @@
       <c r="J688" s="3" t="n"/>
       <c r="K688" s="3" t="n"/>
       <c r="L688" s="3" t="n"/>
+      <c r="M688" s="3" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="3" t="n"/>
@@ -10283,6 +10981,7 @@
       <c r="J689" s="3" t="n"/>
       <c r="K689" s="3" t="n"/>
       <c r="L689" s="3" t="n"/>
+      <c r="M689" s="3" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="3" t="n"/>
@@ -10297,6 +10996,7 @@
       <c r="J690" s="3" t="n"/>
       <c r="K690" s="3" t="n"/>
       <c r="L690" s="3" t="n"/>
+      <c r="M690" s="3" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="3" t="n"/>
@@ -10311,6 +11011,7 @@
       <c r="J691" s="3" t="n"/>
       <c r="K691" s="3" t="n"/>
       <c r="L691" s="3" t="n"/>
+      <c r="M691" s="3" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="3" t="n"/>
@@ -10325,6 +11026,7 @@
       <c r="J692" s="3" t="n"/>
       <c r="K692" s="3" t="n"/>
       <c r="L692" s="3" t="n"/>
+      <c r="M692" s="3" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="3" t="n"/>
@@ -10339,6 +11041,7 @@
       <c r="J693" s="3" t="n"/>
       <c r="K693" s="3" t="n"/>
       <c r="L693" s="3" t="n"/>
+      <c r="M693" s="3" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="3" t="n"/>
@@ -10353,6 +11056,7 @@
       <c r="J694" s="3" t="n"/>
       <c r="K694" s="3" t="n"/>
       <c r="L694" s="3" t="n"/>
+      <c r="M694" s="3" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="3" t="n"/>
@@ -10367,6 +11071,7 @@
       <c r="J695" s="3" t="n"/>
       <c r="K695" s="3" t="n"/>
       <c r="L695" s="3" t="n"/>
+      <c r="M695" s="3" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="3" t="n"/>
@@ -10381,6 +11086,7 @@
       <c r="J696" s="3" t="n"/>
       <c r="K696" s="3" t="n"/>
       <c r="L696" s="3" t="n"/>
+      <c r="M696" s="3" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="3" t="n"/>
@@ -10395,6 +11101,7 @@
       <c r="J697" s="3" t="n"/>
       <c r="K697" s="3" t="n"/>
       <c r="L697" s="3" t="n"/>
+      <c r="M697" s="3" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="3" t="n"/>
@@ -10409,6 +11116,7 @@
       <c r="J698" s="3" t="n"/>
       <c r="K698" s="3" t="n"/>
       <c r="L698" s="3" t="n"/>
+      <c r="M698" s="3" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="3" t="n"/>
@@ -10423,6 +11131,7 @@
       <c r="J699" s="3" t="n"/>
       <c r="K699" s="3" t="n"/>
       <c r="L699" s="3" t="n"/>
+      <c r="M699" s="3" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="3" t="n"/>
@@ -10437,6 +11146,7 @@
       <c r="J700" s="3" t="n"/>
       <c r="K700" s="3" t="n"/>
       <c r="L700" s="3" t="n"/>
+      <c r="M700" s="3" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="3" t="n"/>
@@ -10451,6 +11161,7 @@
       <c r="J701" s="3" t="n"/>
       <c r="K701" s="3" t="n"/>
       <c r="L701" s="3" t="n"/>
+      <c r="M701" s="3" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="3" t="n"/>
@@ -10465,6 +11176,7 @@
       <c r="J702" s="3" t="n"/>
       <c r="K702" s="3" t="n"/>
       <c r="L702" s="3" t="n"/>
+      <c r="M702" s="3" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="3" t="n"/>
@@ -10479,6 +11191,7 @@
       <c r="J703" s="3" t="n"/>
       <c r="K703" s="3" t="n"/>
       <c r="L703" s="3" t="n"/>
+      <c r="M703" s="3" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="3" t="n"/>
@@ -10493,6 +11206,7 @@
       <c r="J704" s="3" t="n"/>
       <c r="K704" s="3" t="n"/>
       <c r="L704" s="3" t="n"/>
+      <c r="M704" s="3" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="3" t="n"/>
@@ -10507,6 +11221,7 @@
       <c r="J705" s="3" t="n"/>
       <c r="K705" s="3" t="n"/>
       <c r="L705" s="3" t="n"/>
+      <c r="M705" s="3" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="3" t="n"/>
@@ -10521,6 +11236,7 @@
       <c r="J706" s="3" t="n"/>
       <c r="K706" s="3" t="n"/>
       <c r="L706" s="3" t="n"/>
+      <c r="M706" s="3" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="3" t="n"/>
@@ -10535,6 +11251,7 @@
       <c r="J707" s="3" t="n"/>
       <c r="K707" s="3" t="n"/>
       <c r="L707" s="3" t="n"/>
+      <c r="M707" s="3" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="3" t="n"/>
@@ -10549,6 +11266,7 @@
       <c r="J708" s="3" t="n"/>
       <c r="K708" s="3" t="n"/>
       <c r="L708" s="3" t="n"/>
+      <c r="M708" s="3" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="3" t="n"/>
@@ -10563,6 +11281,7 @@
       <c r="J709" s="3" t="n"/>
       <c r="K709" s="3" t="n"/>
       <c r="L709" s="3" t="n"/>
+      <c r="M709" s="3" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="3" t="n"/>
@@ -10577,6 +11296,7 @@
       <c r="J710" s="3" t="n"/>
       <c r="K710" s="3" t="n"/>
       <c r="L710" s="3" t="n"/>
+      <c r="M710" s="3" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="3" t="n"/>
@@ -10591,6 +11311,7 @@
       <c r="J711" s="3" t="n"/>
       <c r="K711" s="3" t="n"/>
       <c r="L711" s="3" t="n"/>
+      <c r="M711" s="3" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="3" t="n"/>
@@ -10605,6 +11326,7 @@
       <c r="J712" s="3" t="n"/>
       <c r="K712" s="3" t="n"/>
       <c r="L712" s="3" t="n"/>
+      <c r="M712" s="3" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="3" t="n"/>
@@ -10619,6 +11341,7 @@
       <c r="J713" s="3" t="n"/>
       <c r="K713" s="3" t="n"/>
       <c r="L713" s="3" t="n"/>
+      <c r="M713" s="3" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="3" t="n"/>
@@ -10633,6 +11356,7 @@
       <c r="J714" s="3" t="n"/>
       <c r="K714" s="3" t="n"/>
       <c r="L714" s="3" t="n"/>
+      <c r="M714" s="3" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="3" t="n"/>
@@ -10647,6 +11371,7 @@
       <c r="J715" s="3" t="n"/>
       <c r="K715" s="3" t="n"/>
       <c r="L715" s="3" t="n"/>
+      <c r="M715" s="3" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="3" t="n"/>
@@ -10661,6 +11386,7 @@
       <c r="J716" s="3" t="n"/>
       <c r="K716" s="3" t="n"/>
       <c r="L716" s="3" t="n"/>
+      <c r="M716" s="3" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="3" t="n"/>
@@ -10675,6 +11401,7 @@
       <c r="J717" s="3" t="n"/>
       <c r="K717" s="3" t="n"/>
       <c r="L717" s="3" t="n"/>
+      <c r="M717" s="3" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="3" t="n"/>
@@ -10689,6 +11416,7 @@
       <c r="J718" s="3" t="n"/>
       <c r="K718" s="3" t="n"/>
       <c r="L718" s="3" t="n"/>
+      <c r="M718" s="3" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="3" t="n"/>
@@ -10703,6 +11431,7 @@
       <c r="J719" s="3" t="n"/>
       <c r="K719" s="3" t="n"/>
       <c r="L719" s="3" t="n"/>
+      <c r="M719" s="3" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="3" t="n"/>
@@ -10717,6 +11446,7 @@
       <c r="J720" s="3" t="n"/>
       <c r="K720" s="3" t="n"/>
       <c r="L720" s="3" t="n"/>
+      <c r="M720" s="3" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="3" t="n"/>
@@ -10731,6 +11461,7 @@
       <c r="J721" s="3" t="n"/>
       <c r="K721" s="3" t="n"/>
       <c r="L721" s="3" t="n"/>
+      <c r="M721" s="3" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="3" t="n"/>
@@ -10745,6 +11476,7 @@
       <c r="J722" s="3" t="n"/>
       <c r="K722" s="3" t="n"/>
       <c r="L722" s="3" t="n"/>
+      <c r="M722" s="3" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="3" t="n"/>
@@ -10759,6 +11491,7 @@
       <c r="J723" s="3" t="n"/>
       <c r="K723" s="3" t="n"/>
       <c r="L723" s="3" t="n"/>
+      <c r="M723" s="3" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="3" t="n"/>
@@ -10773,6 +11506,7 @@
       <c r="J724" s="3" t="n"/>
       <c r="K724" s="3" t="n"/>
       <c r="L724" s="3" t="n"/>
+      <c r="M724" s="3" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="3" t="n"/>
@@ -10787,6 +11521,7 @@
       <c r="J725" s="3" t="n"/>
       <c r="K725" s="3" t="n"/>
       <c r="L725" s="3" t="n"/>
+      <c r="M725" s="3" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="3" t="n"/>
@@ -10801,6 +11536,7 @@
       <c r="J726" s="3" t="n"/>
       <c r="K726" s="3" t="n"/>
       <c r="L726" s="3" t="n"/>
+      <c r="M726" s="3" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="3" t="n"/>
@@ -10815,6 +11551,7 @@
       <c r="J727" s="3" t="n"/>
       <c r="K727" s="3" t="n"/>
       <c r="L727" s="3" t="n"/>
+      <c r="M727" s="3" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="3" t="n"/>
@@ -10829,6 +11566,7 @@
       <c r="J728" s="3" t="n"/>
       <c r="K728" s="3" t="n"/>
       <c r="L728" s="3" t="n"/>
+      <c r="M728" s="3" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="3" t="n"/>
@@ -10843,6 +11581,7 @@
       <c r="J729" s="3" t="n"/>
       <c r="K729" s="3" t="n"/>
       <c r="L729" s="3" t="n"/>
+      <c r="M729" s="3" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="3" t="n"/>
@@ -10857,6 +11596,7 @@
       <c r="J730" s="3" t="n"/>
       <c r="K730" s="3" t="n"/>
       <c r="L730" s="3" t="n"/>
+      <c r="M730" s="3" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="3" t="n"/>
@@ -10871,6 +11611,7 @@
       <c r="J731" s="3" t="n"/>
       <c r="K731" s="3" t="n"/>
       <c r="L731" s="3" t="n"/>
+      <c r="M731" s="3" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="3" t="n"/>
@@ -10885,6 +11626,7 @@
       <c r="J732" s="3" t="n"/>
       <c r="K732" s="3" t="n"/>
       <c r="L732" s="3" t="n"/>
+      <c r="M732" s="3" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="3" t="n"/>
@@ -10899,6 +11641,7 @@
       <c r="J733" s="3" t="n"/>
       <c r="K733" s="3" t="n"/>
       <c r="L733" s="3" t="n"/>
+      <c r="M733" s="3" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="3" t="n"/>
@@ -10913,6 +11656,7 @@
       <c r="J734" s="3" t="n"/>
       <c r="K734" s="3" t="n"/>
       <c r="L734" s="3" t="n"/>
+      <c r="M734" s="3" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="3" t="n"/>
@@ -10927,6 +11671,7 @@
       <c r="J735" s="3" t="n"/>
       <c r="K735" s="3" t="n"/>
       <c r="L735" s="3" t="n"/>
+      <c r="M735" s="3" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="3" t="n"/>
@@ -10941,6 +11686,7 @@
       <c r="J736" s="3" t="n"/>
       <c r="K736" s="3" t="n"/>
       <c r="L736" s="3" t="n"/>
+      <c r="M736" s="3" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="3" t="n"/>
@@ -10955,6 +11701,7 @@
       <c r="J737" s="3" t="n"/>
       <c r="K737" s="3" t="n"/>
       <c r="L737" s="3" t="n"/>
+      <c r="M737" s="3" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="3" t="n"/>
@@ -10969,6 +11716,7 @@
       <c r="J738" s="3" t="n"/>
       <c r="K738" s="3" t="n"/>
       <c r="L738" s="3" t="n"/>
+      <c r="M738" s="3" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="3" t="n"/>
@@ -10983,6 +11731,7 @@
       <c r="J739" s="3" t="n"/>
       <c r="K739" s="3" t="n"/>
       <c r="L739" s="3" t="n"/>
+      <c r="M739" s="3" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="3" t="n"/>
@@ -10997,6 +11746,7 @@
       <c r="J740" s="3" t="n"/>
       <c r="K740" s="3" t="n"/>
       <c r="L740" s="3" t="n"/>
+      <c r="M740" s="3" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="3" t="n"/>
@@ -11011,6 +11761,7 @@
       <c r="J741" s="3" t="n"/>
       <c r="K741" s="3" t="n"/>
       <c r="L741" s="3" t="n"/>
+      <c r="M741" s="3" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="3" t="n"/>
@@ -11025,6 +11776,7 @@
       <c r="J742" s="3" t="n"/>
       <c r="K742" s="3" t="n"/>
       <c r="L742" s="3" t="n"/>
+      <c r="M742" s="3" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="3" t="n"/>
@@ -11039,6 +11791,7 @@
       <c r="J743" s="3" t="n"/>
       <c r="K743" s="3" t="n"/>
       <c r="L743" s="3" t="n"/>
+      <c r="M743" s="3" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="3" t="n"/>
@@ -11053,6 +11806,7 @@
       <c r="J744" s="3" t="n"/>
       <c r="K744" s="3" t="n"/>
       <c r="L744" s="3" t="n"/>
+      <c r="M744" s="3" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="3" t="n"/>
@@ -11067,6 +11821,7 @@
       <c r="J745" s="3" t="n"/>
       <c r="K745" s="3" t="n"/>
       <c r="L745" s="3" t="n"/>
+      <c r="M745" s="3" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="3" t="n"/>
@@ -11081,6 +11836,7 @@
       <c r="J746" s="3" t="n"/>
       <c r="K746" s="3" t="n"/>
       <c r="L746" s="3" t="n"/>
+      <c r="M746" s="3" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="3" t="n"/>
@@ -11095,6 +11851,7 @@
       <c r="J747" s="3" t="n"/>
       <c r="K747" s="3" t="n"/>
       <c r="L747" s="3" t="n"/>
+      <c r="M747" s="3" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="3" t="n"/>
@@ -11109,6 +11866,7 @@
       <c r="J748" s="3" t="n"/>
       <c r="K748" s="3" t="n"/>
       <c r="L748" s="3" t="n"/>
+      <c r="M748" s="3" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="3" t="n"/>
@@ -11123,6 +11881,7 @@
       <c r="J749" s="3" t="n"/>
       <c r="K749" s="3" t="n"/>
       <c r="L749" s="3" t="n"/>
+      <c r="M749" s="3" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="3" t="n"/>
@@ -11137,6 +11896,7 @@
       <c r="J750" s="3" t="n"/>
       <c r="K750" s="3" t="n"/>
       <c r="L750" s="3" t="n"/>
+      <c r="M750" s="3" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="3" t="n"/>
@@ -11151,6 +11911,7 @@
       <c r="J751" s="3" t="n"/>
       <c r="K751" s="3" t="n"/>
       <c r="L751" s="3" t="n"/>
+      <c r="M751" s="3" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="3" t="n"/>
@@ -11165,6 +11926,7 @@
       <c r="J752" s="3" t="n"/>
       <c r="K752" s="3" t="n"/>
       <c r="L752" s="3" t="n"/>
+      <c r="M752" s="3" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="3" t="n"/>
@@ -11179,6 +11941,7 @@
       <c r="J753" s="3" t="n"/>
       <c r="K753" s="3" t="n"/>
       <c r="L753" s="3" t="n"/>
+      <c r="M753" s="3" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="3" t="n"/>
@@ -11193,6 +11956,7 @@
       <c r="J754" s="3" t="n"/>
       <c r="K754" s="3" t="n"/>
       <c r="L754" s="3" t="n"/>
+      <c r="M754" s="3" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="3" t="n"/>
@@ -11207,6 +11971,7 @@
       <c r="J755" s="3" t="n"/>
       <c r="K755" s="3" t="n"/>
       <c r="L755" s="3" t="n"/>
+      <c r="M755" s="3" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="3" t="n"/>
@@ -11221,6 +11986,7 @@
       <c r="J756" s="3" t="n"/>
       <c r="K756" s="3" t="n"/>
       <c r="L756" s="3" t="n"/>
+      <c r="M756" s="3" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="3" t="n"/>
@@ -11235,6 +12001,7 @@
       <c r="J757" s="3" t="n"/>
       <c r="K757" s="3" t="n"/>
       <c r="L757" s="3" t="n"/>
+      <c r="M757" s="3" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="3" t="n"/>
@@ -11249,6 +12016,7 @@
       <c r="J758" s="3" t="n"/>
       <c r="K758" s="3" t="n"/>
       <c r="L758" s="3" t="n"/>
+      <c r="M758" s="3" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="3" t="n"/>
@@ -11263,6 +12031,7 @@
       <c r="J759" s="3" t="n"/>
       <c r="K759" s="3" t="n"/>
       <c r="L759" s="3" t="n"/>
+      <c r="M759" s="3" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="3" t="n"/>
@@ -11277,6 +12046,7 @@
       <c r="J760" s="3" t="n"/>
       <c r="K760" s="3" t="n"/>
       <c r="L760" s="3" t="n"/>
+      <c r="M760" s="3" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="3" t="n"/>
@@ -11291,6 +12061,7 @@
       <c r="J761" s="3" t="n"/>
       <c r="K761" s="3" t="n"/>
       <c r="L761" s="3" t="n"/>
+      <c r="M761" s="3" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="3" t="n"/>
@@ -11305,6 +12076,7 @@
       <c r="J762" s="3" t="n"/>
       <c r="K762" s="3" t="n"/>
       <c r="L762" s="3" t="n"/>
+      <c r="M762" s="3" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="3" t="n"/>
@@ -11319,6 +12091,7 @@
       <c r="J763" s="3" t="n"/>
       <c r="K763" s="3" t="n"/>
       <c r="L763" s="3" t="n"/>
+      <c r="M763" s="3" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="3" t="n"/>
@@ -11333,6 +12106,7 @@
       <c r="J764" s="3" t="n"/>
       <c r="K764" s="3" t="n"/>
       <c r="L764" s="3" t="n"/>
+      <c r="M764" s="3" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="3" t="n"/>
@@ -11347,6 +12121,7 @@
       <c r="J765" s="3" t="n"/>
       <c r="K765" s="3" t="n"/>
       <c r="L765" s="3" t="n"/>
+      <c r="M765" s="3" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="3" t="n"/>
@@ -11361,6 +12136,7 @@
       <c r="J766" s="3" t="n"/>
       <c r="K766" s="3" t="n"/>
       <c r="L766" s="3" t="n"/>
+      <c r="M766" s="3" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="3" t="n"/>
@@ -11375,6 +12151,7 @@
       <c r="J767" s="3" t="n"/>
       <c r="K767" s="3" t="n"/>
       <c r="L767" s="3" t="n"/>
+      <c r="M767" s="3" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="3" t="n"/>
@@ -11389,6 +12166,7 @@
       <c r="J768" s="3" t="n"/>
       <c r="K768" s="3" t="n"/>
       <c r="L768" s="3" t="n"/>
+      <c r="M768" s="3" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="3" t="n"/>
@@ -11403,6 +12181,7 @@
       <c r="J769" s="3" t="n"/>
       <c r="K769" s="3" t="n"/>
       <c r="L769" s="3" t="n"/>
+      <c r="M769" s="3" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="3" t="n"/>
@@ -11417,6 +12196,7 @@
       <c r="J770" s="3" t="n"/>
       <c r="K770" s="3" t="n"/>
       <c r="L770" s="3" t="n"/>
+      <c r="M770" s="3" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="3" t="n"/>
@@ -11431,6 +12211,7 @@
       <c r="J771" s="3" t="n"/>
       <c r="K771" s="3" t="n"/>
       <c r="L771" s="3" t="n"/>
+      <c r="M771" s="3" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="3" t="n"/>
@@ -11445,6 +12226,7 @@
       <c r="J772" s="3" t="n"/>
       <c r="K772" s="3" t="n"/>
       <c r="L772" s="3" t="n"/>
+      <c r="M772" s="3" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="3" t="n"/>
@@ -11459,6 +12241,7 @@
       <c r="J773" s="3" t="n"/>
       <c r="K773" s="3" t="n"/>
       <c r="L773" s="3" t="n"/>
+      <c r="M773" s="3" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="3" t="n"/>
@@ -11473,6 +12256,7 @@
       <c r="J774" s="3" t="n"/>
       <c r="K774" s="3" t="n"/>
       <c r="L774" s="3" t="n"/>
+      <c r="M774" s="3" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="3" t="n"/>
@@ -11487,6 +12271,7 @@
       <c r="J775" s="3" t="n"/>
       <c r="K775" s="3" t="n"/>
       <c r="L775" s="3" t="n"/>
+      <c r="M775" s="3" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="3" t="n"/>
@@ -11501,6 +12286,7 @@
       <c r="J776" s="3" t="n"/>
       <c r="K776" s="3" t="n"/>
       <c r="L776" s="3" t="n"/>
+      <c r="M776" s="3" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="3" t="n"/>
@@ -11515,6 +12301,7 @@
       <c r="J777" s="3" t="n"/>
       <c r="K777" s="3" t="n"/>
       <c r="L777" s="3" t="n"/>
+      <c r="M777" s="3" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="3" t="n"/>
@@ -11529,6 +12316,7 @@
       <c r="J778" s="3" t="n"/>
       <c r="K778" s="3" t="n"/>
       <c r="L778" s="3" t="n"/>
+      <c r="M778" s="3" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="3" t="n"/>
@@ -11543,6 +12331,7 @@
       <c r="J779" s="3" t="n"/>
       <c r="K779" s="3" t="n"/>
       <c r="L779" s="3" t="n"/>
+      <c r="M779" s="3" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="3" t="n"/>
@@ -11557,6 +12346,7 @@
       <c r="J780" s="3" t="n"/>
       <c r="K780" s="3" t="n"/>
       <c r="L780" s="3" t="n"/>
+      <c r="M780" s="3" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="3" t="n"/>
@@ -11571,6 +12361,7 @@
       <c r="J781" s="3" t="n"/>
       <c r="K781" s="3" t="n"/>
       <c r="L781" s="3" t="n"/>
+      <c r="M781" s="3" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="3" t="n"/>
@@ -11585,6 +12376,7 @@
       <c r="J782" s="3" t="n"/>
       <c r="K782" s="3" t="n"/>
       <c r="L782" s="3" t="n"/>
+      <c r="M782" s="3" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="3" t="n"/>
@@ -11599,6 +12391,7 @@
       <c r="J783" s="3" t="n"/>
       <c r="K783" s="3" t="n"/>
       <c r="L783" s="3" t="n"/>
+      <c r="M783" s="3" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="3" t="n"/>
@@ -11613,6 +12406,7 @@
       <c r="J784" s="3" t="n"/>
       <c r="K784" s="3" t="n"/>
       <c r="L784" s="3" t="n"/>
+      <c r="M784" s="3" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="3" t="n"/>
@@ -11627,6 +12421,7 @@
       <c r="J785" s="3" t="n"/>
       <c r="K785" s="3" t="n"/>
       <c r="L785" s="3" t="n"/>
+      <c r="M785" s="3" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="3" t="n"/>
@@ -11641,6 +12436,7 @@
       <c r="J786" s="3" t="n"/>
       <c r="K786" s="3" t="n"/>
       <c r="L786" s="3" t="n"/>
+      <c r="M786" s="3" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="3" t="n"/>
@@ -11655,6 +12451,7 @@
       <c r="J787" s="3" t="n"/>
       <c r="K787" s="3" t="n"/>
       <c r="L787" s="3" t="n"/>
+      <c r="M787" s="3" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="3" t="n"/>
@@ -11669,6 +12466,7 @@
       <c r="J788" s="3" t="n"/>
       <c r="K788" s="3" t="n"/>
       <c r="L788" s="3" t="n"/>
+      <c r="M788" s="3" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="3" t="n"/>
@@ -11683,6 +12481,7 @@
       <c r="J789" s="3" t="n"/>
       <c r="K789" s="3" t="n"/>
       <c r="L789" s="3" t="n"/>
+      <c r="M789" s="3" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="3" t="n"/>
@@ -11697,6 +12496,7 @@
       <c r="J790" s="3" t="n"/>
       <c r="K790" s="3" t="n"/>
       <c r="L790" s="3" t="n"/>
+      <c r="M790" s="3" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="3" t="n"/>
@@ -11711,6 +12511,7 @@
       <c r="J791" s="3" t="n"/>
       <c r="K791" s="3" t="n"/>
       <c r="L791" s="3" t="n"/>
+      <c r="M791" s="3" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="3" t="n"/>
@@ -11725,6 +12526,7 @@
       <c r="J792" s="3" t="n"/>
       <c r="K792" s="3" t="n"/>
       <c r="L792" s="3" t="n"/>
+      <c r="M792" s="3" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="3" t="n"/>
@@ -11739,6 +12541,7 @@
       <c r="J793" s="3" t="n"/>
       <c r="K793" s="3" t="n"/>
       <c r="L793" s="3" t="n"/>
+      <c r="M793" s="3" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="3" t="n"/>
@@ -11753,6 +12556,7 @@
       <c r="J794" s="3" t="n"/>
       <c r="K794" s="3" t="n"/>
       <c r="L794" s="3" t="n"/>
+      <c r="M794" s="3" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="3" t="n"/>
@@ -11767,6 +12571,7 @@
       <c r="J795" s="3" t="n"/>
       <c r="K795" s="3" t="n"/>
       <c r="L795" s="3" t="n"/>
+      <c r="M795" s="3" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="3" t="n"/>
@@ -11781,6 +12586,7 @@
       <c r="J796" s="3" t="n"/>
       <c r="K796" s="3" t="n"/>
       <c r="L796" s="3" t="n"/>
+      <c r="M796" s="3" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="3" t="n"/>
@@ -11795,6 +12601,7 @@
       <c r="J797" s="3" t="n"/>
       <c r="K797" s="3" t="n"/>
       <c r="L797" s="3" t="n"/>
+      <c r="M797" s="3" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="3" t="n"/>
@@ -11809,6 +12616,7 @@
       <c r="J798" s="3" t="n"/>
       <c r="K798" s="3" t="n"/>
       <c r="L798" s="3" t="n"/>
+      <c r="M798" s="3" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="3" t="n"/>
@@ -11823,6 +12631,7 @@
       <c r="J799" s="3" t="n"/>
       <c r="K799" s="3" t="n"/>
       <c r="L799" s="3" t="n"/>
+      <c r="M799" s="3" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="3" t="n"/>
@@ -11837,6 +12646,7 @@
       <c r="J800" s="3" t="n"/>
       <c r="K800" s="3" t="n"/>
       <c r="L800" s="3" t="n"/>
+      <c r="M800" s="3" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="3" t="n"/>
@@ -11851,6 +12661,7 @@
       <c r="J801" s="3" t="n"/>
       <c r="K801" s="3" t="n"/>
       <c r="L801" s="3" t="n"/>
+      <c r="M801" s="3" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="3" t="n"/>
@@ -11865,6 +12676,7 @@
       <c r="J802" s="3" t="n"/>
       <c r="K802" s="3" t="n"/>
       <c r="L802" s="3" t="n"/>
+      <c r="M802" s="3" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="3" t="n"/>
@@ -11879,6 +12691,7 @@
       <c r="J803" s="3" t="n"/>
       <c r="K803" s="3" t="n"/>
       <c r="L803" s="3" t="n"/>
+      <c r="M803" s="3" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="3" t="n"/>
@@ -11893,6 +12706,7 @@
       <c r="J804" s="3" t="n"/>
       <c r="K804" s="3" t="n"/>
       <c r="L804" s="3" t="n"/>
+      <c r="M804" s="3" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="3" t="n"/>
@@ -11907,6 +12721,7 @@
       <c r="J805" s="3" t="n"/>
       <c r="K805" s="3" t="n"/>
       <c r="L805" s="3" t="n"/>
+      <c r="M805" s="3" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="3" t="n"/>
@@ -11921,6 +12736,7 @@
       <c r="J806" s="3" t="n"/>
       <c r="K806" s="3" t="n"/>
       <c r="L806" s="3" t="n"/>
+      <c r="M806" s="3" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="3" t="n"/>
@@ -11935,6 +12751,7 @@
       <c r="J807" s="3" t="n"/>
       <c r="K807" s="3" t="n"/>
       <c r="L807" s="3" t="n"/>
+      <c r="M807" s="3" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="3" t="n"/>
@@ -11949,6 +12766,7 @@
       <c r="J808" s="3" t="n"/>
       <c r="K808" s="3" t="n"/>
       <c r="L808" s="3" t="n"/>
+      <c r="M808" s="3" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="3" t="n"/>
@@ -11963,6 +12781,7 @@
       <c r="J809" s="3" t="n"/>
       <c r="K809" s="3" t="n"/>
       <c r="L809" s="3" t="n"/>
+      <c r="M809" s="3" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="3" t="n"/>
@@ -11977,6 +12796,7 @@
       <c r="J810" s="3" t="n"/>
       <c r="K810" s="3" t="n"/>
       <c r="L810" s="3" t="n"/>
+      <c r="M810" s="3" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="3" t="n"/>
@@ -11991,6 +12811,7 @@
       <c r="J811" s="3" t="n"/>
       <c r="K811" s="3" t="n"/>
       <c r="L811" s="3" t="n"/>
+      <c r="M811" s="3" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="3" t="n"/>
@@ -12005,6 +12826,7 @@
       <c r="J812" s="3" t="n"/>
       <c r="K812" s="3" t="n"/>
       <c r="L812" s="3" t="n"/>
+      <c r="M812" s="3" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="3" t="n"/>
@@ -12019,6 +12841,7 @@
       <c r="J813" s="3" t="n"/>
       <c r="K813" s="3" t="n"/>
       <c r="L813" s="3" t="n"/>
+      <c r="M813" s="3" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="3" t="n"/>
@@ -12033,6 +12856,7 @@
       <c r="J814" s="3" t="n"/>
       <c r="K814" s="3" t="n"/>
       <c r="L814" s="3" t="n"/>
+      <c r="M814" s="3" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="3" t="n"/>
@@ -12047,6 +12871,7 @@
       <c r="J815" s="3" t="n"/>
       <c r="K815" s="3" t="n"/>
       <c r="L815" s="3" t="n"/>
+      <c r="M815" s="3" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="3" t="n"/>
@@ -12061,6 +12886,7 @@
       <c r="J816" s="3" t="n"/>
       <c r="K816" s="3" t="n"/>
       <c r="L816" s="3" t="n"/>
+      <c r="M816" s="3" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="3" t="n"/>
@@ -12075,6 +12901,7 @@
       <c r="J817" s="3" t="n"/>
       <c r="K817" s="3" t="n"/>
       <c r="L817" s="3" t="n"/>
+      <c r="M817" s="3" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="3" t="n"/>
@@ -12089,6 +12916,7 @@
       <c r="J818" s="3" t="n"/>
       <c r="K818" s="3" t="n"/>
       <c r="L818" s="3" t="n"/>
+      <c r="M818" s="3" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="3" t="n"/>
@@ -12103,6 +12931,7 @@
       <c r="J819" s="3" t="n"/>
       <c r="K819" s="3" t="n"/>
       <c r="L819" s="3" t="n"/>
+      <c r="M819" s="3" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="3" t="n"/>
@@ -12117,6 +12946,7 @@
       <c r="J820" s="3" t="n"/>
       <c r="K820" s="3" t="n"/>
       <c r="L820" s="3" t="n"/>
+      <c r="M820" s="3" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="3" t="n"/>
@@ -12131,6 +12961,7 @@
       <c r="J821" s="3" t="n"/>
       <c r="K821" s="3" t="n"/>
       <c r="L821" s="3" t="n"/>
+      <c r="M821" s="3" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="3" t="n"/>
@@ -12145,6 +12976,7 @@
       <c r="J822" s="3" t="n"/>
       <c r="K822" s="3" t="n"/>
       <c r="L822" s="3" t="n"/>
+      <c r="M822" s="3" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="3" t="n"/>
@@ -12159,6 +12991,7 @@
       <c r="J823" s="3" t="n"/>
       <c r="K823" s="3" t="n"/>
       <c r="L823" s="3" t="n"/>
+      <c r="M823" s="3" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="3" t="n"/>
@@ -12173,6 +13006,7 @@
       <c r="J824" s="3" t="n"/>
       <c r="K824" s="3" t="n"/>
       <c r="L824" s="3" t="n"/>
+      <c r="M824" s="3" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="3" t="n"/>
@@ -12187,6 +13021,7 @@
       <c r="J825" s="3" t="n"/>
       <c r="K825" s="3" t="n"/>
       <c r="L825" s="3" t="n"/>
+      <c r="M825" s="3" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="3" t="n"/>
@@ -12201,6 +13036,7 @@
       <c r="J826" s="3" t="n"/>
       <c r="K826" s="3" t="n"/>
       <c r="L826" s="3" t="n"/>
+      <c r="M826" s="3" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="3" t="n"/>
@@ -12215,6 +13051,7 @@
       <c r="J827" s="3" t="n"/>
       <c r="K827" s="3" t="n"/>
       <c r="L827" s="3" t="n"/>
+      <c r="M827" s="3" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="3" t="n"/>
@@ -12229,6 +13066,7 @@
       <c r="J828" s="3" t="n"/>
       <c r="K828" s="3" t="n"/>
       <c r="L828" s="3" t="n"/>
+      <c r="M828" s="3" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="3" t="n"/>
@@ -12243,6 +13081,7 @@
       <c r="J829" s="3" t="n"/>
       <c r="K829" s="3" t="n"/>
       <c r="L829" s="3" t="n"/>
+      <c r="M829" s="3" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="3" t="n"/>
@@ -12257,6 +13096,7 @@
       <c r="J830" s="3" t="n"/>
       <c r="K830" s="3" t="n"/>
       <c r="L830" s="3" t="n"/>
+      <c r="M830" s="3" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="3" t="n"/>
@@ -12271,6 +13111,7 @@
       <c r="J831" s="3" t="n"/>
       <c r="K831" s="3" t="n"/>
       <c r="L831" s="3" t="n"/>
+      <c r="M831" s="3" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="3" t="n"/>
@@ -12285,6 +13126,7 @@
       <c r="J832" s="3" t="n"/>
       <c r="K832" s="3" t="n"/>
       <c r="L832" s="3" t="n"/>
+      <c r="M832" s="3" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="3" t="n"/>
@@ -12299,6 +13141,7 @@
       <c r="J833" s="3" t="n"/>
       <c r="K833" s="3" t="n"/>
       <c r="L833" s="3" t="n"/>
+      <c r="M833" s="3" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="3" t="n"/>
@@ -12313,6 +13156,7 @@
       <c r="J834" s="3" t="n"/>
       <c r="K834" s="3" t="n"/>
       <c r="L834" s="3" t="n"/>
+      <c r="M834" s="3" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="3" t="n"/>
@@ -12327,6 +13171,7 @@
       <c r="J835" s="3" t="n"/>
       <c r="K835" s="3" t="n"/>
       <c r="L835" s="3" t="n"/>
+      <c r="M835" s="3" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="3" t="n"/>
@@ -12341,6 +13186,7 @@
       <c r="J836" s="3" t="n"/>
       <c r="K836" s="3" t="n"/>
       <c r="L836" s="3" t="n"/>
+      <c r="M836" s="3" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="3" t="n"/>
@@ -12355,6 +13201,7 @@
       <c r="J837" s="3" t="n"/>
       <c r="K837" s="3" t="n"/>
       <c r="L837" s="3" t="n"/>
+      <c r="M837" s="3" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="3" t="n"/>
@@ -12369,6 +13216,7 @@
       <c r="J838" s="3" t="n"/>
       <c r="K838" s="3" t="n"/>
       <c r="L838" s="3" t="n"/>
+      <c r="M838" s="3" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="3" t="n"/>
@@ -12383,6 +13231,7 @@
       <c r="J839" s="3" t="n"/>
       <c r="K839" s="3" t="n"/>
       <c r="L839" s="3" t="n"/>
+      <c r="M839" s="3" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="3" t="n"/>
@@ -12397,6 +13246,7 @@
       <c r="J840" s="3" t="n"/>
       <c r="K840" s="3" t="n"/>
       <c r="L840" s="3" t="n"/>
+      <c r="M840" s="3" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="3" t="n"/>
@@ -12411,6 +13261,7 @@
       <c r="J841" s="3" t="n"/>
       <c r="K841" s="3" t="n"/>
       <c r="L841" s="3" t="n"/>
+      <c r="M841" s="3" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="3" t="n"/>
@@ -12425,6 +13276,7 @@
       <c r="J842" s="3" t="n"/>
       <c r="K842" s="3" t="n"/>
       <c r="L842" s="3" t="n"/>
+      <c r="M842" s="3" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="3" t="n"/>
@@ -12439,6 +13291,7 @@
       <c r="J843" s="3" t="n"/>
       <c r="K843" s="3" t="n"/>
       <c r="L843" s="3" t="n"/>
+      <c r="M843" s="3" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="3" t="n"/>
@@ -12453,6 +13306,7 @@
       <c r="J844" s="3" t="n"/>
       <c r="K844" s="3" t="n"/>
       <c r="L844" s="3" t="n"/>
+      <c r="M844" s="3" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="3" t="n"/>
@@ -12467,6 +13321,7 @@
       <c r="J845" s="3" t="n"/>
       <c r="K845" s="3" t="n"/>
       <c r="L845" s="3" t="n"/>
+      <c r="M845" s="3" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="3" t="n"/>
@@ -12481,6 +13336,7 @@
       <c r="J846" s="3" t="n"/>
       <c r="K846" s="3" t="n"/>
       <c r="L846" s="3" t="n"/>
+      <c r="M846" s="3" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="3" t="n"/>
@@ -12495,6 +13351,7 @@
       <c r="J847" s="3" t="n"/>
       <c r="K847" s="3" t="n"/>
       <c r="L847" s="3" t="n"/>
+      <c r="M847" s="3" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="3" t="n"/>
@@ -12509,6 +13366,7 @@
       <c r="J848" s="3" t="n"/>
       <c r="K848" s="3" t="n"/>
       <c r="L848" s="3" t="n"/>
+      <c r="M848" s="3" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="3" t="n"/>
@@ -12523,6 +13381,7 @@
       <c r="J849" s="3" t="n"/>
       <c r="K849" s="3" t="n"/>
       <c r="L849" s="3" t="n"/>
+      <c r="M849" s="3" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="3" t="n"/>
@@ -12537,6 +13396,7 @@
       <c r="J850" s="3" t="n"/>
       <c r="K850" s="3" t="n"/>
       <c r="L850" s="3" t="n"/>
+      <c r="M850" s="3" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="3" t="n"/>
@@ -12551,6 +13411,7 @@
       <c r="J851" s="3" t="n"/>
       <c r="K851" s="3" t="n"/>
       <c r="L851" s="3" t="n"/>
+      <c r="M851" s="3" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="3" t="n"/>
@@ -12565,6 +13426,7 @@
       <c r="J852" s="3" t="n"/>
       <c r="K852" s="3" t="n"/>
       <c r="L852" s="3" t="n"/>
+      <c r="M852" s="3" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="3" t="n"/>
@@ -12579,6 +13441,7 @@
       <c r="J853" s="3" t="n"/>
       <c r="K853" s="3" t="n"/>
       <c r="L853" s="3" t="n"/>
+      <c r="M853" s="3" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="3" t="n"/>
@@ -12593,6 +13456,7 @@
       <c r="J854" s="3" t="n"/>
       <c r="K854" s="3" t="n"/>
       <c r="L854" s="3" t="n"/>
+      <c r="M854" s="3" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="3" t="n"/>
@@ -12607,6 +13471,7 @@
       <c r="J855" s="3" t="n"/>
       <c r="K855" s="3" t="n"/>
       <c r="L855" s="3" t="n"/>
+      <c r="M855" s="3" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="3" t="n"/>
@@ -12621,6 +13486,7 @@
       <c r="J856" s="3" t="n"/>
       <c r="K856" s="3" t="n"/>
       <c r="L856" s="3" t="n"/>
+      <c r="M856" s="3" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="3" t="n"/>
@@ -12635,6 +13501,7 @@
       <c r="J857" s="3" t="n"/>
       <c r="K857" s="3" t="n"/>
       <c r="L857" s="3" t="n"/>
+      <c r="M857" s="3" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="3" t="n"/>
@@ -12649,6 +13516,7 @@
       <c r="J858" s="3" t="n"/>
       <c r="K858" s="3" t="n"/>
       <c r="L858" s="3" t="n"/>
+      <c r="M858" s="3" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="3" t="n"/>
@@ -12663,6 +13531,7 @@
       <c r="J859" s="3" t="n"/>
       <c r="K859" s="3" t="n"/>
       <c r="L859" s="3" t="n"/>
+      <c r="M859" s="3" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="3" t="n"/>
@@ -12677,6 +13546,7 @@
       <c r="J860" s="3" t="n"/>
       <c r="K860" s="3" t="n"/>
       <c r="L860" s="3" t="n"/>
+      <c r="M860" s="3" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="3" t="n"/>
@@ -12691,6 +13561,7 @@
       <c r="J861" s="3" t="n"/>
       <c r="K861" s="3" t="n"/>
       <c r="L861" s="3" t="n"/>
+      <c r="M861" s="3" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="3" t="n"/>
@@ -12705,6 +13576,7 @@
       <c r="J862" s="3" t="n"/>
       <c r="K862" s="3" t="n"/>
       <c r="L862" s="3" t="n"/>
+      <c r="M862" s="3" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="3" t="n"/>
@@ -12719,6 +13591,7 @@
       <c r="J863" s="3" t="n"/>
       <c r="K863" s="3" t="n"/>
       <c r="L863" s="3" t="n"/>
+      <c r="M863" s="3" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="3" t="n"/>
@@ -12733,6 +13606,7 @@
       <c r="J864" s="3" t="n"/>
       <c r="K864" s="3" t="n"/>
       <c r="L864" s="3" t="n"/>
+      <c r="M864" s="3" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="3" t="n"/>
@@ -12747,6 +13621,7 @@
       <c r="J865" s="3" t="n"/>
       <c r="K865" s="3" t="n"/>
       <c r="L865" s="3" t="n"/>
+      <c r="M865" s="3" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="3" t="n"/>
@@ -12761,6 +13636,7 @@
       <c r="J866" s="3" t="n"/>
       <c r="K866" s="3" t="n"/>
       <c r="L866" s="3" t="n"/>
+      <c r="M866" s="3" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="3" t="n"/>
@@ -12775,6 +13651,7 @@
       <c r="J867" s="3" t="n"/>
       <c r="K867" s="3" t="n"/>
       <c r="L867" s="3" t="n"/>
+      <c r="M867" s="3" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="3" t="n"/>
@@ -12789,6 +13666,7 @@
       <c r="J868" s="3" t="n"/>
       <c r="K868" s="3" t="n"/>
       <c r="L868" s="3" t="n"/>
+      <c r="M868" s="3" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="3" t="n"/>
@@ -12803,6 +13681,7 @@
       <c r="J869" s="3" t="n"/>
       <c r="K869" s="3" t="n"/>
       <c r="L869" s="3" t="n"/>
+      <c r="M869" s="3" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="3" t="n"/>
@@ -12817,6 +13696,7 @@
       <c r="J870" s="3" t="n"/>
       <c r="K870" s="3" t="n"/>
       <c r="L870" s="3" t="n"/>
+      <c r="M870" s="3" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="3" t="n"/>
@@ -12831,6 +13711,7 @@
       <c r="J871" s="3" t="n"/>
       <c r="K871" s="3" t="n"/>
       <c r="L871" s="3" t="n"/>
+      <c r="M871" s="3" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="3" t="n"/>
@@ -12845,6 +13726,7 @@
       <c r="J872" s="3" t="n"/>
       <c r="K872" s="3" t="n"/>
       <c r="L872" s="3" t="n"/>
+      <c r="M872" s="3" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="3" t="n"/>
@@ -12859,6 +13741,7 @@
       <c r="J873" s="3" t="n"/>
       <c r="K873" s="3" t="n"/>
       <c r="L873" s="3" t="n"/>
+      <c r="M873" s="3" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="3" t="n"/>
@@ -12873,6 +13756,7 @@
       <c r="J874" s="3" t="n"/>
       <c r="K874" s="3" t="n"/>
       <c r="L874" s="3" t="n"/>
+      <c r="M874" s="3" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="3" t="n"/>
@@ -12887,6 +13771,7 @@
       <c r="J875" s="3" t="n"/>
       <c r="K875" s="3" t="n"/>
       <c r="L875" s="3" t="n"/>
+      <c r="M875" s="3" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="3" t="n"/>
@@ -12901,6 +13786,7 @@
       <c r="J876" s="3" t="n"/>
       <c r="K876" s="3" t="n"/>
       <c r="L876" s="3" t="n"/>
+      <c r="M876" s="3" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="3" t="n"/>
@@ -12915,6 +13801,7 @@
       <c r="J877" s="3" t="n"/>
       <c r="K877" s="3" t="n"/>
       <c r="L877" s="3" t="n"/>
+      <c r="M877" s="3" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="3" t="n"/>
@@ -12929,6 +13816,7 @@
       <c r="J878" s="3" t="n"/>
       <c r="K878" s="3" t="n"/>
       <c r="L878" s="3" t="n"/>
+      <c r="M878" s="3" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="3" t="n"/>
@@ -12943,6 +13831,7 @@
       <c r="J879" s="3" t="n"/>
       <c r="K879" s="3" t="n"/>
       <c r="L879" s="3" t="n"/>
+      <c r="M879" s="3" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="3" t="n"/>
@@ -12957,6 +13846,7 @@
       <c r="J880" s="3" t="n"/>
       <c r="K880" s="3" t="n"/>
       <c r="L880" s="3" t="n"/>
+      <c r="M880" s="3" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="3" t="n"/>
@@ -12971,6 +13861,7 @@
       <c r="J881" s="3" t="n"/>
       <c r="K881" s="3" t="n"/>
       <c r="L881" s="3" t="n"/>
+      <c r="M881" s="3" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="3" t="n"/>
@@ -12985,6 +13876,7 @@
       <c r="J882" s="3" t="n"/>
       <c r="K882" s="3" t="n"/>
       <c r="L882" s="3" t="n"/>
+      <c r="M882" s="3" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="3" t="n"/>
@@ -12999,6 +13891,7 @@
       <c r="J883" s="3" t="n"/>
       <c r="K883" s="3" t="n"/>
       <c r="L883" s="3" t="n"/>
+      <c r="M883" s="3" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="3" t="n"/>
@@ -13013,6 +13906,7 @@
       <c r="J884" s="3" t="n"/>
       <c r="K884" s="3" t="n"/>
       <c r="L884" s="3" t="n"/>
+      <c r="M884" s="3" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="3" t="n"/>
@@ -13027,6 +13921,7 @@
       <c r="J885" s="3" t="n"/>
       <c r="K885" s="3" t="n"/>
       <c r="L885" s="3" t="n"/>
+      <c r="M885" s="3" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="3" t="n"/>
@@ -13041,6 +13936,7 @@
       <c r="J886" s="3" t="n"/>
       <c r="K886" s="3" t="n"/>
       <c r="L886" s="3" t="n"/>
+      <c r="M886" s="3" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="3" t="n"/>
@@ -13055,6 +13951,7 @@
       <c r="J887" s="3" t="n"/>
       <c r="K887" s="3" t="n"/>
       <c r="L887" s="3" t="n"/>
+      <c r="M887" s="3" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="3" t="n"/>
@@ -13069,6 +13966,7 @@
       <c r="J888" s="3" t="n"/>
       <c r="K888" s="3" t="n"/>
       <c r="L888" s="3" t="n"/>
+      <c r="M888" s="3" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="3" t="n"/>
@@ -13083,6 +13981,7 @@
       <c r="J889" s="3" t="n"/>
       <c r="K889" s="3" t="n"/>
       <c r="L889" s="3" t="n"/>
+      <c r="M889" s="3" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="3" t="n"/>
@@ -13097,6 +13996,7 @@
       <c r="J890" s="3" t="n"/>
       <c r="K890" s="3" t="n"/>
       <c r="L890" s="3" t="n"/>
+      <c r="M890" s="3" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="3" t="n"/>
@@ -13111,6 +14011,7 @@
       <c r="J891" s="3" t="n"/>
       <c r="K891" s="3" t="n"/>
       <c r="L891" s="3" t="n"/>
+      <c r="M891" s="3" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="3" t="n"/>
@@ -13125,6 +14026,7 @@
       <c r="J892" s="3" t="n"/>
       <c r="K892" s="3" t="n"/>
       <c r="L892" s="3" t="n"/>
+      <c r="M892" s="3" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="3" t="n"/>
@@ -13139,6 +14041,7 @@
       <c r="J893" s="3" t="n"/>
       <c r="K893" s="3" t="n"/>
       <c r="L893" s="3" t="n"/>
+      <c r="M893" s="3" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="3" t="n"/>
@@ -13153,6 +14056,7 @@
       <c r="J894" s="3" t="n"/>
       <c r="K894" s="3" t="n"/>
       <c r="L894" s="3" t="n"/>
+      <c r="M894" s="3" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="3" t="n"/>
@@ -13167,6 +14071,7 @@
       <c r="J895" s="3" t="n"/>
       <c r="K895" s="3" t="n"/>
       <c r="L895" s="3" t="n"/>
+      <c r="M895" s="3" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="3" t="n"/>
@@ -13181,6 +14086,7 @@
       <c r="J896" s="3" t="n"/>
       <c r="K896" s="3" t="n"/>
       <c r="L896" s="3" t="n"/>
+      <c r="M896" s="3" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="3" t="n"/>
@@ -13195,6 +14101,7 @@
       <c r="J897" s="3" t="n"/>
       <c r="K897" s="3" t="n"/>
       <c r="L897" s="3" t="n"/>
+      <c r="M897" s="3" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="3" t="n"/>
@@ -13209,6 +14116,7 @@
       <c r="J898" s="3" t="n"/>
       <c r="K898" s="3" t="n"/>
       <c r="L898" s="3" t="n"/>
+      <c r="M898" s="3" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="3" t="n"/>
@@ -13223,6 +14131,7 @@
       <c r="J899" s="3" t="n"/>
       <c r="K899" s="3" t="n"/>
       <c r="L899" s="3" t="n"/>
+      <c r="M899" s="3" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="3" t="n"/>
@@ -13237,6 +14146,7 @@
       <c r="J900" s="3" t="n"/>
       <c r="K900" s="3" t="n"/>
       <c r="L900" s="3" t="n"/>
+      <c r="M900" s="3" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="3" t="n"/>
@@ -13251,6 +14161,7 @@
       <c r="J901" s="3" t="n"/>
       <c r="K901" s="3" t="n"/>
       <c r="L901" s="3" t="n"/>
+      <c r="M901" s="3" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="3" t="n"/>
@@ -13265,6 +14176,7 @@
       <c r="J902" s="3" t="n"/>
       <c r="K902" s="3" t="n"/>
       <c r="L902" s="3" t="n"/>
+      <c r="M902" s="3" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="3" t="n"/>
@@ -13279,6 +14191,7 @@
       <c r="J903" s="3" t="n"/>
       <c r="K903" s="3" t="n"/>
       <c r="L903" s="3" t="n"/>
+      <c r="M903" s="3" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="3" t="n"/>
@@ -13293,6 +14206,7 @@
       <c r="J904" s="3" t="n"/>
       <c r="K904" s="3" t="n"/>
       <c r="L904" s="3" t="n"/>
+      <c r="M904" s="3" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="3" t="n"/>
@@ -13307,6 +14221,7 @@
       <c r="J905" s="3" t="n"/>
       <c r="K905" s="3" t="n"/>
       <c r="L905" s="3" t="n"/>
+      <c r="M905" s="3" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="3" t="n"/>
@@ -13321,6 +14236,7 @@
       <c r="J906" s="3" t="n"/>
       <c r="K906" s="3" t="n"/>
       <c r="L906" s="3" t="n"/>
+      <c r="M906" s="3" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="3" t="n"/>
@@ -13335,6 +14251,7 @@
       <c r="J907" s="3" t="n"/>
       <c r="K907" s="3" t="n"/>
       <c r="L907" s="3" t="n"/>
+      <c r="M907" s="3" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="3" t="n"/>
@@ -13349,6 +14266,7 @@
       <c r="J908" s="3" t="n"/>
       <c r="K908" s="3" t="n"/>
       <c r="L908" s="3" t="n"/>
+      <c r="M908" s="3" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="3" t="n"/>
@@ -13363,6 +14281,7 @@
       <c r="J909" s="3" t="n"/>
       <c r="K909" s="3" t="n"/>
       <c r="L909" s="3" t="n"/>
+      <c r="M909" s="3" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="3" t="n"/>
@@ -13377,6 +14296,7 @@
       <c r="J910" s="3" t="n"/>
       <c r="K910" s="3" t="n"/>
       <c r="L910" s="3" t="n"/>
+      <c r="M910" s="3" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="3" t="n"/>
@@ -13391,6 +14311,7 @@
       <c r="J911" s="3" t="n"/>
       <c r="K911" s="3" t="n"/>
       <c r="L911" s="3" t="n"/>
+      <c r="M911" s="3" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="3" t="n"/>
@@ -13405,6 +14326,7 @@
       <c r="J912" s="3" t="n"/>
       <c r="K912" s="3" t="n"/>
       <c r="L912" s="3" t="n"/>
+      <c r="M912" s="3" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="3" t="n"/>
@@ -13419,6 +14341,7 @@
       <c r="J913" s="3" t="n"/>
       <c r="K913" s="3" t="n"/>
       <c r="L913" s="3" t="n"/>
+      <c r="M913" s="3" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="3" t="n"/>
@@ -13433,6 +14356,7 @@
       <c r="J914" s="3" t="n"/>
       <c r="K914" s="3" t="n"/>
       <c r="L914" s="3" t="n"/>
+      <c r="M914" s="3" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="3" t="n"/>
@@ -13447,6 +14371,7 @@
       <c r="J915" s="3" t="n"/>
       <c r="K915" s="3" t="n"/>
       <c r="L915" s="3" t="n"/>
+      <c r="M915" s="3" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="3" t="n"/>
@@ -13461,6 +14386,7 @@
       <c r="J916" s="3" t="n"/>
       <c r="K916" s="3" t="n"/>
       <c r="L916" s="3" t="n"/>
+      <c r="M916" s="3" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="3" t="n"/>
@@ -13475,6 +14401,7 @@
       <c r="J917" s="3" t="n"/>
       <c r="K917" s="3" t="n"/>
       <c r="L917" s="3" t="n"/>
+      <c r="M917" s="3" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="3" t="n"/>
@@ -13489,6 +14416,7 @@
       <c r="J918" s="3" t="n"/>
       <c r="K918" s="3" t="n"/>
       <c r="L918" s="3" t="n"/>
+      <c r="M918" s="3" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="3" t="n"/>
@@ -13503,6 +14431,7 @@
       <c r="J919" s="3" t="n"/>
       <c r="K919" s="3" t="n"/>
       <c r="L919" s="3" t="n"/>
+      <c r="M919" s="3" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="3" t="n"/>
@@ -13517,6 +14446,7 @@
       <c r="J920" s="3" t="n"/>
       <c r="K920" s="3" t="n"/>
       <c r="L920" s="3" t="n"/>
+      <c r="M920" s="3" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="3" t="n"/>
@@ -13531,6 +14461,7 @@
       <c r="J921" s="3" t="n"/>
       <c r="K921" s="3" t="n"/>
       <c r="L921" s="3" t="n"/>
+      <c r="M921" s="3" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="3" t="n"/>
@@ -13545,6 +14476,7 @@
       <c r="J922" s="3" t="n"/>
       <c r="K922" s="3" t="n"/>
       <c r="L922" s="3" t="n"/>
+      <c r="M922" s="3" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="3" t="n"/>
@@ -13559,6 +14491,7 @@
       <c r="J923" s="3" t="n"/>
       <c r="K923" s="3" t="n"/>
       <c r="L923" s="3" t="n"/>
+      <c r="M923" s="3" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="3" t="n"/>
@@ -13573,6 +14506,7 @@
       <c r="J924" s="3" t="n"/>
       <c r="K924" s="3" t="n"/>
       <c r="L924" s="3" t="n"/>
+      <c r="M924" s="3" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="3" t="n"/>
@@ -13587,6 +14521,7 @@
       <c r="J925" s="3" t="n"/>
       <c r="K925" s="3" t="n"/>
       <c r="L925" s="3" t="n"/>
+      <c r="M925" s="3" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="3" t="n"/>
@@ -13601,6 +14536,7 @@
       <c r="J926" s="3" t="n"/>
       <c r="K926" s="3" t="n"/>
       <c r="L926" s="3" t="n"/>
+      <c r="M926" s="3" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="3" t="n"/>
@@ -13615,6 +14551,7 @@
       <c r="J927" s="3" t="n"/>
       <c r="K927" s="3" t="n"/>
       <c r="L927" s="3" t="n"/>
+      <c r="M927" s="3" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="3" t="n"/>
@@ -13629,6 +14566,7 @@
       <c r="J928" s="3" t="n"/>
       <c r="K928" s="3" t="n"/>
       <c r="L928" s="3" t="n"/>
+      <c r="M928" s="3" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="3" t="n"/>
@@ -13643,6 +14581,7 @@
       <c r="J929" s="3" t="n"/>
       <c r="K929" s="3" t="n"/>
       <c r="L929" s="3" t="n"/>
+      <c r="M929" s="3" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="3" t="n"/>
@@ -13657,6 +14596,7 @@
       <c r="J930" s="3" t="n"/>
       <c r="K930" s="3" t="n"/>
       <c r="L930" s="3" t="n"/>
+      <c r="M930" s="3" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="3" t="n"/>
@@ -13671,6 +14611,7 @@
       <c r="J931" s="3" t="n"/>
       <c r="K931" s="3" t="n"/>
       <c r="L931" s="3" t="n"/>
+      <c r="M931" s="3" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="3" t="n"/>
@@ -13685,6 +14626,7 @@
       <c r="J932" s="3" t="n"/>
       <c r="K932" s="3" t="n"/>
       <c r="L932" s="3" t="n"/>
+      <c r="M932" s="3" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="3" t="n"/>
@@ -13699,6 +14641,7 @@
       <c r="J933" s="3" t="n"/>
       <c r="K933" s="3" t="n"/>
       <c r="L933" s="3" t="n"/>
+      <c r="M933" s="3" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="3" t="n"/>
@@ -13713,6 +14656,7 @@
       <c r="J934" s="3" t="n"/>
       <c r="K934" s="3" t="n"/>
       <c r="L934" s="3" t="n"/>
+      <c r="M934" s="3" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="3" t="n"/>
@@ -13727,6 +14671,7 @@
       <c r="J935" s="3" t="n"/>
       <c r="K935" s="3" t="n"/>
       <c r="L935" s="3" t="n"/>
+      <c r="M935" s="3" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="3" t="n"/>
@@ -13741,6 +14686,7 @@
       <c r="J936" s="3" t="n"/>
       <c r="K936" s="3" t="n"/>
       <c r="L936" s="3" t="n"/>
+      <c r="M936" s="3" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="3" t="n"/>
@@ -13755,6 +14701,7 @@
       <c r="J937" s="3" t="n"/>
       <c r="K937" s="3" t="n"/>
       <c r="L937" s="3" t="n"/>
+      <c r="M937" s="3" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="3" t="n"/>
@@ -13769,6 +14716,7 @@
       <c r="J938" s="3" t="n"/>
       <c r="K938" s="3" t="n"/>
       <c r="L938" s="3" t="n"/>
+      <c r="M938" s="3" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="3" t="n"/>
@@ -13783,6 +14731,7 @@
       <c r="J939" s="3" t="n"/>
       <c r="K939" s="3" t="n"/>
       <c r="L939" s="3" t="n"/>
+      <c r="M939" s="3" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="3" t="n"/>
@@ -13797,6 +14746,7 @@
       <c r="J940" s="3" t="n"/>
       <c r="K940" s="3" t="n"/>
       <c r="L940" s="3" t="n"/>
+      <c r="M940" s="3" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="3" t="n"/>
@@ -13811,6 +14761,7 @@
       <c r="J941" s="3" t="n"/>
       <c r="K941" s="3" t="n"/>
       <c r="L941" s="3" t="n"/>
+      <c r="M941" s="3" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="3" t="n"/>
@@ -13825,6 +14776,7 @@
       <c r="J942" s="3" t="n"/>
       <c r="K942" s="3" t="n"/>
       <c r="L942" s="3" t="n"/>
+      <c r="M942" s="3" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="3" t="n"/>
@@ -13839,6 +14791,7 @@
       <c r="J943" s="3" t="n"/>
       <c r="K943" s="3" t="n"/>
       <c r="L943" s="3" t="n"/>
+      <c r="M943" s="3" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="3" t="n"/>
@@ -13853,6 +14806,7 @@
       <c r="J944" s="3" t="n"/>
       <c r="K944" s="3" t="n"/>
       <c r="L944" s="3" t="n"/>
+      <c r="M944" s="3" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="3" t="n"/>
@@ -13867,6 +14821,7 @@
       <c r="J945" s="3" t="n"/>
       <c r="K945" s="3" t="n"/>
       <c r="L945" s="3" t="n"/>
+      <c r="M945" s="3" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="3" t="n"/>
@@ -13881,6 +14836,7 @@
       <c r="J946" s="3" t="n"/>
       <c r="K946" s="3" t="n"/>
       <c r="L946" s="3" t="n"/>
+      <c r="M946" s="3" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="3" t="n"/>
@@ -13895,6 +14851,7 @@
       <c r="J947" s="3" t="n"/>
       <c r="K947" s="3" t="n"/>
       <c r="L947" s="3" t="n"/>
+      <c r="M947" s="3" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="3" t="n"/>
@@ -13909,6 +14866,7 @@
       <c r="J948" s="3" t="n"/>
       <c r="K948" s="3" t="n"/>
       <c r="L948" s="3" t="n"/>
+      <c r="M948" s="3" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="3" t="n"/>
@@ -13923,6 +14881,7 @@
       <c r="J949" s="3" t="n"/>
       <c r="K949" s="3" t="n"/>
       <c r="L949" s="3" t="n"/>
+      <c r="M949" s="3" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="3" t="n"/>
@@ -13937,6 +14896,7 @@
       <c r="J950" s="3" t="n"/>
       <c r="K950" s="3" t="n"/>
       <c r="L950" s="3" t="n"/>
+      <c r="M950" s="3" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="3" t="n"/>
@@ -13951,6 +14911,7 @@
       <c r="J951" s="3" t="n"/>
       <c r="K951" s="3" t="n"/>
       <c r="L951" s="3" t="n"/>
+      <c r="M951" s="3" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="3" t="n"/>
@@ -13965,6 +14926,7 @@
       <c r="J952" s="3" t="n"/>
       <c r="K952" s="3" t="n"/>
       <c r="L952" s="3" t="n"/>
+      <c r="M952" s="3" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="3" t="n"/>
@@ -13979,6 +14941,7 @@
       <c r="J953" s="3" t="n"/>
       <c r="K953" s="3" t="n"/>
       <c r="L953" s="3" t="n"/>
+      <c r="M953" s="3" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="3" t="n"/>
@@ -13993,6 +14956,7 @@
       <c r="J954" s="3" t="n"/>
       <c r="K954" s="3" t="n"/>
       <c r="L954" s="3" t="n"/>
+      <c r="M954" s="3" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="3" t="n"/>
@@ -14007,6 +14971,7 @@
       <c r="J955" s="3" t="n"/>
       <c r="K955" s="3" t="n"/>
       <c r="L955" s="3" t="n"/>
+      <c r="M955" s="3" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="3" t="n"/>
@@ -14021,6 +14986,7 @@
       <c r="J956" s="3" t="n"/>
       <c r="K956" s="3" t="n"/>
       <c r="L956" s="3" t="n"/>
+      <c r="M956" s="3" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="3" t="n"/>
@@ -14035,6 +15001,7 @@
       <c r="J957" s="3" t="n"/>
       <c r="K957" s="3" t="n"/>
       <c r="L957" s="3" t="n"/>
+      <c r="M957" s="3" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="3" t="n"/>
@@ -14049,6 +15016,7 @@
       <c r="J958" s="3" t="n"/>
       <c r="K958" s="3" t="n"/>
       <c r="L958" s="3" t="n"/>
+      <c r="M958" s="3" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="3" t="n"/>
@@ -14063,6 +15031,7 @@
       <c r="J959" s="3" t="n"/>
       <c r="K959" s="3" t="n"/>
       <c r="L959" s="3" t="n"/>
+      <c r="M959" s="3" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="3" t="n"/>
@@ -14077,6 +15046,7 @@
       <c r="J960" s="3" t="n"/>
       <c r="K960" s="3" t="n"/>
       <c r="L960" s="3" t="n"/>
+      <c r="M960" s="3" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="3" t="n"/>
@@ -14091,6 +15061,7 @@
       <c r="J961" s="3" t="n"/>
       <c r="K961" s="3" t="n"/>
       <c r="L961" s="3" t="n"/>
+      <c r="M961" s="3" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="3" t="n"/>
@@ -14105,6 +15076,7 @@
       <c r="J962" s="3" t="n"/>
       <c r="K962" s="3" t="n"/>
       <c r="L962" s="3" t="n"/>
+      <c r="M962" s="3" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="3" t="n"/>
@@ -14119,6 +15091,7 @@
       <c r="J963" s="3" t="n"/>
       <c r="K963" s="3" t="n"/>
       <c r="L963" s="3" t="n"/>
+      <c r="M963" s="3" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="3" t="n"/>
@@ -14133,6 +15106,7 @@
       <c r="J964" s="3" t="n"/>
       <c r="K964" s="3" t="n"/>
       <c r="L964" s="3" t="n"/>
+      <c r="M964" s="3" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="3" t="n"/>
@@ -14147,6 +15121,7 @@
       <c r="J965" s="3" t="n"/>
       <c r="K965" s="3" t="n"/>
       <c r="L965" s="3" t="n"/>
+      <c r="M965" s="3" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="3" t="n"/>
@@ -14161,6 +15136,7 @@
       <c r="J966" s="3" t="n"/>
       <c r="K966" s="3" t="n"/>
       <c r="L966" s="3" t="n"/>
+      <c r="M966" s="3" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="3" t="n"/>
@@ -14175,6 +15151,7 @@
       <c r="J967" s="3" t="n"/>
       <c r="K967" s="3" t="n"/>
       <c r="L967" s="3" t="n"/>
+      <c r="M967" s="3" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="3" t="n"/>
@@ -14189,6 +15166,7 @@
       <c r="J968" s="3" t="n"/>
       <c r="K968" s="3" t="n"/>
       <c r="L968" s="3" t="n"/>
+      <c r="M968" s="3" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="3" t="n"/>
@@ -14203,6 +15181,7 @@
       <c r="J969" s="3" t="n"/>
       <c r="K969" s="3" t="n"/>
       <c r="L969" s="3" t="n"/>
+      <c r="M969" s="3" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="3" t="n"/>
@@ -14217,6 +15196,7 @@
       <c r="J970" s="3" t="n"/>
       <c r="K970" s="3" t="n"/>
       <c r="L970" s="3" t="n"/>
+      <c r="M970" s="3" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="3" t="n"/>
@@ -14231,6 +15211,7 @@
       <c r="J971" s="3" t="n"/>
       <c r="K971" s="3" t="n"/>
       <c r="L971" s="3" t="n"/>
+      <c r="M971" s="3" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="3" t="n"/>
@@ -14245,6 +15226,7 @@
       <c r="J972" s="3" t="n"/>
       <c r="K972" s="3" t="n"/>
       <c r="L972" s="3" t="n"/>
+      <c r="M972" s="3" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="3" t="n"/>
@@ -14259,6 +15241,7 @@
       <c r="J973" s="3" t="n"/>
       <c r="K973" s="3" t="n"/>
       <c r="L973" s="3" t="n"/>
+      <c r="M973" s="3" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="3" t="n"/>
@@ -14273,6 +15256,7 @@
       <c r="J974" s="3" t="n"/>
       <c r="K974" s="3" t="n"/>
       <c r="L974" s="3" t="n"/>
+      <c r="M974" s="3" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="3" t="n"/>
@@ -14287,6 +15271,7 @@
       <c r="J975" s="3" t="n"/>
       <c r="K975" s="3" t="n"/>
       <c r="L975" s="3" t="n"/>
+      <c r="M975" s="3" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="3" t="n"/>
@@ -14301,6 +15286,7 @@
       <c r="J976" s="3" t="n"/>
       <c r="K976" s="3" t="n"/>
       <c r="L976" s="3" t="n"/>
+      <c r="M976" s="3" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="3" t="n"/>
@@ -14315,6 +15301,7 @@
       <c r="J977" s="3" t="n"/>
       <c r="K977" s="3" t="n"/>
       <c r="L977" s="3" t="n"/>
+      <c r="M977" s="3" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="3" t="n"/>
@@ -14329,6 +15316,7 @@
       <c r="J978" s="3" t="n"/>
       <c r="K978" s="3" t="n"/>
       <c r="L978" s="3" t="n"/>
+      <c r="M978" s="3" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="3" t="n"/>
@@ -14343,6 +15331,7 @@
       <c r="J979" s="3" t="n"/>
       <c r="K979" s="3" t="n"/>
       <c r="L979" s="3" t="n"/>
+      <c r="M979" s="3" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="3" t="n"/>
@@ -14357,6 +15346,7 @@
       <c r="J980" s="3" t="n"/>
       <c r="K980" s="3" t="n"/>
       <c r="L980" s="3" t="n"/>
+      <c r="M980" s="3" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="3" t="n"/>
@@ -14371,6 +15361,7 @@
       <c r="J981" s="3" t="n"/>
       <c r="K981" s="3" t="n"/>
       <c r="L981" s="3" t="n"/>
+      <c r="M981" s="3" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="3" t="n"/>
@@ -14385,6 +15376,7 @@
       <c r="J982" s="3" t="n"/>
       <c r="K982" s="3" t="n"/>
       <c r="L982" s="3" t="n"/>
+      <c r="M982" s="3" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="3" t="n"/>
@@ -14399,6 +15391,7 @@
       <c r="J983" s="3" t="n"/>
       <c r="K983" s="3" t="n"/>
       <c r="L983" s="3" t="n"/>
+      <c r="M983" s="3" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="3" t="n"/>
@@ -14413,6 +15406,7 @@
       <c r="J984" s="3" t="n"/>
       <c r="K984" s="3" t="n"/>
       <c r="L984" s="3" t="n"/>
+      <c r="M984" s="3" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="3" t="n"/>
@@ -14427,6 +15421,7 @@
       <c r="J985" s="3" t="n"/>
       <c r="K985" s="3" t="n"/>
       <c r="L985" s="3" t="n"/>
+      <c r="M985" s="3" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="3" t="n"/>
@@ -14441,6 +15436,7 @@
       <c r="J986" s="3" t="n"/>
       <c r="K986" s="3" t="n"/>
       <c r="L986" s="3" t="n"/>
+      <c r="M986" s="3" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="3" t="n"/>
@@ -14455,6 +15451,7 @@
       <c r="J987" s="3" t="n"/>
       <c r="K987" s="3" t="n"/>
       <c r="L987" s="3" t="n"/>
+      <c r="M987" s="3" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="3" t="n"/>
@@ -14469,6 +15466,7 @@
       <c r="J988" s="3" t="n"/>
       <c r="K988" s="3" t="n"/>
       <c r="L988" s="3" t="n"/>
+      <c r="M988" s="3" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="3" t="n"/>
@@ -14483,6 +15481,7 @@
       <c r="J989" s="3" t="n"/>
       <c r="K989" s="3" t="n"/>
       <c r="L989" s="3" t="n"/>
+      <c r="M989" s="3" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="3" t="n"/>
@@ -14497,6 +15496,7 @@
       <c r="J990" s="3" t="n"/>
       <c r="K990" s="3" t="n"/>
       <c r="L990" s="3" t="n"/>
+      <c r="M990" s="3" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="3" t="n"/>
@@ -14511,6 +15511,7 @@
       <c r="J991" s="3" t="n"/>
       <c r="K991" s="3" t="n"/>
       <c r="L991" s="3" t="n"/>
+      <c r="M991" s="3" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="3" t="n"/>
@@ -14525,6 +15526,7 @@
       <c r="J992" s="3" t="n"/>
       <c r="K992" s="3" t="n"/>
       <c r="L992" s="3" t="n"/>
+      <c r="M992" s="3" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="3" t="n"/>
@@ -14539,6 +15541,7 @@
       <c r="J993" s="3" t="n"/>
       <c r="K993" s="3" t="n"/>
       <c r="L993" s="3" t="n"/>
+      <c r="M993" s="3" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="3" t="n"/>
@@ -14553,6 +15556,7 @@
       <c r="J994" s="3" t="n"/>
       <c r="K994" s="3" t="n"/>
       <c r="L994" s="3" t="n"/>
+      <c r="M994" s="3" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="3" t="n"/>
@@ -14567,6 +15571,7 @@
       <c r="J995" s="3" t="n"/>
       <c r="K995" s="3" t="n"/>
       <c r="L995" s="3" t="n"/>
+      <c r="M995" s="3" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="3" t="n"/>
@@ -14581,6 +15586,7 @@
       <c r="J996" s="3" t="n"/>
       <c r="K996" s="3" t="n"/>
       <c r="L996" s="3" t="n"/>
+      <c r="M996" s="3" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="3" t="n"/>
@@ -14595,6 +15601,7 @@
       <c r="J997" s="3" t="n"/>
       <c r="K997" s="3" t="n"/>
       <c r="L997" s="3" t="n"/>
+      <c r="M997" s="3" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="3" t="n"/>
@@ -14609,6 +15616,7 @@
       <c r="J998" s="3" t="n"/>
       <c r="K998" s="3" t="n"/>
       <c r="L998" s="3" t="n"/>
+      <c r="M998" s="3" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="3" t="n"/>
@@ -14623,6 +15631,7 @@
       <c r="J999" s="3" t="n"/>
       <c r="K999" s="3" t="n"/>
       <c r="L999" s="3" t="n"/>
+      <c r="M999" s="3" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="3" t="n"/>
@@ -14637,6 +15646,7 @@
       <c r="J1000" s="3" t="n"/>
       <c r="K1000" s="3" t="n"/>
       <c r="L1000" s="3" t="n"/>
+      <c r="M1000" s="3" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="3" t="n"/>
@@ -14651,13 +15661,14 @@
       <c r="J1001" s="3" t="n"/>
       <c r="K1001" s="3" t="n"/>
       <c r="L1001" s="3" t="n"/>
+      <c r="M1001" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A2:A1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Catégorie" error="Choisissez Filtre ou PDR." type="list" errorStyle="stop">
       <formula1>=Listes!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Engin inconnu" error="Ce code engin n'existe pas dans la liste des engins de l'application." type="list" errorStyle="stop">
+    <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Engin inconnu" error="Ce code engin n'existe pas dans la liste des engins de l'application." type="list" errorStyle="stop">
       <formula1>=Listes!$B$2:$B$173</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Date" error="Saisissez une date au format jj/mm/aaaa." type="date" operator="greaterThan">
@@ -19069,7 +20080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M32"/>
+  <dimension ref="B1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -19083,8 +20094,9 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19222,174 +20234,191 @@
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>• Engin destinataire : Code engin (liste). Vide = stock commun.</t>
+          <t>• Fournisseur : Nom du fournisseur (facultatif).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="10" t="inlineStr">
         <is>
+          <t>• Engin destinataire : Code engin (liste). Vide = stock commun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
           <t>• Observations : Remarque libre.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="10" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Règles utiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>• Une commande pas encore livrée : remplissez Qté demandée (BC), laissez Qté livrée (BL) vide. Elle apparaît dans « Commandés non livrés ».</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>• Filtres et PDR peuvent être mélangés dans le même fichier grâce à la colonne Catégorie.</t>
+          <t>• Une commande pas encore livrée : remplissez Qté demandée (BC), laissez Qté livrée (BL) vide. Elle apparaît dans « Commandés non livrés ».</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>• Une ligne identique déjà saisie (même date, référence, quantités, N° BL) est signalée « doublon possible » et ignorée par défaut.</t>
+          <t>• Filtres et PDR peuvent être mélangés dans le même fichier grâce à la colonne Catégorie.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="10" t="inlineStr">
         <is>
+          <t>• Une ligne identique déjà saisie (même date, référence, quantités, N° BL) est signalée « doublon possible » et ignorée par défaut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
           <t>• Gardez les références en texte (les zéros au début sont conservés).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="10" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Exemple de ligne correctement remplie (à ne pas recopier dans « Import »)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="12" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Référence</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Désignation / type</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Réf. équivalentes</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>Qté demandée (BC)</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>Qté livrée (BL)</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>N° BC</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>N° BL</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>Engin destinataire</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="N32" s="12" t="inlineStr">
         <is>
           <t>Observations</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="13" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Filtre</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C33" s="14" t="n">
         <v>46309</v>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>P550820</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>FILTRE A HUILE</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>DONALDSON</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="13" t="n">
+      <c r="G33" s="13" t="inlineStr"/>
+      <c r="H33" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="J32" s="13" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>4400044415</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>BL-1201</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>SOCIETE X</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
         <is>
           <t>50406</t>
         </is>
       </c>
-      <c r="M32" s="13" t="inlineStr"/>
+      <c r="N33" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
